--- a/Excel/9_Refrigerants_WIP_v02.xlsx
+++ b/Excel/9_Refrigerants_WIP_v02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1864875-6D00-4364-8024-3BF184F25CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464D31BE-555F-4C23-87C5-0D88A2EB1C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="795" yWindow="855" windowWidth="36900" windowHeight="18960" firstSheet="1" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -19,8 +19,11 @@
     <sheet name="Input - Refrigerants" sheetId="70" r:id="rId4"/>
     <sheet name="9.1.1.1-2 Refrigerant use" sheetId="69" r:id="rId5"/>
     <sheet name="Constants - Refrigerants" sheetId="110" r:id="rId6"/>
-    <sheet name="Constants - Common" sheetId="111" r:id="rId7"/>
+    <sheet name="Constants - Common" sheetId="119" r:id="rId7"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId8"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -186,9 +189,12 @@
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.Livestock_LookupMCFState">_xlfn.LAMBDA(_xlpm.MMS,_xlpm.MMSArray,_xlpm.State,_xlpm.StateArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateArray, _xlpm.ReturnArray)))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain" localSheetId="6">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth" localSheetId="6">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth">_xlfn.LAMBDA(_xlpm.HeadAtStart,_xlpm.Month,_xlpm.LivestockClass, _xlpm.HeadAtStart + [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth" localSheetId="6">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStartOfMonth, MAX(_xlpm.HeadAtStartOfMonth - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.WeightAtMovementDate,_xlpm.Head, IFERROR(_xlpm.Head * (_xlpm.WeightAtMovementDate + [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate)), 0))</definedName>
@@ -200,9 +206,12 @@
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightRemainingHead(_xlpm.Month, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth" localSheetId="6">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth" localSheetId="6">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Fertiliser_Equations_Lime.VEERG_5_3_1_1__1_LimeApplication">_xlfn.LAMBDA(_xlpm.Mlime,_xlpm.FracLime,_xlpm.Plime,_xlpm.EFlime,_xlpm.FracDol,_xlpm.Pdol,_xlpm.EFdol,_xlpm.CgCO2, ((_xlpm.Mlime * _xlpm.FracLime * _xlpm.Plime * _xlpm.EFlime) + (_xlpm.Mlime * _xlpm.FracDol * _xlpm.Pdol * _xlpm.EFdol)) * _xlpm.CgCO2 * 10 ^ -3)</definedName>
     <definedName name="Fertiliser_Equations_Organic.VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser">_xlfn.LAMBDA(_xlpm.Morganicjf,_xlpm.FNorganicf, _xlpm.Morganicjf * _xlpm.FNorganicf)</definedName>
     <definedName name="Fuel_Equations.VEERG_8_1_1_1__1_FuelCombustionTransport">_xlfn.LAMBDA(_xlpm.Q_Transtq,_xlpm.EC_Transq,_xlpm.EF_Trans1tqg, Fuel_Equations.VEERG_8_FuelCombustion(_xlpm.Q_Transtq, _xlpm.EC_Transq, _xlpm.EF_Trans1tqg))</definedName>
@@ -260,6 +269,20 @@
     <definedName name="Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Title">_xlfn.LAMBDA(("Fuel scope 3 emission factors - Stationary gaseous fuels"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Variation">_xlfn.LAMBDA(("VARIATION OF SOURCE DATA: NSW and ACT split into separate rows. 'C' Values for Tasmania and Northern Territory replaced with those for Victoria and Western Australia respectively. (See appendices)"))</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="Inoput_Cell_Livestock_antibiotics">#REF!</definedName>
+    <definedName name="Inoput_Cell_Livestockantibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_CO2_for_carbonation">#REF!</definedName>
+    <definedName name="Input_Cell_CO2forcarbonation">#REF!</definedName>
+    <definedName name="Input_Cell_Livestock_antibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_Livestock_tags">#REF!</definedName>
+    <definedName name="Input_Cell_LivestockAntibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_Nylon_netting_for_horticulture">#REF!</definedName>
+    <definedName name="Input_Cell_Nylonnettingforhorticulture">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets__Plastic">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets__Wood">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets_Plastic">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets_Wood">#REF!</definedName>
+    <definedName name="Range_LivestockStartingValues">#REF!</definedName>
     <definedName name="Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking">_xlfn.LAMBDA(_xlpm.charge_Ra,_xlpm.leakagerate_a, (_xlpm.charge_Ra * (_xlpm.leakagerate_a / 100)) * 10 ^ -3)</definedName>
     <definedName name="Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"charge_Ra","Amount of refrigerant R contained in appliance a","kg","Input";"leakagerate_a","Prcentage of total charge leaked from appliance a each year","Percent","Constant";"a","Appliance type","","Input";"R","Refrigerant","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking_LatexEquation">_xlfn.LAMBDA("E_R = \sum\nolimits_a \left( charge_{Ra} \times \frac{leakage\,rate_a}{100} \right) \times 10^{-3}")</definedName>
@@ -292,6 +315,9 @@
     <definedName name="Refrigerants_SourceData.Refrigerants_LeakageRates_Source">_xlfn.LAMBDA(("Australian National Greenhouse Accounts Factors 2025 - Table 10"))</definedName>
     <definedName name="Refrigerants_SourceData.Refrigerants_LeakageRates_Title">_xlfn.LAMBDA(("Indicative leakage rates for common refrigeration and air - conditioning equipment"))</definedName>
     <definedName name="Refrigerants_SourceData.Refrigerants_LeakageRates_Variation">_xlfn.LAMBDA((""))</definedName>
+    <definedName name="Step1">#REF!</definedName>
+    <definedName name="Step2">#REF!</definedName>
+    <definedName name="Step3">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1709,7 +1735,7 @@
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -1919,9 +1945,6 @@
     <xf numFmtId="0" fontId="48" fillId="4" borderId="2" xfId="52" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="56" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="50" fillId="4" borderId="1" xfId="8" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2001,177 +2024,7 @@
     <cellStyle name="Variable type input" xfId="62" xr:uid="{83ED2376-8555-47B3-98E3-2416CC880284}"/>
     <cellStyle name="Variable type other" xfId="63" xr:uid="{6646F6F7-E4F9-4165-8015-E25083532B5B}"/>
   </cellStyles>
-  <dxfs count="65">
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="60">
     <dxf>
       <font>
         <b val="0"/>
@@ -3038,6 +2891,126 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1" tint="0.24994659260841701"/>
       </font>
       <fill>
@@ -3238,20 +3211,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="64"/>
-      <tableStyleElement type="headerRow" dxfId="63"/>
-      <tableStyleElement type="totalRow" dxfId="62"/>
-      <tableStyleElement type="firstColumn" dxfId="61"/>
-      <tableStyleElement type="firstRowStripe" dxfId="60"/>
-      <tableStyleElement type="secondRowStripe" dxfId="59"/>
+      <tableStyleElement type="wholeTable" dxfId="59"/>
+      <tableStyleElement type="headerRow" dxfId="58"/>
+      <tableStyleElement type="totalRow" dxfId="57"/>
+      <tableStyleElement type="firstColumn" dxfId="56"/>
+      <tableStyleElement type="firstRowStripe" dxfId="55"/>
+      <tableStyleElement type="secondRowStripe" dxfId="54"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="58"/>
-      <tableStyleElement type="headerRow" dxfId="57"/>
-      <tableStyleElement type="totalRow" dxfId="56"/>
-      <tableStyleElement type="firstColumn" dxfId="55"/>
-      <tableStyleElement type="firstRowStripe" dxfId="54"/>
-      <tableStyleElement type="secondRowStripe" dxfId="53"/>
+      <tableStyleElement type="wholeTable" dxfId="53"/>
+      <tableStyleElement type="headerRow" dxfId="52"/>
+      <tableStyleElement type="totalRow" dxfId="51"/>
+      <tableStyleElement type="firstColumn" dxfId="50"/>
+      <tableStyleElement type="firstRowStripe" dxfId="49"/>
+      <tableStyleElement type="secondRowStripe" dxfId="48"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -3844,8 +3817,8 @@
       <xdr:rowOff>54909</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2898358" cy="380361"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -4257,7 +4230,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -4344,8 +4317,8 @@
       <xdr:rowOff>159124</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2279022" cy="168829"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -4387,6 +4360,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -4585,7 +4559,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -4642,6 +4616,26 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4729,7 +4723,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{5EB24DAD-7938-4A28-8102-A92DD6232701}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{23E8EA07-16D0-4744-9285-B13305AFD092}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4749,52 +4743,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{7C646E3D-156E-438B-9E75-102B5E96E255}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{AA8187F8-0042-4C0E-A158-2B1DDD89C55E}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3F6652C3-1BDE-4F33-9D5E-1BA7F24CFE1E}" name="MAT" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{EAA8886F-E011-45A8-B808-0BEFAC3A35DF}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{68D3A033-0C56-472E-A3CF-B482905871CF}" name="MAP" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{AA7B88F7-095C-4E16-9CF8-A98235D82885}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{18D7CFC5-1F89-47C0-AF12-0FD6A80AD2C8}" name="Frost days per year" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{0ECBB133-8208-4BC5-87AC-C9A17199BA63}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{694DED4D-19CA-49A7-A7A4-ED3CD36E0BA2}" name="Elevation" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{3D9AC821-75C8-4D27-BCEF-C2056472F642}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{BE47AD00-59A1-4916-A3FF-4E905492D142}" name="MAP:PET" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{D643E4EB-D004-46BD-9D3C-B84163D0D6FB}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8CD0BB0E-B9A0-4065-920B-F859089361EB}" name="Min temp" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{12A07609-F08E-4413-B6D3-C87FDF66E215}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9AD474F5-6F0E-4F15-87EA-A3E86BD8CD84}" name="Max temp" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{F102AF9F-9FEA-40DD-AF28-041C1461D83E}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4132B96D-08DF-47B8-9134-F88DA6CBA26A}" name="Min rainfall" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{90A51AC4-8B22-4441-A14C-E02D0326E5F8}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{799D2CC4-68A8-4F6B-B5E8-BA9B134CD629}" name="Max rainfall" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{3FD86231-C6F8-4A32-80AD-5D4060FD1B31}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FF3C7CFE-CC8F-4407-9CD2-DB7BCF735828}" name="Min frost days" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{73D202BF-BFCE-42FA-9D0F-2DA13C4481FC}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{9CB12B6D-F283-41CE-A0AC-7DA70F3FEA35}" name="Max frost days" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{F3AAFA92-EA40-43BB-8481-31088FE8F2A5}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{DE6B8D57-DEA5-4CDB-BEA5-6794B3B8B4C1}" name="Min elevation" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{EFBF1273-7CCE-435E-9C54-D0FC021C2D12}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F1C5507D-FFFD-4456-AAE0-9309987F0339}" name="Max elevation" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{35C9987E-D507-47A4-9DE5-D9177126FF2D}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BB91B1DF-4B57-426B-BF6A-71715747D3B2}" name="Min MAP:PET" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{F27CE1D5-2216-4EDB-B3ED-8A6CCE6C7142}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{7674CAA3-6E67-48AA-BF62-AECA84F01CB9}" name="Max MAP:PET" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{520A4B37-7DA2-48BF-AF37-03D14FA097BC}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4803,16 +4797,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{3FAC77B2-7BB0-4B78-B387-3E2D5CA67215}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{5AAD80A4-98CA-4A77-AF91-D13C800FBEDB}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9DF69629-1C76-40A4-BBA1-FB28BF754268}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{4EF58733-2135-49D9-856E-9C4907356A09}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{99A9C0E3-7924-426C-A581-5C219452362E}" name="Wet or Dry Zone" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{F7659FA5-BEFD-4223-A8BA-0F0B54D3C77A}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4821,7 +4815,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{AE4202F8-BB52-48CE-B368-8D0A44A67525}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{B4EF9EAB-A496-4FA6-9FF3-9C2DA7DF988D}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4829,16 +4823,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4BD1B715-E9FF-4B2E-A162-3DD06FA33AAE}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{692CCA7F-354D-4462-A5CC-B470737A3175}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3FDEC609-65F3-40EC-B489-B99CC8E44680}" name="MAT">
+    <tableColumn id="2" xr3:uid="{9417D96B-90BA-4033-B9C6-FDA813678B4C}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{25C140A7-4F53-46DB-A6E5-3FFA5FE81DD6}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{F61EA434-BCC2-42F2-8919-8D2C0B407D0C}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C2D4126F-3B56-4A19-AD7E-FA0C2ECA0D87}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{ECBB14F8-F7FB-45E5-B482-8ACA32BD90F9}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4847,7 +4841,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="44" xr:uid="{F8066D7D-5B7A-4C2D-96C5-0B642AEDBDD8}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{CF1750BE-922B-48E8-ADA4-66091A5A0FE9}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4855,16 +4849,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{CFC2CD32-0D6A-477F-9AB9-8CC735000875}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{4F8142C1-4652-4EFB-ACD0-F33E4ADF1A95}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{66F05498-A494-40EC-A370-E31F9319F6E9}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{C4EAC22C-2A06-49E0-913C-77E92F7B10F6}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0FEB24E7-52AA-4E09-8CAD-E3593BA1850C}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{433AECB9-327A-4C6E-8EE9-E1448F5E2DBE}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B9588CB4-A6E3-43EF-86F2-28512F6C0466}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{2AA94844-B51B-405E-B9AD-53CEE3499D09}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4873,16 +4867,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="45" xr:uid="{371EB3B0-E5DE-49F4-9F8F-370B9594177E}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{596BD446-2F05-45FD-83F3-42F2F34B5B9E}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1EC0469C-3AAC-4C25-8B45-E899791ECD1F}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{3FBF0D07-67BB-436A-9984-469656A28704}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D8738CB7-C0A6-466E-AD54-75590BF18BAC}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{EC0DCA32-396C-478E-90F8-04A7BED9BB16}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4891,16 +4885,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{8320C659-C167-4CAA-9C06-854A612436E9}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{490FA27C-33C1-4662-9AFF-006C08A4211E}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2CBE0C09-88F8-4FC0-91F9-37AD76A1AEAA}" name="Data source">
+    <tableColumn id="1" xr3:uid="{F71770D4-9368-4676-B714-C7475FF89B62}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{390BA082-D34B-4509-BBAD-72ABE42C4B39}" name="Data score">
+    <tableColumn id="2" xr3:uid="{0C157665-6F13-4351-A6EB-9119D273426C}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4909,16 +4903,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="47" xr:uid="{D7EAD11A-DC1E-416A-A0F3-2127BEE727A4}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{9B5F685E-7CFD-4B01-8F98-11C78979ED5D}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D0B2F492-E516-47ED-A029-67FEF667A678}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{75BEBE37-39B4-4E59-A52E-53C1E93F718F}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{51E6CA6F-68DC-47AB-A1BB-C75D3CA8FA3B}" name="FracWET" dataDxfId="36">
+    <tableColumn id="2" xr3:uid="{C0D50F48-A838-46A3-8B4E-BD74578D5EA5}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4927,7 +4921,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="48" xr:uid="{BE2E746E-A542-4963-9138-4CB3534F691E}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{C38EC5FD-5E4F-4880-BB81-BDF89DA918CA}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4936,19 +4930,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{10155645-FDE5-446A-BDDD-C71CD77DD825}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{CFB3196B-0D9B-41E0-81A6-84DA7CAE04DD}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A33C56B8-DAE9-434B-8228-CD6E219067F7}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{209F7857-519C-48A2-BB2E-9BCB020F651D}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{415F2F98-1C0C-4F1B-A357-E4F0898F9DA1}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{5DF0D2F4-5F2B-4DE6-ADC7-CD7463078EEE}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{364F973B-700F-4051-9AE8-A5B5A5144B24}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{EC04533A-568D-4D72-AC19-2C7248B47182}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6B401083-C682-49B6-9293-290F6E0CCE9C}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{C32F65B2-1CB1-4ABE-9FC4-BE4364E12ECE}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4957,16 +4951,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="49" xr:uid="{F2CB8BB6-7664-477A-B6EF-EAA92A00C8A0}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{89729ED1-E86C-4E41-B0BE-BE545A1501D2}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0CAEDF1E-5A86-4C59-ADB4-2A63E7ABD4DD}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{058EE474-821C-46B8-B9DB-A856FC27B7A9}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{57851871-7E08-4269-B67C-A96E5A947487}" name="FracWET" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{64C441F6-07CD-4748-BEAE-C8625EB5AEF9}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4975,16 +4969,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="50" xr:uid="{BFE0DDAE-EACA-4433-A3E7-753CE50EADFD}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{578524F2-0357-449F-ABA2-BC0D3754A4DA}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{04E57D99-757F-4374-BB84-42339A5C3083}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{A9D82E06-BBC8-48FF-87E0-4E5D302CD314}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{92543612-DE1F-4C45-B1F2-46B34452C302}" name="EFPRP" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6B8B8187-2CE6-4828-B655-AC0E679BD856}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5023,16 +5017,16 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="51" xr:uid="{31E1F417-A09B-41DA-9456-3458FDF04264}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{87C71CAF-1371-452F-BE5F-BBFF68E929C1}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5C54F0C5-3505-4964-A85B-6C95900D28A5}" name="Month">
+    <tableColumn id="1" xr3:uid="{DB86F89E-F0C6-4E23-84FA-724586BBF2C0}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DE5E22FE-C43A-4172-9EDB-6FE00B1DF854}" name="Season" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E19CC679-0382-4B3E-B2BA-CA84BD9BEC57}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5041,7 +5035,7 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="52" xr:uid="{AF70AA04-1AD5-4DF8-9CC4-5F92B5EE2A0A}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{3E8C17E0-8327-49FB-920D-57E9236C3ACA}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5061,52 +5055,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{FD606263-AC8F-4B13-96E2-C9CA0ECFC2B3}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{DD282435-2C2B-4691-B43F-3A454A86ADF0}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{328E4735-CE75-4070-9C88-AE6AC281FA52}" name="MAT (ºC)" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{9F6E82C4-3071-42FC-93D6-968F926A0031}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{AAAA9F18-86A5-4F62-9B13-8EC468FD3268}" name="Anaerobic lagoon" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{B27891F1-2A40-4958-9F1E-6BEBC12FF7C4}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{16CDDAC7-40E8-4B7E-A5A7-534574EF9960}" name="Digester / covered lagoons" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{5662A798-B4DE-4CC1-A843-7A6191D9632B}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7BE7531C-242C-4F06-B612-2455D4071B48}" name="Liquid systems" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{605030C8-492D-4496-BF8E-7FA67C7FE1EA}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4AA6EA91-67D5-4225-8E66-D79949E45C79}" name="Daily spread" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{0002A82C-EACF-411E-A58B-682D7665BB39}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A682CC91-6B5E-45D1-857C-0228079BCC7C}" name="Composting (passive windrow)" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{4BF9F484-91EC-450F-8028-73876D34E694}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{516A42DC-F452-4685-9EE1-8DB5323E888F}" name="Solid storage" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{8A5C68A4-F5AA-4764-A03E-2279AB444523}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3E59565B-237D-4BF7-8514-8C00EE69787F}" name="Pit storage" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{123BF989-3B2E-4BA3-8E54-20C4BE277CFE}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B94C989A-1174-49BC-8E63-5C88C372C925}" name="Deep litter" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{8DAAE1D4-960B-4197-A78A-30E617DF6E41}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{4E416B5A-6B9A-4444-8C96-0603C11DC870}" name="Poultry manure with bedding" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{34450AE7-D05C-4631-8EE5-4679D80792CD}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{2302252A-7FB0-4046-9B12-B1CD2F1BBED4}" name="Poultry manure without bedding" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{3C9DF90B-C67E-43D8-8207-6500A71BC3F4}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{50CED419-50AF-49B3-8F42-E496D5B781AB}" name="Direct processing" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{89E1FE1C-A229-4E74-BA5A-27BCE54D61FC}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{FACDE6F8-8A2F-4040-8D12-2E35D0831482}" name="Direct application" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{12B2DF86-A0C2-49AA-921F-AD97795AEDAB}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{2134A83A-1EB7-471E-ADAA-05ADE14C7593}" name="Pasture range and paddock" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{782429A0-44D3-4681-BFA0-84CC3419FDAC}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{1C3199CA-00F6-4D2D-9A1A-14E5576B6B3A}" name="MAT raw" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{FF208E44-6053-4431-AA07-E648AB1553AE}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5115,16 +5109,16 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1F061C8D-6288-498A-A3C6-A58C7CA98367}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
-  <autoFilter ref="D257:E259" xr:uid="{1F061C8D-6288-498A-A3C6-A58C7CA98367}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{6D5D4212-3420-44AD-9282-E9DBF49BF3A5}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+  <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6441941C-5801-414B-9EFC-BFCD02E9AABA}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{27068885-8281-4700-BCD0-1F0F37B151C2}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AFFF76A7-AEC2-426D-9FB9-7DCEAE399701}" name="EFNi &amp; EFN2Oi" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{4BCC72ED-670B-4B3C-AECD-20306DA91098}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5225,20 +5219,20 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3AE6144E-A1E7-4518-B032-EF188F35C422}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{39B225CC-22FF-489B-944A-4F2BEE1F8643}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A67EF497-7B1B-4776-9D83-A8AD1BEAF517}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{0ACCCA86-D47A-49E6-B57D-A4B7CE23D744}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6E9614A8-2F7E-4491-9C0D-E14664D3CBD5}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{B27BEAA4-A451-46EC-B597-B9703A1B45A7}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{48FCC7EC-93CF-4022-930C-DFF884BE9C3A}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{9FC59DF2-1592-4CD6-AF02-761876063B49}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5247,12 +5241,12 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{A98080EA-F2FB-4179-A336-59EF5AF50E8F}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{0A034682-B3AF-4777-98F1-9BE6449F5298}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{8E44BE92-8969-4CB0-B814-3C00C2C18F3C}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{6DBBCDA6-30C0-4638-8E70-258F978DAC2B}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5261,16 +5255,16 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{3B270221-00F4-4B48-BE2F-1F9DCAB7874A}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{591615C9-B0E8-48DF-83C0-32D82AC8F59D}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D82C5D5A-F88F-46E7-868F-025402490369}" name="Gas">
+    <tableColumn id="1" xr3:uid="{56F20BC2-56F5-427B-8FF1-7EF09C514D4E}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6DC661F8-0615-4FB7-8AE2-83962657C55A}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{C03A9D3C-DC7B-4F14-83E7-72FA50D1D978}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5279,7 +5273,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{79E591EE-C4BF-4FA2-8F75-39DA84C25602}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C2AF2589-D67C-4A7B-8DF4-E3C3EA7870C2}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5288,19 +5282,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BABC03E3-165B-407A-BF04-28738E72D28A}" name="Gas">
+    <tableColumn id="1" xr3:uid="{F494CD3D-C587-4121-ACC7-41E23F5D8191}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CF0196FE-D2CF-4F66-8847-9CE3DB549E9B}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{259B97AB-2FE6-4FFB-A603-AD4E4F868E5E}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{71C50FB6-28B8-4C5F-B7F7-F9E98423215B}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{20CFD2D3-87F3-4A7E-8D15-1F8646164388}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9E60D175-C714-4272-922B-6384C81A6A4A}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{76ABA1C2-D154-4611-93A1-492948E1A4E1}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{77C6E5B1-2CB1-4714-9B60-3FC1F2C784D3}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{E61BB90F-07C1-464B-861B-4976CFBE2EEC}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7177,10 +7171,10 @@
       <c r="F13" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="G13" s="78">
+      <c r="G13" s="70">
         <v>10</v>
       </c>
-      <c r="H13" s="78">
+      <c r="H13" s="70">
         <v>10</v>
       </c>
     </row>
@@ -7198,10 +7192,10 @@
       <c r="F14" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="G14" s="78">
+      <c r="G14" s="70">
         <v>10</v>
       </c>
-      <c r="H14" s="78">
+      <c r="H14" s="70">
         <v>10</v>
       </c>
     </row>
@@ -7408,62 +7402,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F49">
-    <cfRule type="cellIs" dxfId="16" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F129">
-    <cfRule type="cellIs" dxfId="15" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140:F141">
-    <cfRule type="cellIs" dxfId="14" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F152:F153">
-    <cfRule type="cellIs" dxfId="13" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F164:F165">
-    <cfRule type="cellIs" dxfId="12" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F252:F253">
-    <cfRule type="cellIs" dxfId="11" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F258">
-    <cfRule type="cellIs" dxfId="10" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F262:F263">
-    <cfRule type="cellIs" dxfId="9" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F286:F287">
-    <cfRule type="cellIs" dxfId="8" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F291:F292">
-    <cfRule type="cellIs" dxfId="7" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296:F297">
-    <cfRule type="cellIs" dxfId="6" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45:H47 E212:G212">
-    <cfRule type="cellIs" dxfId="5" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7844,7 +7838,7 @@
         <v>5</v>
       </c>
       <c r="I22" s="29">
-        <f>G22*H22</f>
+        <f t="shared" ref="I22:I31" si="0">G22*H22</f>
         <v>50</v>
       </c>
       <c r="J22" s="29" cm="1">
@@ -7856,7 +7850,7 @@
         <v>1.7000000000000001E-4</v>
       </c>
       <c r="L22" s="77">
-        <f>K22*H22</f>
+        <f t="shared" ref="L22:L31" si="1">K22*H22</f>
         <v>8.5000000000000006E-4</v>
       </c>
     </row>
@@ -7878,7 +7872,7 @@
         <v>5</v>
       </c>
       <c r="I23" s="29">
-        <f>G23*H23</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J23" s="29" cm="1">
@@ -7890,7 +7884,7 @@
         <v>3.5000000000000005E-4</v>
       </c>
       <c r="L23" s="77">
-        <f>K23*H23</f>
+        <f t="shared" si="1"/>
         <v>1.7500000000000003E-3</v>
       </c>
     </row>
@@ -7911,7 +7905,7 @@
         <v>13</v>
       </c>
       <c r="I24" s="29">
-        <f>G24*H24</f>
+        <f t="shared" si="0"/>
         <v>130</v>
       </c>
       <c r="J24" s="29" cm="1">
@@ -7923,7 +7917,7 @@
         <v>6.7000000000000002E-4</v>
       </c>
       <c r="L24" s="77">
-        <f>K24*H24</f>
+        <f t="shared" si="1"/>
         <v>8.7100000000000007E-3</v>
       </c>
     </row>
@@ -7944,7 +7938,7 @@
         <v>10</v>
       </c>
       <c r="I25" s="29">
-        <f>G25*H25</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="J25" s="29" cm="1">
@@ -7956,7 +7950,7 @@
         <v>3.5000000000000005E-4</v>
       </c>
       <c r="L25" s="77">
-        <f>K25*H25</f>
+        <f t="shared" si="1"/>
         <v>3.5000000000000005E-3</v>
       </c>
     </row>
@@ -7977,7 +7971,7 @@
         <v>10</v>
       </c>
       <c r="I26" s="29">
-        <f>G26*H26</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="J26" s="29" cm="1">
@@ -7989,7 +7983,7 @@
         <v>1.57E-3</v>
       </c>
       <c r="L26" s="77">
-        <f>K26*H26</f>
+        <f t="shared" si="1"/>
         <v>1.5699999999999999E-2</v>
       </c>
     </row>
@@ -8000,7 +7994,7 @@
       <c r="G27" s="29"/>
       <c r="H27" s="29"/>
       <c r="I27" s="29">
-        <f>G27*H27</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J27" s="29" cm="1">
@@ -8012,7 +8006,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="77">
-        <f>K27*H27</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -8023,7 +8017,7 @@
       <c r="G28" s="29"/>
       <c r="H28" s="29"/>
       <c r="I28" s="29">
-        <f>G28*H28</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J28" s="29" cm="1">
@@ -8035,7 +8029,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="77">
-        <f>K28*H28</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -8046,7 +8040,7 @@
       <c r="G29" s="29"/>
       <c r="H29" s="29"/>
       <c r="I29" s="29">
-        <f>G29*H29</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J29" s="29" cm="1">
@@ -8058,7 +8052,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="77">
-        <f>K29*H29</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -8069,7 +8063,7 @@
       <c r="G30" s="29"/>
       <c r="H30" s="29"/>
       <c r="I30" s="29">
-        <f>G30*H30</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J30" s="29" cm="1">
@@ -8081,7 +8075,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="77">
-        <f>K30*H30</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -8092,7 +8086,7 @@
       <c r="G31" s="29"/>
       <c r="H31" s="29"/>
       <c r="I31" s="29">
-        <f>G31*H31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J31" s="29" cm="1">
@@ -8104,7 +8098,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="77">
-        <f>K31*H31</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -8133,7 +8127,7 @@
         <v>R-402A</v>
       </c>
       <c r="E36" s="29">
-        <f>SUMIF($F$22:$F$31,D36,$L$22:$L$31)</f>
+        <f t="shared" ref="E36:E45" si="2">SUMIF($F$22:$F$31,D36,$L$22:$L$31)</f>
         <v>8.5000000000000006E-4</v>
       </c>
       <c r="H36" s="71"/>
@@ -8147,7 +8141,7 @@
         <v>R-422B</v>
       </c>
       <c r="E37" s="29">
-        <f>SUMIF($F$22:$F$31,D37,$L$22:$L$31)</f>
+        <f t="shared" si="2"/>
         <v>1.7500000000000003E-3</v>
       </c>
       <c r="H37" s="71"/>
@@ -8161,7 +8155,7 @@
         <v>R-400 60/40</v>
       </c>
       <c r="E38" s="29">
-        <f>SUMIF($F$22:$F$31,D38,$L$22:$L$31)</f>
+        <f t="shared" si="2"/>
         <v>1.2210000000000002E-2</v>
       </c>
       <c r="H38" s="71"/>
@@ -8175,49 +8169,49 @@
         <v>R-504</v>
       </c>
       <c r="E39" s="29">
-        <f>SUMIF($F$22:$F$31,D39,$L$22:$L$31)</f>
+        <f t="shared" si="2"/>
         <v>1.5699999999999999E-2</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="29"/>
       <c r="E40" s="29">
-        <f>SUMIF($F$22:$F$31,D40,$L$22:$L$31)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="29"/>
       <c r="E41" s="29">
-        <f>SUMIF($F$22:$F$31,D41,$L$22:$L$31)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="29"/>
       <c r="E42" s="29">
-        <f>SUMIF($F$22:$F$31,D42,$L$22:$L$31)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="29"/>
       <c r="E43" s="29">
-        <f>SUMIF($F$22:$F$31,D43,$L$22:$L$31)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="29"/>
       <c r="E44" s="29">
-        <f>SUMIF($F$22:$F$31,D44,$L$22:$L$31)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="29"/>
       <c r="E45" s="29">
-        <f>SUMIF($F$22:$F$31,D45,$L$22:$L$31)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -8362,11 +8356,11 @@
     </row>
     <row r="63" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="29" t="str">
-        <f>D37</f>
+        <f t="shared" ref="D63:D71" si="3">D37</f>
         <v>R-422B</v>
       </c>
       <c r="E63" s="29">
-        <f t="shared" ref="E63:E71" si="0">E37</f>
+        <f t="shared" ref="E63:E71" si="4">E37</f>
         <v>1.7500000000000003E-3</v>
       </c>
       <c r="F63" s="29" cm="1">
@@ -8380,11 +8374,11 @@
     </row>
     <row r="64" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="29" t="str">
-        <f>D38</f>
+        <f t="shared" si="3"/>
         <v>R-400 60/40</v>
       </c>
       <c r="E64" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>1.2210000000000002E-2</v>
       </c>
       <c r="F64" s="29" cm="1">
@@ -8398,11 +8392,11 @@
     </row>
     <row r="65" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="29" t="str">
-        <f>D39</f>
+        <f t="shared" si="3"/>
         <v>R-504</v>
       </c>
       <c r="E65" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>1.5699999999999999E-2</v>
       </c>
       <c r="F65" s="29" cm="1">
@@ -8416,11 +8410,11 @@
     </row>
     <row r="66" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="29">
-        <f>D40</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E66" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F66" s="29" cm="1">
@@ -8434,11 +8428,11 @@
     </row>
     <row r="67" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="29">
-        <f>D41</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E67" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F67" s="29" cm="1">
@@ -8452,11 +8446,11 @@
     </row>
     <row r="68" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D68" s="29">
-        <f>D42</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E68" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F68" s="29" cm="1">
@@ -8470,11 +8464,11 @@
     </row>
     <row r="69" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="29">
-        <f>D43</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E69" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F69" s="29" cm="1">
@@ -8488,11 +8482,11 @@
     </row>
     <row r="70" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="29">
-        <f>D44</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E70" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F70" s="29" cm="1">
@@ -8506,11 +8500,11 @@
     </row>
     <row r="71" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="29">
-        <f>D45</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E71" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F71" s="29" cm="1">
@@ -8528,14 +8522,14 @@
         <f>HYPERLINK("#A1", "▲ Back to top")</f>
         <v>▲ Back to top</v>
       </c>
-      <c r="D73" s="79" t="s">
+      <c r="D73" s="78" t="s">
         <v>138</v>
       </c>
-      <c r="E73" s="80">
+      <c r="E73" s="79">
         <f>SUM(G62:G71)</f>
         <v>108.05338346960002</v>
       </c>
-      <c r="F73" s="81" t="str">
+      <c r="F73" s="80" t="str">
         <f>E54</f>
         <v>t CO2-e</v>
       </c>
@@ -15001,7 +14995,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C96C07E-3BBC-40AD-9550-B73B24462357}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEB3E54E-9905-434A-883A-4B73532B3F1C}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16405,31 +16399,31 @@
       </c>
       <c r="T97" s="26"/>
     </row>
-    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="30" t="str" cm="1">
-        <f t="array" ref="D98:D101">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
+    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D99" s="30" t="str" cm="1">
+        <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
-      </c>
-    </row>
-    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="30" t="str">
-        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="30" t="str">
-        <v>MAP = mean annual precipitation</v>
+        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="30" t="str">
+        <v>MAP = mean annual precipitation</v>
+      </c>
+    </row>
+    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D102" s="30" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D102" s="30"/>
-    </row>
-    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D103" s="30"/>
+    </row>
     <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="5" t="str" cm="1">
@@ -18993,12 +18987,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19197,24 +19193,25 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAJgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzACAAaQBuAGMAbAB1AGQAaQBuAGcAIABsAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgACAAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA1AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAIAAoAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAKQBcACIALAAgAFwAIgBGAHUAZQBsACAAdQBuAGkAdABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAE8AMgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAEgANABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABOADIATwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAG8AbQBiAGkAbgBlAGQAIABnAGEAcwBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAyACwAIAAwAC4AMAAzACwAIAA1ADEALgA2ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAbQBpAG4AZQAgAHcAYQBzAHQAZQAgAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4AOQAsACAANAAuADYALAAgADAALgAzACwAIAA1ADYALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAoAHIAZQB2AGUAcgB0AGkAbgBnACAAdABvACAAcwB0AGEAbgBkAGEAcgBkACAAYwBvAG4AZABpAHQAaQBvAG4AcwApAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQBuAHAAcgBvAGMAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAA2ADIAOQAsACAAXAAiAG0AMwBcACIALAAgADUANgAuADUALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANgAuADUANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBrAGUAIABvAHYAZQBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAxADgAMQAsACAAXAAiAG0AMwBcACIALAAgADMANwAuADAALAAgADAALgAwADMALAAgADAALgAwADUALAAgADMANwAuADAAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABhAHMAdAAgAGYAdQByAG4AYQBjAGUAIABnAGEAcwBcACIALAAgADAALgAwADAANAAwACwAIABcACIAbQAzAFwAIgAsACAAMgAzADQALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAAyACwAIAAyADMANAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADAANAAsACAAMAAuADAAMwAsACAANgAwAC4AMgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBMAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAGUAbwB1AHMAIABmAG8AcwBzAGkAbAAgAGYAdQBlAGwAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA5ADAALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABhAG4AZABmAGkAbABsACAAYgBpAG8AZwBhAHMAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtAGUAdABoAGEAbgBlACAAbwBuAGwAeQApAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAsACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAwAC4AMAAzADcAMAAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAG0AZQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAAMAAuADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAeQBkAHIAbwBnAGUAbgBcACIALAAgADAALgAwADEAMgAyACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADAALgAwACwAIAAwAC4ANQAsACAAMAAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIAAxACwAIABcACIARwBKAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgACcATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzACcAIABhAG4AZAAgACcAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAJwAgAHcAZQByAGUAIABhAGQAZABlAGQALAAgAGUAYQBjAGgAIAB3AGkAdABoACAAYQBuACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIAAxACAARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAAuACAAVABoAGkAcwAgAGkAcwAgAGYAbwByACAAdQBzAGUAcgBzACAAdwBoAG8AIABoAGEAdgBlACAAZgB1AGUAbAAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGQAYQB0AGEAIABpAG4AIABHAEoAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABtADMALgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGcAYQBzAGUAbwB1AHMAIABmAHUAZQBsAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGcAYQBzAGUAbwB1AHMAIABmAHUAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEkAbgBkAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMALgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADYAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAB0AGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAATgBhAHQAdQByAGEAbAAgAEcAYQBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATQBlAHQAcgBvAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABOAGEAdAB1AHIAYQBsACAARwBhAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABOAG8AbgAgAC0AIABNAGUAdAByAG8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIAAxADMALgAxACwAIAAxADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIAAxADMALgAxACwAIAAxADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAANAAuADAALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgADgALgA4ACwAIAA3AC4AOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAMQAwAC4ANwAsACAAMQAwAC4ANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADQALgAxACwAIAA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgADQALgAwACwAIAA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAANAAuADEALAAgADQALgAwAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAATgBTAFcAIABhAG4AZAAgAEEAQwBUACAAcwBwAGwAaQB0ACAAaQBuAHQAbwAgAHMAZQBwAGEAcgBhAHQAZQAgAHIAbwB3AHMALgAgACcAQwAnACAAVgBhAGwAdQBlAHMAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAGEAbgBkACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAdABoAG8AcwBlACAAZgBvAHIAIABWAGkAYwB0AG8AcgBpAGEAIABhAG4AZAAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AIAAoAFMAZQBlACAAYQBwAHAAZQBuAGQAaQBjAGUAcwApAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEEAcwAgAFMAYwBvAHAAZQAgADMAIABmAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAYQB0ACAAdABoAGUAIABwAG8AaQBuAHQAIAB3AGgAZQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABpAHMAIABkAGUAbABpAHYAZQByAGUAZAAgAHQAbwAgAGUAbgBkACAAdQBzAGUAcgBzACwAIABpAHQAIABpAHMAIABuAGUAYwBlAHMAcwBhAHIAeQAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQB0ACAAZQBhAGMAaAAgAG8AZgAgAHQAaABlACAAbABvAGEAZAAgAGMAZQBuAHQAcgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBHAGEAcwAgAHIAZQBhAGMAaABlAHMAIABlAG4AZAAgAHUAcwBlAHIAcwAgAGUAaQB0AGgAZQByACAAZgByAG8AbQAgAHQAaABlACAAbQBlAHQAcgBvACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABuAGUAdAB3AG8AcgBrAHMAIABvAHIAIABkAGkAcgBlAGMAdAAgAGYAcgBvAG0AIAB0AGgAZQAgAGgAaQBnAGgAIAAtACAAcAByAGUAcwBzAHUAcgBlACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABwAGkAcABlAGwAaQBuAGUAcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAEgAbwB1AHMAZQBoAG8AbABkAHMAIABhAG4AZAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB1AHMAZQByAHMAIAB0AGUAbgBkACAAdABvACAAYgBlACAAcwBlAHIAdgBlAGQAIABiAHkAIAB0AGgAZQAgAGYAbwByAG0AZQByACwAIABhAG4AZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAGcAZQBuAGUAcgBhAHQAbwByAHMAIABhAG4AZAAgAGwAYQByAGcAZQAgAGkAbgBkAHUAcwB0AHIAaQBhAGwAIABwAGwAYQBuAHQAcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGwAYQB0AHQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBNAGUAdAByAG8AIABpAHMAIABkAGUAZgBpAG4AZQBkACAAYQBzACAAbABvAGMAYQB0AGUAZAAgAG8AbgAgAG8AcgAgAGUAYQBzAHQAIABvAGYAIAB0AGgAZQAgAGQAaQB2AGkAZABpAG4AZwAgAHIAYQBuAGcAZQAgAGkAbgAgAE4AUwBXACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAEMAYQBuAGIAZQByAHIAYQAgAGEAbgBkACAAUQB1AGUAYQBuAGIAZQB5AGEAbgAsACAATQBlAGwAYgBvAHUAcgBuAGUALAAgAEIAcgBpAHMAYgBhAG4AZQAsACAAQQBkAGUAbABhAGkAZABlACAAbwByACAAUABlAHIAdABoAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIATwB0AGgAZQByAHcAaQBzAGUALAAgAHQAaABlACAAbgBvAG4AIAAtACAAbQBlAHQAcgBvACAAZgBhAGMAdABvAHIAIABzAGgAbwB1AGwAZAAgAGIAZQAgAHUAcwBlAGQALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEYAYQBjAHQAbwByAHMAIABhAHIAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAGEAbABsACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAHcAaABpAGMAaAAgAG0AYQB5ACAAaQBuAGMAbAB1AGQAZQAgAGMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIAVABhAGIAbABlACAANgAgAGkAcwAgAG4AbwB0ACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHQAbwAgAGUAdABoAGEAbgBlAC4AIABTAGUAZQAgAFQAYQBiAGwAZQAgADcAIABJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEMAIAA9ACAAQwBvAG4AZgBpAGQAZQBuAHQAaQBhAGwALgAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAHQAaABlACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIABhAHIAZQAgAG4AbwB0ACAAYQB2AGEAaQBsAGEAYgBsAGUAIABkAHUAZQAgAHQAbwAgAGMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAGkAdAB5ACAAYwBvAG4AcwB0AHIAYQBpAG4AdABzACAAdABoAGEAdAAgAGEAcgBpAHMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGEAIABsAGkAbQBpAHQAZQBkACAAbgB1AG0AYgBlAHIAIABvAGYAIABOAEcARQBSACAAZABhAHQAYQAgAGkAbgBwAHUAdABzAC4AIABJAHQAIABpAHMAIABzAHUAZwBnAGUAcwB0AGUAZAAgAHQAaABhAHQAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAHQAaABlACAAdQBzAGUAIABvAGYAIAB0AGgAZQAgAFYAaQBjAHQAbwByAGkAYQBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGkAcwAgAGEAcABwAHIAbwBwAHIAaQBhAHQAZQAsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAHcAaABpAGwAZQAgAGYAbwByACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZABvACAAbgBvAHQAIABpAG4AYwBsAHUAZABlACAAZgB1AGcAaQB0AGkAdgBlACAAZQBtAGkAcwBzAGkAbwBuACAAbABlAGEAawBhAGcAZQAgAGYAcgBvAG0AIABsAG8AdwAgAHAAcgBlAHMAcwB1AHIAZQAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlACAAbgBlAHQAdwBvAHIAawBzACAAdwBoAGkAbABlACAAdABoAG8AcwBlACAAZgByAG8AbQAgAGgAaQBnAGgAIABwAHIAZQBzAHMAdQByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZwBhAHMAIABuAGUAdAB3AG8AcgBrAHMAIABhAHIAZQAgAGMAbwBuAHMAaQBkAGUAcgBlAGQAIABuAGUAZwBsAGkAZwBpAGIAbABlAC4AXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAYwBlAHIAdABhAGkAbgAgAHAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMALgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA4AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADUALAAgADgALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsAHMAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsACAAdQBzAGUAZAAgAGEAcwAgAGYAdQBlAGwAKQAsACAAZQAuAGcALgAgAGwAdQBiAHIAaQBjAGEAbgB0AHMAXAAiACwAIAAzADgALgA4ACwAIABcACIAawBsAFwAIgAsACAAMQAzAC4AOQAsACAAMAAuADAALAAgADAALgAwACwAIAAxADMALgA5ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABnAHIAZQBhAHMAZQBzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADMALgA1ACwAIAAwAC4AMAAsACAAMAAuADAALAAgADMALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAHUAZABlACAAbwBpAGwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAcgB1AGQAZQAgAG8AaQBsACAAYwBvAG4AZABlAG4AcwBhAHQAZQBzAFwAIgAsACAANAA1AC4AMwAsACAAXAAiAHQAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgA5AC4AOAA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADYALgA1ACwAIABcACIAdABcACIALAAgADYAMQAuADAALAAgADAALgAwADgALAAgADAALgAyACwAIAA2ADEALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB1AHQAbwBtAG8AdABpAHYAZQAgAGcAYQBzAG8AbABpAG4AZQAgAC8AIABwAGUAdAByAG8AbAAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA4ADAALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIABnAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADMALgAxACwAIABcACIAawBMAFwAIgAsACAANgA3ACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYANwAuADQAMAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADcALgA1ACwAIABcACIAawBMAFwAIgAsACAANgA4AC4AOQAsACAAMAAuADAAMQAsACAAMAAuADIALAAgADYAOQAuADEAMQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgAgAHQAdQByAGIAaQBuAGUAIABmAHUAZQBsACAALwAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdABpAG4AZwAgAG8AaQBsAFwAIgAsACAAMwA3AC4AMwAsACAAXAAiAGsATABcACIALAAgADYAOQAuADUALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA3ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAxACwAIAAwAC4AMgAsACAANwAwAC4AMgAwACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAwADQALAAgADAALgAyACwAIAA3ADMALgA4ADQALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAGEAcgBvAG0AYQB0AGkAYwAgAGgAeQBkAHIAbwBjAGEAcgBiAG8AbgBzAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADcALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA5ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbAB2AGUAbgB0AHMAOgAgAG0AaQBuAGUAcgBhAGwAIAB0AHUAcgBwAGUAbgB0AGkAbgBlACAAbwByACAAdwBoAGkAdABlACAAcwBwAGkAcgBpAHQAcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABwAGUAdAByAG8AbABlAHUAbQAgAGcAYQBzACAAKABMAFAARwApAFwAIgAsACAAMgA1AC4ANwAsACAAXAAiAGsATABcACIALAAgADYAMAAuADIALAAgADAALgAyACwAIAAwAC4AMgAsACAANgAwAC4ANgAwACwAIAAyADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHAAaAB0AGgAYQBcACIALAAgADMAMQAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAA2ADkALgA4ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAZgBpAG4AZQByAHkAIABnAGEAcwAgAGEAbgBkACAAbABpAHEAdQBpAGQAcwBcACIALAAgADQAMgAuADkALAAgAFwAIgB0AFwAIgAsACAANQA0AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAANQA0AC4ANwA2ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAYwBvAGsAZQBcACIALAAgADMANAAuADIALAAgAFwAIgB0AFwAIgAsACAAOQAyAC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADkAMgAuADgAOAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMgAsACAAMAAuADEALAAgADYAOQAuADkAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA0AC4ANgAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAHQAaABhAG4AbwBsACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGEAIABmAHUAZQBsACAAaQBuACAAYQBuACAAaQBuAHQAZQByAG4AYQBsACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGUAbgBnAGkAbgBlAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQAgAGEAbgBkACAAYgBlAGwAbwB3AFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADAALgAyADIALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMwAwACwAIABcACIATgBFAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAJwBOAEUAJwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAIABpAG4AIABkAGkAZgBmAGUAcgBlAG4AdAAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADkAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADYALAAgADEAMAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAXAAiACwAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBsAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYANwAuADYAMgAsACAAMQA3AC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAANwAwAC4ANAAxACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAHAAZQB0AHIAbwBsAGUAdQBtACAAZwBhAHMAIAAoAEwAUABHACkAXAAiACwAIAAyADYALgAyACwAIABcACIAawBsAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADUALAAgADAALgAzACwAIAA2ADEALgAwADAALAAgADIAMAAuADIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAGwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4ANQAsACAANwA0AC4AMQA4ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBFAHQAaABhAG4AbwBsAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADIALAAgADAALgA0ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQgBpAG8AZABpAGUAcwBlAGwAXAAiACwAIAAzADQALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgA4ACwAIAAxAC4ANwAsACAAMgAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAAMAAuADUAMQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAE8AdABoAGUAcgAgAGIAaQBvAGYAdQBlAGwAcwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAZwBoAHQAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADcALgAzACwAIAAwAC4AMwAsACAANQA5AC4AMAAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBDAG8AbQBwAHIAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAyAC4AOAAsACAAMAAuADMALAAgADUANAAuADUALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsAbABcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADAANwAsACAAMAAuADQALAAgADcAMAAuADMANwAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADEALAAgADAALgA0ACwAIAA3ADAALgA0ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANAAsACAANwAwAC4ANQAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADcALAAgADAALgA0ACwAIAAwAC4ANAA3ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4ANAAsACAAMAAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADQALAAgADAALgA2ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdABcACIALAAgADMAMwAuADEALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgAwACwAIAAwAC4AMAA2ACwAIAAwAC4ANgAsACAANgA3AC4ANgA2ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwA2AC4AOAAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADYALAAgADAALgAwADEALAAgADAALgA2ACwAIAA3ADAALgAyADEALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA2ACwAIAAwAC4ANgAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADEAMAAuADEALAAgADAALgAzACwAIABcACIAXAAiACwAIAAxADcALgAyACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIABcACIAXAAiACwAIAAxADcALgAzACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEAOAAuADAALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgACcATgBFACcAIAB2AGEAbAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAGEAcwAgAHoAZQByAG8AIABmAG8AcgAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABPAGYAZgAtAHIAYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAE8AZgBmAC0AcgBvAGEAZAAgAGUAcQB1AGkAcABtAGUAbgB0ACAAYQBuAGQAIAB2AGUAcwBzAGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADEAKQAgAGEAbgBkACAAaQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGkAbgAgAG8AZgBmAC0AcgBvAGEAZAAgAGUAcQB1AGkAcABtAGUAbgB0ACAAYQBuAGQAIAB2AGUAcwBzAGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA3ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBwAG8AcgB0ACAAdAB5AHAAZQAgAHQAXAAiACwAIABcACIARgB1AGUAbAAgAHQAeQBwAGUAIABxAFwAIgAsACAAXAAiAEUAQwBUAHIAYQBuAHMALABxACAAKABHAEoALwBrAEwAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAQwBPADIAIABFAEYAVAByAGEAbgAsADEALAB0AHEAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEMASAA0ACAARQBGAFQAcgBhAG4ALAAxACwAdABnAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABOADIATwAgAEUARgBUAHIAYQBuACwAMQAsAHQAZwBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBGAFQAcgBhAG4AcwAsADMALABxACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABcACIALAAgAFwAIgBQAGUAdAByAG8AbABcACIALAAgADMANAAuADIALAAgADYANwAuADQALAAgADEAMAAuADEALAAgADAALgAzACwAIAAxADcALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIARABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIAA2ADkALgA5ACwAIAAwAC4AMgAsACAAMAAuADUALAAgADEANwAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABcACIALAAgAFwAIgBGAHUAZQBsACAATwBpAGwAXAAiACwAIAAzADkALgA3ACwAIAA3ADMALgA2ACwAIAAwAC4AMgAsACAAMAAuADUALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGYAZgAtAHIAbwBhAGQAIABBAGcAcgBpAGMAdQBsAHQAdQByAGUAIABhAG4AZAAgAGYAbwByAGUAcwB0AHIAeQAgAGUAcQB1AGkAcABtAGUAbgB0AFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAANgA5AC4AOQAsACAAMAAuADMALAAgADAALgA1ACwAIAAxADcALgAzAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAEYAdQBlAGwAXwBHAGUAdABUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAFMAdAByAGkAbgBnAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsAFwAbgAgACAAIAAgAEwARQBGAFQAKABDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAIABcACIALABDAGUAbABsACkAIAAtADEAKQBcAG4AKQA7AFwAbgBcAG4ARgB1AGUAbABfAEcAZQB0AFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABTAHQAcgBpAG4AZwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALABcAG4AIAAgACAAIABSAEkARwBIAFQAKABDAGUAbABsACwAIABMAEUATgAoAEMAZQBsAGwAKQAgAC0AIABGAEkATgBEACgAXAAiACwAIABcACIALAAgAEMAZQBsAGwAKQAgAC0AIAAxACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAFwAbgA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALAAgAEYAdQBlAGwAVQBzAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlACwAIABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFQAeQBwAGUALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAUwBVAE0AKABcAG4AIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAEYAdQBlAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACAAPQAgAEYAdQBlAGwAVAB5AHAAZQApACAAKgAgAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFUAcwBlACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgADAAXABuACAAIAApAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AOAA6ACAARgB1AGUAbAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgALgAxACAARgB1AGUAbAAgAFUAcwBlACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAAZgB1AGUAbABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRACwAIABFAEMALAAgAEUARgAsAFwAbgAgACAAIAAgACgAUQAgACoAIABFAEMAIAAqACAARQBGACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBRACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAARwBKAC8AawBMAFwAbgBFAEYAIAA6ACAAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFQAcgBhAG4AcwB0AHEALAAgAEUAQwBfAFQAcgBhAG4AcwBxACwAIABFAEYAXwBUAHIAYQBuAHMAMQB0AHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMwAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB0ACAAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBxAFwAXABsAGUAZgB0ACgAUQBfAHsAVAByAGEAbgBzACwAdABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAVAByAGEAbgBzACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFQAcgBhAG4AcwAsADEALAB0AHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFQAcgBhAG4AcwB0AHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIABjAG8AbQBiAHUAcwB0AGUAZAAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIALAAgAFwAIgBWAGEAcgBpAGUAcwAgAGIAYQBzAGUAZAAgAG8AbgAgAGYAdQBlAGwAIAB0AHkAcABlADoAIABrAEwALAAgAG0AMwAsACAARwBKAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AVAByAGEAbgBzAHEAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AVAByAGEAbgBzADEAdABxAGcAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBcACIALAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAHUAcwBlAGQAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABrAEwAXABuAEUAQwAgADoAIABFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAIAA6ACAAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AUwBDAHEALAAgAEUAQwBfAFMAQwBxACwAIABFAEYAXwBTAEMAMQBxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA4AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADIAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcwBvAHUAcgBjAGUAcwAgAC0AIABDAGEAbABjAHUAbABhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFMAQwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUwBDACwAMQAsAHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AUwBDAHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFMAQwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUwBDADEAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBDAFwAIgAsACAAXAAiAFMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADIAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIABnAGUAbgBlAHIAaQBjACAAZgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIAB3AGgAZQByAGUAIAB0AGgAZQAgAHUAcwBhAGcAZQAgAGkAcwAgAG4AbwB0ACAAawBuAG8AdwBuAFwAbgBRACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAdQBzAGUAZAAgAGYAbwByACAAZwBlAG4AZQByAGkAYwAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzACAAOgAgAGsATABcAG4ARQBDACAAOgAgAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABnAGUAbgBlAHIAaQBjACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAA6ACAARwBKAC8AawBMAFwAbgBFAEYAIAA6ACAAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABnAGUAbgBlAHIAaQBjACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwAgADoAIABrAGcAIABDAE8AMgBlACAALwAgAEcASgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8ARwBDAHEALAAgAEUAQwBfAEcAQwBxACwAIABFAEYAXwBHAEMAMQBxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAEcAQwBxACwAIABFAEMAXwBHAEMAcQAsACAARQBGAF8ARwBDADEAcQBnACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAGcAZQBuAGUAcgBpAGMAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVQBzAGUAcwAgAFYARQBFAFIARwAgADIAMAAyADYAOgAgADgALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApACwAIAA4AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQAgAGEAbgBkACAAZQB2AGUAcgBhAGcAZQBzACAAdABoAGUAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGEAbgBkACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGYAdQBlAGwAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADIAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZwBlAG4AZQByAGkAYwAgAGUAbgBlAHIAZwB5ACAAcwBvAHUAcgBjAGUAcwAgAC0AIABDAGEAbABjAHUAbABhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABnAGUAbgBlAHIAaQBjACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzACAAYQBuAGQAIAAyAC4AMwAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB0ACAAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBxAFwAXABsAGUAZgB0ACgAUQBfAHsARwBDACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEMAXwB7AEcAQwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBHAEMALAAxACwAcQBnAH0AXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8ARwBDAHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABnAGUAbgBlAHIAaQBjACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAEcAQwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABnAGUAbgBlAHIAaQBjACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ARwBDADEAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZwBlAG4AZQByAGkAYwAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBDAFwAIgAsACAAXAAiAEcAZQBuAGUAcgBpAGMAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAVABoAGkAcwAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAgAHUAcwBlAHMAIABhAHYAZQByAGEAZwBlAHMAIABvAGYAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGEAbgBkACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGYAdQBlAGwAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAdwBoAGUAcgBlACAAdABoAGUAIAB1AHMAYQBnAGUAIABpAHMAIABuAG8AdAAgAGsAbgBvAHcAbgAuAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADkAOgAgAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADkALgAxACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXABuAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXABuAEcAVwBQAFIAIAA6ACAARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSACAAOgAgAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAGMAaABhAHIAZwBlAF8AUgBhACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAGMAbwBuAHQAYQBpAG4AZQBkACAAaQBuACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAOgAgAGsAZwBcAG4AbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAgADoAIABQAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAHQAbwB0AGEAbAAgAGMAaABhAHIAZwBlACAAbABlAGEAawBlAGQAIABmAHIAbwBtACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAZQBhAGMAaAAgAHkAZQBhAHIAIAA6ACAAUABlAHIAYwBlAG4AdABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYwBoAGEAcgBnAGUAXwBSAGEALAAgAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALABcAG4AIAAgACAAIAAoAGMAaABhAHIAZwBlAF8AUgBhACAAKgAgACgAbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAvADEAMAAwACkAKQAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AUgAsACAARwBXAFAAXwBSACwAXABuACAAIAAgACAAKAAoAEUAXwBSACAAKgAgADEAMABeADMAKQAgACoAIABHAFcAUABfAFIAKQAgACoAIAAxADAAXgAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABoAGUAIAB0AG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGwAZQBhAGsAaQBuAGcAIABkAHUAcgBpAG4AZwAgAG8AcABlAHIAYQB0AGkAbwBuACAAKABuAG8AdAAgAGQAdQByAGkAbgBnACAAaQBuAHMAdABhAGwAbABhAHQAaQBvAG4AIABvAHIAIABkAGkAcwBwAG8AcwBhAGwAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGwAZQBhAGsAYQBnAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAFIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAZwBhAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAzAC4AMQAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABpAG4AZAB1AHMAdAByAGkAYQBsACAAcAByAG8AYwBlAHMAcwBlAHMAIABlAG0AaQBzAHMAaQBvAG4AcwAgAC0AIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGEAZwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGMAaABhAHIAZwBlAF8AUgBhACAAKgAgACgAbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAvADEAMAAwACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBSACAAPQAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYQAgAFwAXABsAGUAZgB0ACgAIABjAGgAYQByAGcAZQBfAHsAUgBhAH0AIABcAFwAdABpAG0AZQBzACAAXABcAGYAcgBhAGMAewBsAGUAYQBrAGEAZwBlAFwAXAAsAHIAYQB0AGUAXwBhAH0AewAxADAAMAB9ACAAXABcAHIAaQBnAGgAdAApACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMATwAyAGUAIAA9ACAAXABcAGwAZQBmAHQAKABFAF8AUgAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7ADMAfQAgAFwAXAByAGkAZwBoAHQAKQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAFIAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAaABhAHIAZwBlAF8AUgBhAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAGMAbwBuAHQAYQBpAG4AZQBkACAAaQBuACAAYQBwAHAAbABpAGEAbgBjAGUAIABhAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEAXAAiACwAIABcACIAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByAFwAIgAsACAAXAAiAFAAZQByAGMAZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBhAFwAIgAsACAAXAAiAEEAcABwAGwAaQBhAG4AYwBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXAAiACwAIABcACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAF8AUgBcACIALAAgAFwAIgBUAG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAXAAiACwAIABcACIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGcAYQBzAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAOQAuADEALgAxACAAKAAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAF8AUgBcACIALAAgAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAXAAiACwAIABcACIARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABlAHEAdQBhAHQAaQBvAG4AIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAHQAbwAgAEMATwAyAC0AZQAgAHUAcwBpAG4AZwAgAHQAaABlACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACcAcwAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAKABHAFcAUAApAC4AXAAiACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQQBwAHAAZQBuAGQAaQB4ACAAMgAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsAHMAOgAgAFQAYQBiAGwAZQAgADIAMwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAEEAcABwAGUAbgBkAGkAeAAgADIAIAAtACAAVABhAGIAbABlACAAMgAzAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzADkALAAgADUALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBoAGUAbQBpAGMAYQBsACAAZgBvAHIAbQB1AGwAYQBcACIALAAgAFwAIgBHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgACgAQQBSADUAKQBcACIALAAgAFwAIgBHAGEAcwAgAC0AIABGAEMAIABuAGEAbQBlAFwAIgAsACAAXAAiAEEAZABpAHQAaQBvAG4AYQBsACAAZABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQBcACIALAAgAFwAIgBDAE8AMgBcACIALAAgADEALAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ACwAIABcACIAQwBIADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQBcACIALAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ACwAIABcACIATgAyAE8AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGwAcABoAHUAcgAgAGgAZQB4AGEAZgBsAHUAbwByAGkAZABlAFwAIgAsACAAXAAiAFMARgA2AFwAIgAsACAAMgAzADUAMAAwACwAIABcACIAUwBGADYAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADMAIAAoAFIALQAyADMAKQBcACIALAAgAFwAIgBDAEgARgAzAFwAIgAsACAAIAAxADIANAAwADAALAAgAFwAIgBIAEYAQwAtADIAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADMAMgAgACgAUgAtADMAMgApAFwAIgAsACAAXAAiAEMASAAyAEYAMgBcACIALAAgADYANwA3ACwAIABcACIASABGAEMALQAzADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQA0ADEAIAAoAFIALQA0ADEAKQBcACIALAAgAFwAIgBDAEgAMwBGAFwAIgAsACAAIAAxADEANgAsACAAXAAiAEgARgBDAC0ANAAxAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0ANAAzAC0AMQAwAG0AZQBlACAAKABSAC0ANAAzADEAMABtAGUAZQApAFwAIgAsACAAXAAiAEMANQBIADIARgAxADAAXAAiACwAIAAxADYANQAwACwAIABcACIASABGAEMALQA0ADMALQAxADAAbQBlAGUAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADIANQAgACgAUgAtADEAMgA1ACkAXAAiACwAIABcACIAQwAyAEgARgA1AFwAIgAsACAAIAAzADEANwAwACwAIABcACIASABGAEMALQAxADIANQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMwA0ACAAKABSAC0AMQAzADQAKQBcACIALAAgAFwAIgBDADIASAAyAEYANAAgACgAQwBIAEYAMgBDAEgARgAyACkAXAAiACwAIAAgADEAMQAyADAALAAgAFwAIgBIAEYAQwAtADEAMwA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAzADQAYQAgACgAUgAtADEAMwA0AGEAKQBcACIALAAgAFwAIgBDADIASAAyAEYANAAgACgAQwBIADIARgBDAEYAMwApAFwAIgAsACAAMQAzADAAMAAsACAAXAAiAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEANAAzACAAKABSAC0AMQA0ADMAKQBcACIALAAgAFwAIgBDADIASAAzAEYAMwAgACgAQwBIAEYAMgBDAEgAMgBGACkAXAAiACwAIAAzADIAOAAsACAAXAAiAEgARgBDAC0AMQA0ADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADQAMwBhACAAKABSAC0AMQA0ADMAYQApAFwAIgAsACAAXAAiAEMAMgBIADMARgAzACAAKABDAEYAMwBDAEgAMwApAFwAIgAsACAANAA4ADAAMAAsACAAXAAiAEgARgBDAC0AMQA0ADMAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEANQAyAGEAIAAoAFIALQAxADUAMgBhACkAXAAiACwAIABcACIAQwAyAEgANABGADIAIAAoAEMASAAzAEMASABGADIAKQBcACIALAAgADEAMwA4ACwAIABcACIASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgAyADcAZQBhACAAKABSAC0AMgAyADcAZQBhACkAXAAiACwAIABcACIAQwAzAEgARgA3AFwAIgAsACAAMwAzADUAMAAsACAAXAAiAEgARgBDAC0AMgAyADcAZQBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgAzADYAZgBhACAAKABSAC0AMgAzADYAZgBhACkAXAAiACwAIABcACIAQwAzAEgAMgBGADYAXAAiACwAIAA4ADAANgAwACwAIABcACIASABGAEMALQAyADMANgBmAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADQANQBjAGEAIAAoAFIALQAyADQANQBjAGEAKQBcACIALAAgAFwAIgBDADMASAAzAEYANQBcACIALAAgADcAMQA2ACwAIABcACIASABGAEMALQAyADQANQBjAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADQANQBmAGEAIAAoAFIALQAyADQANQBmAGEAKQBcACIALAAgAFwAIgBDAEgARgAyAEMASAAyAEMARgAzAFwAIgAsACAAOAA1ADgALAAgAFwAIgBIAEYAQwAtADIANAA1AGYAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADMANgA1AG0AZgBjACAAKABSAC0AMwA2ADUAbQBmAGMAKQBcACIALAAgAFwAIgBDAEgAMwBDAEYAMgBDAEgAMgBDAEYAMwBcACIALAAgADgAMAA0ACwAIABcACIASABGAEMALQAzADYANQBtAGYAYwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMgAyACAAKABSAC0AMgAyACkAXAAiACwAIABcACIAQwBIAEMAbABGADIAXAAiACwAIAAxADcANgAwACwAIABcACIASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQAyADMAIAAoAFIALQAxADIAMwApAFwAIgAsACAAXAAiAEMASABDAGwAMgAyAEMARgAzAFwAIgAsACAANwA5ACwAIABcACIASABDAEYAQwAtADEAMgAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADIANAAgACgAUgAtADEAMgA0ACkAXAAiACwAIABcACIAQwBIAEMAbABGAEMARgAzAFwAIgAsACAANQAyADcALAAgAFwAIgBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEANAAxAGIAIAAoAFIALQAxADQAMQBiACkAXAAiACwAIABcACIAQwBIADMAQwBDAGwAMgBGAFwAIgAsACAANwA4ADIALAAgAFwAIgBIAEMARgBDAC0AMQA0ADEAYgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQA0ADIAYgAgACgAUgAtADEANAAyAGIAKQBcACIALAAgAFwAIgBDAEgAMgBDAEMAbABGADIAXAAiACwAIAAxADkAOAAwACwAIABcACIASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADIAMgA1AGMAYQAgACgAUgAtADIAMgA1AGMAYQApAFwAIgAsACAAXAAiAEMASABDAGwAMgBDAEYAMgBDAEYAMwBcACIALAAgADEAMgA3ACwAIABcACIASABDAEYAQwAtADIAMgA1AGMAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBiACAAKABSAC0AMgAyADUAYwBiACkAXAAiACwAIABcACIAQwBIAEMAbABGAEMARgAyAEMAQwBJAEYAMgBcACIALAAgADUAMgA1ACwAIABcACIASABDAEYAQwAtADIAMgA1AGMAYgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADEANAAgAFAAZQByAGYAbAB1AG8AcgBvAG0AZQB0AGgAYQBuAGUAIAAoAHQAZQB0AHIAYQBmAGwAdQBvAHIAbwBtAGUAdABoAGEAbgBlACkAXAAiACwAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwACwAIABcACIAUABGAEMALQAxADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAxADEANgAgAFAAZQByAGYAbAB1AG8AcgBvAGUAdABoAGEAbgBlACAAKABoAGUAeABhAGYAbAB1AG8AcgBvAGUAdABoAGEAbgBlACkAXAAiACwAIABcACIAQwAyAEYANgBcACIALAAgADEAMQAxADAAMAAsACAAXAAiAFAARgBDAC0AMQAxADYAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAyADEAOAAgAFAAZQByAGYAbAB1AG8AcgBvAHAAcgBvAHAAYQBuAGUAXAAiACwAIABcACIAQwAzAEYAOABcACIALAAgADgAOQAwADAALAAgAFwAIgBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMwAxAC0AMQAwACAAUABlAHIAZgBsAHUAbwByAG8AYgB1AHQAYQBuAGUAXAAiACwAIABcACIAQwA0AEYAMQAwAFwAIgAsACAAOQAyADAAMAAsACAAXAAiAFAARgBDAC0AMwAxAC0AMQAwAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMwAxADgAIABQAGUAcgBmAGwAdQBvAHIAbwBjAHkAYwBsAG8AYgB1AHQAYQBuAGUAXAAiACwAIABcACIAYwAtAEMANABGADgAXAAiACwAIAA5ADUANAAwACwAIABcACIAUABGAEMALQAzADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADQAMQAtADEAMgAgAFAAZQByAGYAbAB1AG8AcgBvAHAAZQBuAHQAYQBuAGUAXAAiACwAIABcACIAQwA1AEYAMQAyAFwAIgAsACAAOAA1ADUAMAAsACAAXAAiAFAARgBDAC0ANAAxAC0AMQAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0ANQAxAC0AMQA0ACAAUABlAHIAZgBsAHUAbwByAG8AaABlAHgAYQBuAGUAXAAiACwAIABcACIAQwA2AEYAMQA0AFwAIgAsACAANwA5ADEAMAAsACAAXAAiAFAARgBDAC0ANQAxAC0AMQA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AOQAxAC0AMQA4ACAAUABlAHIAZgBsAHUAbgBhAGYAZQBuAGUAXAAiACwAIABcACIAQwAxADAARgAxADgAXAAiACwAIAA3ADEAOQAwACwAIABcACIAUABGAEMALQA5ADEALQAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADIAXAAiACwAIABcACIAQwBDAGwAMgBGADIAXAAiACwAIAAxADAAMgAwADAALAAgAFwAIgBDAEYAQwAtADEAMgBcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAzAFwAIgAsACAAXAAiAEMAQwBsAEYAMwBcACIALAAgADEAMwA5ADAAMAAsACAAXAAiAEMARgBDAC0AMQAzAFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADEANABcACIALAAgAFwAIgBDAEMAbABGADIAQwBDAGwARgAyAFwAIgAsACAAOAA1ADkAMAAsACAAXAAiAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMQA1AFwAIgAsACAAXAAiAEMAQwBsAEYAMgBDAEYAMwBcACIALAAgADcANgA3ADAALAAgAFwAIgBDAEYAQwAtADEAMQA1AFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgACcARwBBAFMAIAAtACAARgBDACAAbgBhAG0AZQAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAdAByAHUAbgBjAGEAdABlAGQAIABnAGEAcwAgAG4AYQBtAGUAIAB0AG8AIABhAGwAbABvAHcAIABtAGEAdABjAGgAaQBuAGcAIAB3AGkAdABoACAAbwB0AGgAZQByACAAdABhAGIAbABlAHMALgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAGcAYQBzAGUAcwAgAGYAcgBvAG0AIABJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAC4AIABBAGQAZABlAGQAIAAnAEEAZABkAGkAdABpAG8AbgBhAGwAIABkAGEAdABhACAAcwBvAHUAcgBjAGUAJwAgAGMAbwBsAHUAbQBuAC4AXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAQgBsAGUAbgBkAGUAZAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAbABlAG4AZABlAGQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAcwAgACgAbQBhAG4AeQAgAGMAbwBuAHQAYQBpAG4AaQBuAGcAIABIAEYAQwBTACAAYQBuAGQALwBvAHIAIABQAEYAQwBTACkAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABBAHAAcABlAG4AZABpAHgAIAAyACAALQAgAFQAYQBiAGwAZQAgADIANABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAxACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABlAG4AZABcACIALAAgAFwAIgBDAG8AbgBzAHQAaQB0AHUAZQBuAHQAcwBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwBpAHQAaQBvAG4AIAAoACUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAFIALQA0ADAAMAAgAGMAYQBuACAAaABhAHYAZQAgAHYAYQByAGkAbwB1AHMAIABwAHIAbwBwAG8AcgB0AGkAbwBuAHMAIABvAGYAIABDAEYAQwAtADEAMgAgAGEAbgBkACAAQwBGAEMALQAxADEANAAuACAAVABoAGUAIABlAHgAYQBjAHQAIABjAG8AbQBwAG8AcwBpAHQAaQBvAG4AIABuAGUAZQBkAHMAIAB0AG8AIABiAGUAIABzAHAAZQBjAGkAZgBpAGUAZAAsACAAZQAuAGcALgAsACAAUgAtADQAMAAwACAAKAA2ADAALwA0ADAAKQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAA1ADMALgAwAC8AMQAzAC4AMAAvADMANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgANgAxAC4AMAAvADEAMQAuADAALwAyADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEMAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADMAMwAuADAALwAxADUALgAwAC8ANQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA2ADAALgAwAC8AMgAuADAALwAzADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAyAEIAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADMAOAAuADAALwAyAC4AMAAvADYAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADMAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANQAuADAALwA3ADUALgAwAC8AMgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMwBCAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA1AC4AMAAvADUANgAuADAALwAzADkALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA0AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADQANAAuADAALwA1ADIALgAwAC8ANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADUAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AIABIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQA0ADIAYgAvAFAARgBDAC0AMwAxADgAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANwAuADAALwA1AC4ANQAvADQAMgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADYAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQA1AC4AMAAvADEANAAuADAALwA0ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAwAC4AMAAvADQAMAAuADAALwA0ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEIAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQAwAC4AMAAvADcAMAAuADAALwAyADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEMAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAzAC4AMAAvADIANQAuADAALwA1ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEQAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQA1AC4AMAAvADEANQAuADAALwA3ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEUAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgA1AC4AMAAvADEANQAuADAALwA2ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA4AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA3AC4AMAAvADQANgAuADAALwA0ADcALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgAwAC4AMAAvADIANQAuADAALwAxADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgA1AC4AMAAvADIANQAuADAALwAxADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAwAEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiACgANQAwAC4AMAAvADUAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADAAQgBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANQA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBBAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMQAuADUALwA4ADcALgA1AC8AMQAxAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBCAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMwAuADAALwA5ADQALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADEAQwBcACIALAAgAFwAIgBIAEMALQAxADIANwAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADMALgAwAC8AOQA1AC4ANQAvADEALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAyAEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADcAMAAuADAALwA1AC4AMAAvADIANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADMAQQBcACIALAAgAFwAIgBQAEYAQwAtADIAMQA4AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADkALgAwAC8AOAA4AC4AMAAvADMALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMQAuADAALwAyADgALgA1AC8ANAAuADAALwAxADYALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMAAuADAALwAzADkALgAwAC8AMQAuADUALwA5AC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA4ADIALgAwAC8AMQA4AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAyADUALgAwAC8ANwA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAFwAIgAsACAAXAAiACgANQA5AC4AMAAvADMAOQAuADUALwAxAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABcACIALAAgAFwAIgAoADQANgAuADYALwA1ADAALgAwAC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADgAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAxAC4ANQAvADkANgAuADAALwAyAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAOQBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEUALQBFADEANwAwAFwAIgAsACAAXAAiACgANwA3AC4AMAAvADEAOQAuADAALwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMABBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgAOAA4AC4AMAAvADEAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADEAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgANQA4AC4AMAAvADQAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgANQAuADEALwAxADEALgA1AC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQgBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADUANQAuADAALwA0ADIALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQwBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgAMgAuADAALwAxADUALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA3ADMALgA4AC8AMgA2AC4AMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADIAXAAiACwAIABcACIAKAA3ADUALgAwAC8AMgA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADEANQBcACIALAAgAFwAIgAoADQAOAAuADgALwA1ADEALgAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAzAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AQwBGAEMALQAxADMAXAAiACwAIABcACIAKAA0ADAALgAxAC8ANQA5AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANABcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAKAA0ADgALgAyAC8ANQAxAC4AOAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANQBcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEgAQwBGAEMALQAzADEAXAAiACwAIABcACIAKAA3ADgALgAwAC8AMgAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANgBcACIALAAgAFwAIgBDAEYAQwAtADMAMQAvAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAKAA1ADUALgAxAC8ANAA0AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEANAAzAGEAXAAiACwAIABcACIAKAA1ADAALgAwAC8ANQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOABBAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AUABGAEMALQAxADEANgBcACIALAAgAFwAIgAoADMAOQAuADAALwA2ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA4AEIAXAAiACwAIABcACIASABGAEMALQAyADMALwBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiACgANAA2AC4AMAAvADUANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADkAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADQANAAuADAALwA1ADYALgAwACkAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAYwBoAGEAbgBnAGUAZAAgAEgAQwA2ADAAMABhACAAdABvACAASABDAC0ANgAwADAAYQAgAGYAbwByACAAYgBsAGUAbgBkACAAUgAtADQAMQA0AEIALgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABmAG8AcgAgAGIAbABlAG4AZAAgAFIALQA0ADAANQBBACAALQAgAEMAaABhAG4AZwBlAGQAIABIAEMARgBDADEANAAyAGIAIAB0AG8AIABIAEMARgBDAC0AMQA0ADIAYgAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEwAZQBhAGsAYQBnAGUAIAByAGEAdABlAHMAIABmAG8AcgAgAGMAbwBtAG0AbwBuACAAcgBlAGYAcgBpAGcAZQByAGEAdABpAG8AbgAgAGEAbgBkACAAYQBpAHIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAGMAYQB0AGkAdgBlACAAbABlAGEAawBhAGcAZQAgAHIAYQB0AGUAcwAgAGYAbwByACAAYwBvAG0AbQBvAG4AIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuACAAYQBuAGQAIABhAGkAcgAgAC0AIABjAG8AbgBkAGkAdABpAG8AbgBpAG4AZwAgAGUAcQB1AGkAcABtAGUAbgB0AFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADEAMABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ADEALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAGwAZQBhAGsAYQBnAGUAIAByAGEAdABlACAAKAAlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAcgBlAGYAcgBpAGcAZQByAGEAdABvAHIAcwBcACIALAAgADEALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuAFwAIgAsACAAMQA1AC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcABvAHIAdABhAGIAbABlAFwAIgAsACAAMgAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHMAcABsAGkAdABcACIALAAgADMALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABwAGEAYwBrAGEAZwBlAGQAXAAiACwAIAAyAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAHYAZQBoAGkAYwBsAGUAIABBAC8AQwBcACIALAAgADYALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAdgBlAGgAaQBjAGwAZQAgAEEALwBDAFwAIgAsACAAMQAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBhAGwAYwB1AGwAYQB0AGUAQgBsAGUAbgBkAEcAVwBQAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMQAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMgAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMwAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAANAAsAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAxACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAyACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAzACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAA0ACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0ACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGEAbABjAHUAbABhAHQAZQBCAGwAZQBuAGQARwBXAFAAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwAgAGkAbgBjAGwAdQBkAGkAbgBnACAAbABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIAAgAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADkALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMgAsACAAMAAuADAAMwAsACAANQAxAC4ANgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAGEAbAAgAG0AaQBuAGUAIAB3AGEAcwB0AGUAIABnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADkALAAgADQALgA2ACwAIAAwAC4AMwAsACAANQA2AC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAKAByAGUAdgBlAHIAdABpAG4AZwAgAHQAbwAgAHMAdABhAG4AZABhAHIAZAAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAKQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBwAHIAbwBjAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAANgAyADkALAAgAFwAIgBtADMAXAAiACwAIAA1ADYALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMAAzACwAIAA1ADYALgA1ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AawBlACAAbwB2AGUAbgAgAGcAYQBzAFwAIgAsACAAMAAuADAAMQA4ADEALAAgAFwAIgBtADMAXAAiACwAIAAzADcALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAA1ACwAIAAzADcALgAwADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGwAYQBzAHQAIABmAHUAcgBuAGEAYwBlACAAZwBhAHMAXAAiACwAIAAwAC4AMAAwADQAMAAsACAAXAAiAG0AMwBcACIALAAgADIAMwA0AC4AMAAsACAAMAAuADAAMwAsACAAMAAuADAAMgAsACAAMgAzADQALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMAAsACAAXAAiAG0AMwBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsATABcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBlAG8AdQBzACAAZgBvAHMAcwBpAGwAIABmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAYQBuAGQAZgBpAGwAbAAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIAAoAG0AZQB0AGgAYQBuAGUAIABvAG4AbAB5ACkAXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4ALAAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA3ADAALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBtAGUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAwADMALAAgADAALgAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAHkAZAByAG8AZwBlAG4AXAAiACwAIAAwAC4AMAAxADIAMgAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMAAsACAAMAAuADUALAAgADAALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgADEALAAgAFwAIgBHAEoAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAzACwAIAA2ADAALgAyADcAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABcAHUAMAAwADIANwBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAdQAwADAAMgA3ACAAdwBlAHIAZQAgAGEAZABkAGUAZAAsACAAZQBhAGMAaAAgAHcAaQB0AGgAIABhAG4AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgADEAIABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAC4AIABUAGgAaQBzACAAaQBzACAAZgBvAHIAIAB1AHMAZQByAHMAIAB3AGgAbwAgAGgAYQB2AGUAIABmAHUAZQBsACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAZABhAHQAYQAgAGkAbgAgAEcASgAgAHIAYQB0AGgAZQByACAAdABoAGEAbgAgAG0AMwAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAuAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABOAGEAdAB1AHIAYQBsACAARwBhAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABNAGUAdAByAG8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AbwBuACAALQAgAE0AZQB0AHIAbwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAOAAuADgALAAgADcALgA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAAxADAALgA3ACwAIAAxADAALgA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAANAAuADEALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAANAAuADAALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIAA0AC4AMQAsACAANAAuADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABOAFMAVwAgAGEAbgBkACAAQQBDAFQAIABzAHAAbABpAHQAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAcgBvAHcAcwAuACAAXAB1ADAAMAAyADcAQwBcAHUAMAAwADIANwAgAFYAYQBsAHUAZQBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAcgBlAHAAbABhAGMAZQBkACAAdwBpAHQAaAAgAHQAaABvAHMAZQAgAGYAbwByACAAVgBpAGMAdABvAHIAaQBhACAAYQBuAGQAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAByAGUAcwBwAGUAYwB0AGkAdgBlAGwAeQAuACAAKABTAGUAZQAgAGEAcABwAGUAbgBkAGkAYwBlAHMAKQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADIALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBBAHMAIABTAGMAbwBwAGUAIAAzACAAZgBhAGMAdABvAHIAcwAgAGEAcgBlACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGEAdAAgAHQAaABlACAAcABvAGkAbgB0ACAAdwBoAGUAcgBlACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAaQBzACAAZABlAGwAaQB2AGUAcgBlAGQAIAB0AG8AIABlAG4AZAAgAHUAcwBlAHIAcwAsACAAaQB0ACAAaQBzACAAbgBlAGMAZQBzAHMAYQByAHkAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAdAAgAGUAYQBjAGgAIABvAGYAIAB0AGgAZQAgAGwAbwBhAGQAIABjAGUAbgB0AHIAZQBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIARwBhAHMAIAByAGUAYQBjAGgAZQBzACAAZQBuAGQAIAB1AHMAZQByAHMAIABlAGkAdABoAGUAcgAgAGYAcgBvAG0AIAB0AGgAZQAgAG0AZQB0AHIAbwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAbgBlAHQAdwBvAHIAawBzACAAbwByACAAZABpAHIAZQBjAHQAIABmAHIAbwBtACAAdABoAGUAIABoAGkAZwBoACAALQAgAHAAcgBlAHMAcwB1AHIAZQAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBIAG8AdQBzAGUAaABvAGwAZABzACAAYQBuAGQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdQBzAGUAcgBzACAAdABlAG4AZAAgAHQAbwAgAGIAZQAgAHMAZQByAHYAZQBkACAAYgB5ACAAdABoAGUAIABmAG8AcgBtAGUAcgAsACAAYQBuAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABnAGUAbgBlAHIAYQB0AG8AcgBzACAAYQBuAGQAIABsAGEAcgBnAGUAIABpAG4AZAB1AHMAdAByAGkAYQBsACAAcABsAGEAbgB0AHMAIABmAHIAbwBtACAAdABoAGUAIABsAGEAdAB0AGUAcgAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIATQBlAHQAcgBvACAAaQBzACAAZABlAGYAaQBuAGUAZAAgAGEAcwAgAGwAbwBjAGEAdABlAGQAIABvAG4AIABvAHIAIABlAGEAcwB0ACAAbwBmACAAdABoAGUAIABkAGkAdgBpAGQAaQBuAGcAIAByAGEAbgBnAGUAIABpAG4AIABOAFMAVwAsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABDAGEAbgBiAGUAcgByAGEAIABhAG4AZAAgAFEAdQBlAGEAbgBiAGUAeQBhAG4ALAAgAE0AZQBsAGIAbwB1AHIAbgBlACwAIABCAHIAaQBzAGIAYQBuAGUALAAgAEEAZABlAGwAYQBpAGQAZQAgAG8AcgAgAFAAZQByAHQAaAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAE8AdABoAGUAcgB3AGkAcwBlACwAIAB0AGgAZQAgAG4AbwBuACAALQAgAG0AZQB0AHIAbwAgAGYAYQBjAHQAbwByACAAcwBoAG8AdQBsAGQAIABiAGUAIAB1AHMAZQBkAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBGAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABhAGwAbAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAB3AGgAaQBjAGgAIABtAGEAeQAgAGkAbgBjAGwAdQBkAGUAIABjAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFQAYQBiAGwAZQAgADYAIABpAHMAIABuAG8AdAAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIAB0AG8AIABlAHQAaABhAG4AZQAuACAAUwBlAGUAIABUAGEAYgBsAGUAIAA3ACAASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGUAdABoAGEAbgBlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBDACAAPQAgAEMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAC4AIABTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAVABhAHMAbQBhAG4AaQBhACAAYQBuAGQAIAB0AGgAZQAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAYQByAGUAIABuAG8AdAAgAGEAdgBhAGkAbABhAGIAbABlACAAZAB1AGUAIAB0AG8AIABjAG8AbgBmAGkAZABlAG4AdABpAGEAbABpAHQAeQAgAGMAbwBuAHMAdAByAGEAaQBuAHQAcwAgAHQAaABhAHQAIABhAHIAaQBzAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABhACAAbABpAG0AaQB0AGUAZAAgAG4AdQBtAGIAZQByACAAbwBmACAATgBHAEUAUgAgAGQAYQB0AGEAIABpAG4AcAB1AHQAcwAuACAASQB0ACAAaQBzACAAcwB1AGcAZwBlAHMAdABlAGQAIAB0AGgAYQB0ACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABWAGkAYwB0AG8AcgBpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgB3AGgAaQBsAGUAIABmAG8AcgAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHQAaABlACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAaQBzACAAYQBwAHAAcgBvAHAAcgBpAGEAdABlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGQAbwAgAG4AbwB0ACAAaQBuAGMAbAB1AGQAZQAgAGYAdQBnAGkAdABpAHYAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGwAZQBhAGsAYQBnAGUAIABmAHIAbwBtACAAbABvAHcAIABwAHIAZQBzAHMAdQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABpAG8AbgAgAHAAaQBwAGUAbABpAG4AZQAgAG4AZQB0AHcAbwByAGsAcwAgAHcAaABpAGwAZQAgAHQAaABvAHMAZQAgAGYAcgBvAG0AIABoAGkAZwBoACAAcAByAGUAcwBzAHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAGcAYQBzACAAbgBlAHQAdwBvAHIAawBzACAAYQByAGUAIABjAG8AbgBzAGkAZABlAHIAZQBkACAAbgBlAGcAbABpAGcAaQBiAGwAZQAuAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGEAbgBkACAAaQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAZQByAHQAYQBpAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgA1ACwAIAA4ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABjAG8AbQBiAHUAcwB0AGUAZABcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAEMAbwBuAHQAZQBuAHQAIABGAGEAYwB0AG8AcgAgACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbABzACAAKABvAHQAaABlAHIAIAB0AGgAYQBuACAAcABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbAAgAHUAcwBlAGQAIABhAHMAIABmAHUAZQBsACkALAAgAGUALgBnAC4AIABsAHUAYgByAGkAYwBhAG4AdABzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADEAMwAuADkALAAgADAALgAwACwAIAAwAC4AMAAsACAAMQAzAC4AOQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAZwByAGUAYQBzAGUAcwBcACIALAAgADMAOAAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAzAC4ANQAsACAAMAAuADAALAAgADAALgAwACwAIAAzAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAcgB1AGQAZQAgAG8AaQBsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABjAHIAdQBkAGUAIABvAGkAbAAgAGMAbwBuAGQAZQBuAHMAYQB0AGUAcwBcACIALAAgADQANQAuADMALAAgAFwAIgB0AFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADYAOQAuADgAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABsAGkAcQB1AGkAZABzAFwAIgAsACAANAA2AC4ANQAsACAAXAAiAHQAXAAiACwAIAA2ADEALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgAxAC4AMgA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdQB0AG8AbQBvAHQAaQB2AGUAIABnAGEAcwBvAGwAaQBuAGUAIAAvACAAcABlAHQAcgBvAGwAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADAALgAyACwAIAAwAC4AMgAsACAANgA3AC4AOAAwACwAIAAxADcALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuACAAZwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsATABcACIALAAgADYANwAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA0ADAALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBLAGUAcgBvAHMAZQBuAGUAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA3AC4ANQAsACAAXAAiAGsATABcACIALAAgADYAOAAuADkALAAgADAALgAwADEALAAgADAALgAyACwAIAA2ADkALgAxADEALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIAB0AHUAcgBiAGkAbgBlACAAZgB1AGUAbAAgAC8AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYAOQAuADgAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHQAaQBuAGcAIABvAGkAbABcACIALAAgADMANwAuADMALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4ANwAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADcAMAAuADIAMAAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA0ACwAIAAwAC4AMgAsACAANwAzAC4AOAA0ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABhAHIAbwBtAGEAdABpAGMAIABoAHkAZAByAG8AYwBhAHIAYgBvAG4AcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAdgBlAG4AdABzADoAIABtAGkAbgBlAHIAYQBsACAAdAB1AHIAcABlAG4AdABpAG4AZQAgAG8AcgAgAHcAaABpAHQAZQAgAHMAcABpAHIAaQB0AHMAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADIALAAgADYAOQAuADkAMwAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYAMAAuADYAMAAsACAAMgAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQBwAGgAdABoAGEAXAAiACwAIAAzADEALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABjAG8AawBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAHQAXAAiACwAIAA5ADIALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAOQAyAC4AOAA4ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAZwBhAHMAIABhAG4AZAAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADIALgA5ACwAIABcACIAdABcACIALAAgADUANAAuADcALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANAAuADcANgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGkAbgBlAHIAeQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADgALAAgADAALgAwADIALAAgADAALgAxACwAIAA2ADkALgA5ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAG8AbAAgAGYAbwByACAAdQBzAGUAIABhAHMAIABhACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGkAbgB0AGUAcgBuAGEAbAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABlAG4AZwBpAG4AZQBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBpAG8AZgB1AGUAbABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAIABhAG4AZAAgAGIAZQBsAG8AdwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAwADIALAAgADAALgAyACwAIAAwAC4AMgAyACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADMAMAAsACAAXAAiAE4ARQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAIABpAG4AIABkAGkAZgBmAGUAcgBlAG4AdAAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADkAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADYALAAgADEAMAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAXAAiACwAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBsAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYANwAuADYAMgAsACAAMQA3AC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAANwAwAC4ANAAxACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAHAAZQB0AHIAbwBsAGUAdQBtACAAZwBhAHMAIAAoAEwAUABHACkAXAAiACwAIAAyADYALgAyACwAIABcACIAawBsAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADUALAAgADAALgAzACwAIAA2ADEALgAwADAALAAgADIAMAAuADIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAGwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4ANQAsACAANwA0AC4AMQA4ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBFAHQAaABhAG4AbwBsAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADIALAAgADAALgA0ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQgBpAG8AZABpAGUAcwBlAGwAXAAiACwAIAAzADQALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgA4ACwAIAAxAC4ANwAsACAAMgAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAAMAAuADUAMQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAE8AdABoAGUAcgAgAGIAaQBvAGYAdQBlAGwAcwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAZwBoAHQAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADcALgAzACwAIAAwAC4AMwAsACAANQA5AC4AMAAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBDAG8AbQBwAHIAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAyAC4AOAAsACAAMAAuADMALAAgADUANAAuADUALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsAbABcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADAANwAsACAAMAAuADQALAAgADcAMAAuADMANwAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADEALAAgADAALgA0ACwAIAA3ADAALgA0ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANAAsACAANwAwAC4ANQAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADcALAAgADAALgA0ACwAIAAwAC4ANAA3ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4ANAAsACAAMAAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADQALAAgADAALgA2ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdABcACIALAAgADMAMwAuADEALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgAwACwAIAAwAC4AMAA2ACwAIAAwAC4ANgAsACAANgA3AC4ANgA2ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwA2AC4AOAAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADYALAAgADAALgAwADEALAAgADAALgA2ACwAIAA3ADAALgAyADEALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA2ACwAIAAwAC4ANgAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADEAMAAuADEALAAgADAALgAzACwAIABcACIAXAAiACwAIAAxADcALgAyACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIABcACIAXAAiACwAIAAxADcALgAzACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEAOAAuADAALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAE8AZgBmAC0AcgBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAaQBuACAAbwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQAgAHEAXAAiACwAIABcACIARQBDAFQAcgBhAG4AcwAsAHEAIAAoAEcASgAvAGsATAApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAE8AMgAgAEUARgBUAHIAYQBuACwAMQAsAHQAcQBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAQwBIADQAIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAE4AMgBPACAARQBGAFQAcgBhAG4ALAAxACwAdABnAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAEYAVAByAGEAbgBzACwAMwAsAHEAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAFAAZQB0AHIAbwBsAFwAIgAsACAAMwA0AC4AMgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgADEANwAuADMAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAATABFAEYAVAAoAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQAgAC0AMQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8ARwBlAHQAUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAFMAdAByAGkAbgBnAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFIASQBHAEgAVAAoAEMAZQBsAGwALABMAEUATgAoAEMAZQBsAGwAKQAtAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8AVABvAHQAYQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBcAG4APQAgAEwAQQBNAEIARABBACgAXABuACAAIAAgACAARgB1AGUAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAsACAARgB1AGUAbABVAHMAZQAsACAARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAsACAARgB1AGUAbABUAHkAcABlACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgAFMAVQBNACgAXABuACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAXABuACAAIAAgACAAIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFQAeQBwAGUAKQAgACoAIABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABVAHMAZQBBAHIAcgBhAHkAIAA9ACAARgB1AGUAbABVAHMAZQApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIAAwAFwAbgAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgAOgAgAEYAdQBlAGwAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA4AC4AMQAgAEYAdQBlAGwAIABVAHMAZQAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsACAARQBDACwAIABFAEYALABcAG4AIAAgACAAIAAoAFEAIAAqACAARQBDACAAKgAgAEUARgApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAGMAbwBtAGIAdQBzAHQAZQBkACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAGsATABcAG4ARQBDACAAOgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwAgADoAIABrAGcAIABDAE8AMgBlACAALwAgAEcASgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AVAByAGEAbgBzAHQAcQAsACAARQBDAF8AVAByAGEAbgBzAHEALAAgAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADgALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADMAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFQAcgBhAG4AcwAsAHQAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEMAXwB7AFQAcgBhAG4AcwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBUAHIAYQBuAHMALAAxACwAdABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBUAHIAYQBuAHMAdABxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlACAALwAgAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHEAXAAiACwAIABcACIARgB1AGUAbAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAXAAiACwAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXABuAFEAIAA6ACAAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABHAEoALwBrAEwAXABuAEUARgAgADoAIABTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBTAEMAcQAsACAARQBDAF8AUwBDAHEALAAgAEUARgBfAFMAQwAxAHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgADIALgAyACAARQBzAHQAaQBtAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABlAG4AZQByAGcAeQAgAHMAbwB1AHIAYwBlAHMAIAAtACAAQwBhAGwAYwB1AGwAYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHQAIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEAXABcAGwAZQBmAHQAKABRAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAUwBDACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFMAQwAsADEALABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFMAQwBxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAdQBzAGUAZAAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAFYAYQByAGkAZQBzACAAYgBhAHMAZQBkACAAbwBuACAAZgB1AGUAbAAgAHQAeQBwAGUAOgAgAGsATAAsACAAbQAzACwAIABHAEoAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMAXwBTAEMAcQBcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFMAQwAxAHEAZwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQwBcACIALAAgAFwAIgBTAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAMQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA5ADoAIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA5AC4AMQAgAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgBUAGgAZQAgAHQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBpAG4AZwAgAGQAdQByAGkAbgBnACAAbwBwAGUAcgBhAHQAaQBvAG4AIAAoAG4AbwB0ACAAZAB1AHIAaQBuAGcAIABpAG4AcwB0AGEAbABsAGEAdABpAG8AbgAgAG8AcgAgAGQAaQBzAHAAbwBzAGEAbAApAFwAbgBHAFcAUABSACAAOgAgAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgADoAIABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBjAGgAYQByAGcAZQBfAFIAYQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIABjAG8AbgB0AGEAaQBuAGUAZAAgAGkAbgAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgADoAIABrAGcAXABuAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEAIAA6ACAAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByACAAOgAgAFAAZQByAGMAZQBuAHQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGMAaABhAHIAZwBlAF8AUgBhACwAIABsAGUAYQBrAGEAZwBlAHIAYQB0AGUAXwBhACwAXABuACAAIAAgACAAKABjAGgAYQByAGcAZQBfAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALwAxADAAMAApACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAFIALAAgAEcAVwBQAF8AUgAsAFwAbgAgACAAIAAgACgAKABFAF8AUgAgACoAIAAxADAAXgAzACkAIAAqACAARwBXAFAAXwBSACkAIAAqACAAMQAwAF4ALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGEAZwBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABjAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBSAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGcAYQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADkALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMwAuADEAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAaQBuAGQAdQBzAHQAcgBpAGEAbAAgAHAAcgBvAGMAZQBzAHMAZQBzACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAtACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBhAGcAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBjAGgAYQByAGcAZQBfAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALwAxADAAMAApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AUgAgAD0AIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGEAIABcAFwAbABlAGYAdAAoACAAYwBoAGEAcgBnAGUAXwB7AFIAYQB9ACAAXABcAHQAaQBtAGUAcwAgAFwAXABmAHIAYQBjAHsAbABlAGEAawBhAGcAZQBcAFwALAByAGEAdABlAF8AYQB9AHsAMQAwADAAfQAgAFwAXAByAGkAZwBoAHQAKQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBDAE8AMgBlACAAPQAgAFwAXABsAGUAZgB0ACgARQBfAFIAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AIABcAFwAcgBpAGcAaAB0ACkAIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwBSACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAGgAYQByAGcAZQBfAFIAYQBcACIALAAgAFwAIgBBAG0AbwB1AG4AdAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIABjAG8AbgB0AGEAaQBuAGUAZAAgAGkAbgAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBsAGUAYQBrAGEAZwBlAHIAYQB0AGUAXwBhAFwAIgAsACAAXAAiAFAAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAAdABvAHQAYQBsACAAYwBoAGEAcgBnAGUAIABsAGUAYQBrAGUAZAAgAGYAcgBvAG0AIABhAHAAcABsAGkAYQBuAGMAZQAgAGEAIABlAGEAYwBoACAAeQBlAGEAcgBcACIALAAgAFwAIgBQAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYQBcACIALAAgAFwAIgBBAHAAcABsAGkAYQBuAGMAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAFwAIgAsACAAXAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAFIAXAAiACwAIABcACIAVABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSAFwAIgAsACAAXAAiAHQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABnAGEAcwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADkALgAxAC4AMQAgACgAMQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABfAFIAXAAiACwAIABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSAFwAIgAsACAAXAAiAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAZQBxAHUAYQB0AGkAbwBuACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIAB0AG8AIABDAE8AMgAtAGUAIAB1AHMAaQBuAGcAIAB0AGgAZQAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABcAHUAMAAwADIANwBzACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIAAoAEcAVwBQACkALgBcACIAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAVABhAGIAbABlACAAMgAzACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAQQBwAHAAZQBuAGQAaQB4ACAAMgAgAC0AIABUAGEAYgBsAGUAIAAyADMAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMAOQAsACAANQAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAGgAZQBtAGkAYwBhAGwAIABmAG8AcgBtAHUAbABhAFwAIgAsACAAXAAiAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAKABBAFIANQApAFwAIgAsACAAXAAiAEcAYQBzACAALQAgAEYAQwAgAG4AYQBtAGUAXAAiACwAIABcACIAQQBkAGkAdABpAG8AbgBhAGwAIABkAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlAFwAIgAsACAAXAAiAEMATwAyAFwAIgAsACAAMQAsACAAXAAiAEMATwAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAQwBIADQAXAAiACwAIAAyADgALAAgAFwAIgBDAEgANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlAFwAIgAsACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUALAAgAFwAIgBOADIATwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAbABwAGgAdQByACAAaABlAHgAYQBmAGwAdQBvAHIAaQBkAGUAXAAiACwAIABcACIAUwBGADYAXAAiACwAIAAyADMANQAwADAALAAgAFwAIgBTAEYANgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMwAgACgAUgAtADIAMwApAFwAIgAsACAAXAAiAEMASABGADMAXAAiACwAIAAgADEAMgA0ADAAMAAsACAAXAAiAEgARgBDAC0AMgAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMwAyACAAKABSAC0AMwAyACkAXAAiACwAIABcACIAQwBIADIARgAyAFwAIgAsACAANgA3ADcALAAgAFwAIgBIAEYAQwAtADMAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADQAMQAgACgAUgAtADQAMQApAFwAIgAsACAAXAAiAEMASAAzAEYAXAAiACwAIAAgADEAMQA2ACwAIABcACIASABGAEMALQA0ADEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQA0ADMALQAxADAAbQBlAGUAIAAoAFIALQA0ADMAMQAwAG0AZQBlACkAXAAiACwAIABcACIAQwA1AEgAMgBGADEAMABcACIALAAgADEANgA1ADAALAAgAFwAIgBIAEYAQwAtADQAMwAtADEAMABtAGUAZQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMgA1ACAAKABSAC0AMQAyADUAKQBcACIALAAgAFwAIgBDADIASABGADUAXAAiACwAIAAgADMAMQA3ADAALAAgAFwAIgBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAzADQAIAAoAFIALQAxADMANAApAFwAIgAsACAAXAAiAEMAMgBIADIARgA0ACAAKABDAEgARgAyAEMASABGADIAKQBcACIALAAgACAAMQAxADIAMAAsACAAXAAiAEgARgBDAC0AMQAzADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADMANABhACAAKABSAC0AMQAzADQAYQApAFwAIgAsACAAXAAiAEMAMgBIADIARgA0ACAAKABDAEgAMgBGAEMARgAzACkAXAAiACwAIAAxADMAMAAwACwAIABcACIASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA0ADMAIAAoAFIALQAxADQAMwApAFwAIgAsACAAXAAiAEMAMgBIADMARgAzACAAKABDAEgARgAyAEMASAAyAEYAKQBcACIALAAgADMAMgA4ACwAIABcACIASABGAEMALQAxADQAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEANAAzAGEAIAAoAFIALQAxADQAMwBhACkAXAAiACwAIABcACIAQwAyAEgAMwBGADMAIAAoAEMARgAzAEMASAAzACkAXAAiACwAIAA0ADgAMAAwACwAIABcACIASABGAEMALQAxADQAMwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA1ADIAYQAgACgAUgAtADEANQAyAGEAKQBcACIALAAgAFwAIgBDADIASAA0AEYAMgAgACgAQwBIADMAQwBIAEYAMgApAFwAIgAsACAAMQAzADgALAAgAFwAIgBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADIANwBlAGEAIAAoAFIALQAyADIANwBlAGEAKQBcACIALAAgAFwAIgBDADMASABGADcAXAAiACwAIAAzADMANQAwACwAIABcACIASABGAEMALQAyADIANwBlAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADMANgBmAGEAIAAoAFIALQAyADMANgBmAGEAKQBcACIALAAgAFwAIgBDADMASAAyAEYANgBcACIALAAgADgAMAA2ADAALAAgAFwAIgBIAEYAQwAtADIAMwA2AGYAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIANAA1AGMAYQAgACgAUgAtADIANAA1AGMAYQApAFwAIgAsACAAXAAiAEMAMwBIADMARgA1AFwAIgAsACAANwAxADYALAAgAFwAIgBIAEYAQwAtADIANAA1AGMAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIANAA1AGYAYQAgACgAUgAtADIANAA1AGYAYQApAFwAIgAsACAAXAAiAEMASABGADIAQwBIADIAQwBGADMAXAAiACwAIAA4ADUAOAAsACAAXAAiAEgARgBDAC0AMgA0ADUAZgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMwA2ADUAbQBmAGMAIAAoAFIALQAzADYANQBtAGYAYwApAFwAIgAsACAAXAAiAEMASAAzAEMARgAyAEMASAAyAEMARgAzAFwAIgAsACAAOAAwADQALAAgAFwAIgBIAEYAQwAtADMANgA1AG0AZgBjAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIAIAAoAFIALQAyADIAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAMgBcACIALAAgADEANwA2ADAALAAgAFwAIgBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADIAMwAgACgAUgAtADEAMgAzACkAXAAiACwAIABcACIAQwBIAEMAbAAyADIAQwBGADMAXAAiACwAIAA3ADkALAAgAFwAIgBIAEMARgBDAC0AMQAyADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEAMgA0ACAAKABSAC0AMQAyADQAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAQwBGADMAXAAiACwAIAA1ADIANwAsACAAXAAiAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQA0ADEAYgAgACgAUgAtADEANAAxAGIAKQBcACIALAAgAFwAIgBDAEgAMwBDAEMAbAAyAEYAXAAiACwAIAA3ADgAMgAsACAAXAAiAEgAQwBGAEMALQAxADQAMQBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADQAMgBiACAAKABSAC0AMQA0ADIAYgApAFwAIgAsACAAXAAiAEMASAAyAEMAQwBsAEYAMgBcACIALAAgADEAOQA4ADAALAAgAFwAIgBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBhACAAKABSAC0AMgAyADUAYwBhACkAXAAiACwAIABcACIAQwBIAEMAbAAyAEMARgAyAEMARgAzAFwAIgAsACAAMQAyADcALAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGIAIAAoAFIALQAyADIANQBjAGIAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAQwBGADIAQwBDAEkARgAyAFwAIgAsACAANQAyADUALAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMQA0ACAAUABlAHIAZgBsAHUAbwByAG8AbQBlAHQAaABhAG4AZQAgACgAdABlAHQAcgBhAGYAbAB1AG8AcgBvAG0AZQB0AGgAYQBuAGUAKQBcACIALAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAALAAgAFwAIgBQAEYAQwAtADEANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADEAMQA2ACAAUABlAHIAZgBsAHUAbwByAG8AZQB0AGgAYQBuAGUAIAAoAGgAZQB4AGEAZgBsAHUAbwByAG8AZQB0AGgAYQBuAGUAKQBcACIALAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAxADEAMAAwACwAIABcACIAUABGAEMALQAxADEANgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADIAMQA4ACAAUABlAHIAZgBsAHUAbwByAG8AcAByAG8AcABhAG4AZQBcACIALAAgAFwAIgBDADMARgA4AFwAIgAsACAAOAA5ADAAMAAsACAAXAAiAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAzADEALQAxADAAIABQAGUAcgBmAGwAdQBvAHIAbwBiAHUAdABhAG4AZQBcACIALAAgAFwAIgBDADQARgAxADAAXAAiACwAIAA5ADIAMAAwACwAIABcACIAUABGAEMALQAzADEALQAxADAAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAzADEAOAAgAFAAZQByAGYAbAB1AG8AcgBvAGMAeQBjAGwAbwBiAHUAdABhAG4AZQBcACIALAAgAFwAIgBjAC0AQwA0AEYAOABcACIALAAgADkANQA0ADAALAAgAFwAIgBQAEYAQwAtADMAMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0ANAAxAC0AMQAyACAAUABlAHIAZgBsAHUAbwByAG8AcABlAG4AdABhAG4AZQBcACIALAAgAFwAIgBDADUARgAxADIAXAAiACwAIAA4ADUANQAwACwAIABcACIAUABGAEMALQA0ADEALQAxADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA1ADEALQAxADQAIABQAGUAcgBmAGwAdQBvAHIAbwBoAGUAeABhAG4AZQBcACIALAAgAFwAIgBDADYARgAxADQAXAAiACwAIAA3ADkAMQAwACwAIABcACIAUABGAEMALQA1ADEALQAxADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA5ADEALQAxADgAIABQAGUAcgBmAGwAdQBuAGEAZgBlAG4AZQBcACIALAAgAFwAIgBDADEAMABGADEAOABcACIALAAgADcAMQA5ADAALAAgAFwAIgBQAEYAQwAtADkAMQAtADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMgBcACIALAAgAFwAIgBDAEMAbAAyAEYAMgBcACIALAAgADEAMAAyADAAMAAsACAAXAAiAEMARgBDAC0AMQAyAFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADMAXAAiACwAIABcACIAQwBDAGwARgAzAFwAIgAsACAAMQAzADkAMAAwACwAIABcACIAQwBGAEMALQAxADMAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAEMAQwBsAEYAMgBDAEMAbABGADIAXAAiACwAIAA4ADUAOQAwACwAIABcACIAQwBGAEMALQAxADEANABcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAQwBDAGwARgAyAEMARgAzAFwAIgAsACAANwA2ADcAMAAsACAAXAAiAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcARwBBAFMAIAAtACAARgBDACAAbgBhAG0AZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAHQAcgB1AG4AYwBhAHQAZQBkACAAZwBhAHMAIABuAGEAbQBlACAAdABvACAAYQBsAGwAbwB3ACAAbQBhAHQAYwBoAGkAbgBnACAAdwBpAHQAaAAgAG8AdABoAGUAcgAgAHQAYQBiAGwAZQBzAC4AIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABnAGEAcwBlAHMAIABmAHIAbwBtACAASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQAuACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAQQBkAGQAaQB0AGkAbwBuAGEAbAAgAGQAYQB0AGEAIABzAG8AdQByAGMAZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAC4AXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAQgBsAGUAbgBkAGUAZAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAbABlAG4AZABlAGQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAcwAgACgAbQBhAG4AeQAgAGMAbwBuAHQAYQBpAG4AaQBuAGcAIABIAEYAQwBTACAAYQBuAGQALwBvAHIAIABQAEYAQwBTACkAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABBAHAAcABlAG4AZABpAHgAIAAyACAALQAgAFQAYQBiAGwAZQAgADIANABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAxACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABlAG4AZABcACIALAAgAFwAIgBDAG8AbgBzAHQAaQB0AHUAZQBuAHQAcwBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwBpAHQAaQBvAG4AIAAoACUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAFIALQA0ADAAMAAgAGMAYQBuACAAaABhAHYAZQAgAHYAYQByAGkAbwB1AHMAIABwAHIAbwBwAG8AcgB0AGkAbwBuAHMAIABvAGYAIABDAEYAQwAtADEAMgAgAGEAbgBkACAAQwBGAEMALQAxADEANAAuACAAVABoAGUAIABlAHgAYQBjAHQAIABjAG8AbQBwAG8AcwBpAHQAaQBvAG4AIABuAGUAZQBkAHMAIAB0AG8AIABiAGUAIABzAHAAZQBjAGkAZgBpAGUAZAAsACAAZQAuAGcALgAsACAAUgAtADQAMAAwACAAKAA2ADAALwA0ADAAKQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAA1ADMALgAwAC8AMQAzAC4AMAAvADMANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgANgAxAC4AMAAvADEAMQAuADAALwAyADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEMAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADMAMwAuADAALwAxADUALgAwAC8ANQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA2ADAALgAwAC8AMgAuADAALwAzADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAyAEIAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADMAOAAuADAALwAyAC4AMAAvADYAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADMAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANQAuADAALwA3ADUALgAwAC8AMgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMwBCAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA1AC4AMAAvADUANgAuADAALwAzADkALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA0AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADQANAAuADAALwA1ADIALgAwAC8ANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADUAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AIABIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQA0ADIAYgAvAFAARgBDAC0AMwAxADgAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANwAuADAALwA1AC4ANQAvADQAMgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADYAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQA1AC4AMAAvADEANAAuADAALwA0ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAwAC4AMAAvADQAMAAuADAALwA0ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEIAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQAwAC4AMAAvADcAMAAuADAALwAyADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEMAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAzAC4AMAAvADIANQAuADAALwA1ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEQAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQA1AC4AMAAvADEANQAuADAALwA3ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEUAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgA1AC4AMAAvADEANQAuADAALwA2ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA4AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA3AC4AMAAvADQANgAuADAALwA0ADcALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgAwAC4AMAAvADIANQAuADAALwAxADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgA1AC4AMAAvADIANQAuADAALwAxADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAwAEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiACgANQAwAC4AMAAvADUAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADAAQgBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANQA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBBAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMQAuADUALwA4ADcALgA1AC8AMQAxAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBCAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMwAuADAALwA5ADQALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADEAQwBcACIALAAgAFwAIgBIAEMALQAxADIANwAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADMALgAwAC8AOQA1AC4ANQAvADEALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAyAEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADcAMAAuADAALwA1AC4AMAAvADIANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADMAQQBcACIALAAgAFwAIgBQAEYAQwAtADIAMQA4AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADkALgAwAC8AOAA4AC4AMAAvADMALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMQAuADAALwAyADgALgA1AC8ANAAuADAALwAxADYALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMAAuADAALwAzADkALgAwAC8AMQAuADUALwA5AC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA4ADIALgAwAC8AMQA4AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAyADUALgAwAC8ANwA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAFwAIgAsACAAXAAiACgANQA5AC4AMAAvADMAOQAuADUALwAxAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABcACIALAAgAFwAIgAoADQANgAuADYALwA1ADAALgAwAC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADgAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAxAC4ANQAvADkANgAuADAALwAyAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAOQBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEUALQBFADEANwAwAFwAIgAsACAAXAAiACgANwA3AC4AMAAvADEAOQAuADAALwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMABBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgAOAA4AC4AMAAvADEAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADEAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgANQA4AC4AMAAvADQAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgANQAuADEALwAxADEALgA1AC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQgBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADUANQAuADAALwA0ADIALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQwBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgAMgAuADAALwAxADUALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA3ADMALgA4AC8AMgA2AC4AMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADIAXAAiACwAIABcACIAKAA3ADUALgAwAC8AMgA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADEANQBcACIALAAgAFwAIgAoADQAOAAuADgALwA1ADEALgAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAzAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AQwBGAEMALQAxADMAXAAiACwAIABcACIAKAA0ADAALgAxAC8ANQA5AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANABcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAKAA0ADgALgAyAC8ANQAxAC4AOAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANQBcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEgAQwBGAEMALQAzADEAXAAiACwAIABcACIAKAA3ADgALgAwAC8AMgAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANgBcACIALAAgAFwAIgBDAEYAQwAtADMAMQAvAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAKAA1ADUALgAxAC8ANAA0AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEANAAzAGEAXAAiACwAIABcACIAKAA1ADAALgAwAC8ANQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOABBAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AUABGAEMALQAxADEANgBcACIALAAgAFwAIgAoADMAOQAuADAALwA2ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA4AEIAXAAiACwAIABcACIASABGAEMALQAyADMALwBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiACgANAA2AC4AMAAvADUANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADkAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADQANAAuADAALwA1ADYALgAwACkAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAYwBoAGEAbgBnAGUAZAAgAEgAQwA2ADAAMABhACAAdABvACAASABDAC0ANgAwADAAYQAgAGYAbwByACAAYgBsAGUAbgBkACAAUgAtADQAMQA0AEIALgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABmAG8AcgAgAGIAbABlAG4AZAAgAFIALQA0ADAANQBBACAALQAgAEMAaABhAG4AZwBlAGQAIABIAEMARgBDADEANAAyAGIAIAB0AG8AIABIAEMARgBDAC0AMQA0ADIAYgAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEwAZQBhAGsAYQBnAGUAIAByAGEAdABlAHMAIABmAG8AcgAgAGMAbwBtAG0AbwBuACAAcgBlAGYAcgBpAGcAZQByAGEAdABpAG8AbgAgAGEAbgBkACAAYQBpAHIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAGMAYQB0AGkAdgBlACAAbABlAGEAawBhAGcAZQAgAHIAYQB0AGUAcwAgAGYAbwByACAAYwBvAG0AbQBvAG4AIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuACAAYQBuAGQAIABhAGkAcgAgAC0AIABjAG8AbgBkAGkAdABpAG8AbgBpAG4AZwAgAGUAcQB1AGkAcABtAGUAbgB0AFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADEAMABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ADEALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAGwAZQBhAGsAYQBnAGUAIAByAGEAdABlACAAKAAlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAcgBlAGYAcgBpAGcAZQByAGEAdABvAHIAcwBcACIALAAgADEALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuAFwAIgAsACAAMQA1AC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcABvAHIAdABhAGIAbABlAFwAIgAsACAAMgAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHMAcABsAGkAdABcACIALAAgADMALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABwAGEAYwBrAGEAZwBlAGQAXAAiACwAIAAyAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAHYAZQBoAGkAYwBsAGUAIABBAC8AQwBcACIALAAgADYALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAdgBlAGgAaQBjAGwAZQAgAEEALwBDAFwAIgAsACAAMQAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBhAGwAYwB1AGwAYQB0AGUAQgBsAGUAbgBkAEcAVwBQAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMQAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMgAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMwAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAANAAsAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAxACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAyACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAzACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAA0ACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0ACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGEAbABjAHUAbABhAHQAZQBCAGwAZQBuAGQARwBXAFAAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19239,12 +19236,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/9_Refrigerants_WIP_v02.xlsx
+++ b/Excel/9_Refrigerants_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464D31BE-555F-4C23-87C5-0D88A2EB1C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139887C6-196F-4183-9A8B-C7801FE3CC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="525" yWindow="255" windowWidth="37335" windowHeight="19740" firstSheet="2" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -21,9 +21,6 @@
     <sheet name="Constants - Refrigerants" sheetId="110" r:id="rId6"/>
     <sheet name="Constants - Common" sheetId="119" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -318,6 +315,27 @@
     <definedName name="Step1">#REF!</definedName>
     <definedName name="Step2">#REF!</definedName>
     <definedName name="Step3">#REF!</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend1_Name_Method1">'9.1.1.1-2 Refrigerant use'!$D$36</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend1_Value_Method1">'9.1.1.1-2 Refrigerant use'!$E$36</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend10_Name_Method1">'9.1.1.1-2 Refrigerant use'!$D$45</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend10_Value_Method1">'9.1.1.1-2 Refrigerant use'!$E$45</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend2_Name_Method1">'9.1.1.1-2 Refrigerant use'!$D$37</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend2_Value_Method1">'9.1.1.1-2 Refrigerant use'!$E$37</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend3_Name_Method1">'9.1.1.1-2 Refrigerant use'!$D$38</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend3_Value_Method1">'9.1.1.1-2 Refrigerant use'!$E$38</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend4_Name_Method1">'9.1.1.1-2 Refrigerant use'!$D$39</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend4_Value_Method1">'9.1.1.1-2 Refrigerant use'!$E$39</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend5_Name_Method1">'9.1.1.1-2 Refrigerant use'!$D$40</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend5_Value_Method1">'9.1.1.1-2 Refrigerant use'!$E$40</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend6_Name_Method1">'9.1.1.1-2 Refrigerant use'!$D$41</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend6_Value_Method1">'9.1.1.1-2 Refrigerant use'!$E$41</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend7_Name_Method1">'9.1.1.1-2 Refrigerant use'!$D$42</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend7_Value_Method1">'9.1.1.1-2 Refrigerant use'!$E$42</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend8_Name_Method1">'9.1.1.1-2 Refrigerant use'!$D$43</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend8_Value_Method1">'9.1.1.1-2 Refrigerant use'!$E$43</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend9_Name_Method1">'9.1.1.1-2 Refrigerant use'!$D$44</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend9_Value_Method1">'9.1.1.1-2 Refrigerant use'!$E$44</definedName>
+    <definedName name="VEERG_9_1_1__1_RefrigerantLeakingGWP_Result_Method1">'9.1.1.1-2 Refrigerant use'!$E$73</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1355,7 +1373,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1543,6 +1561,19 @@
       <bottom style="thin">
         <color theme="3" tint="0.749961851863155"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1735,7 +1766,7 @@
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -1939,9 +1970,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="55" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="4" borderId="7" xfId="39" applyFill="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="48" fillId="4" borderId="2" xfId="52" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1953,6 +1981,15 @@
     </xf>
     <xf numFmtId="0" fontId="49" fillId="4" borderId="1" xfId="53" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="17" xfId="15" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="56" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="14">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="67">
@@ -2025,6 +2062,126 @@
     <cellStyle name="Variable type other" xfId="63" xr:uid="{6646F6F7-E4F9-4165-8015-E25083532B5B}"/>
   </cellStyles>
   <dxfs count="60">
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2886,126 +3043,6 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4618,26 +4655,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -4703,8 +4720,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{522F53FC-4417-4684-906D-1EAA429D66BB}" name="Table_Input_Refrigerant" displayName="Table_Input_Refrigerant" ref="D9:H14" totalsRowShown="0" headerRowCellStyle="Input table column header">
-  <autoFilter ref="D9:H14" xr:uid="{522F53FC-4417-4684-906D-1EAA429D66BB}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{522F53FC-4417-4684-906D-1EAA429D66BB}" name="Table_Input_Refrigerant" displayName="Table_Input_Refrigerant" ref="D9:H19" totalsRowShown="0" headerRowCellStyle="Input table column header">
+  <autoFilter ref="D9:H19" xr:uid="{522F53FC-4417-4684-906D-1EAA429D66BB}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4712,7 +4729,7 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{6746A01D-1612-49BB-8917-35F6F366E6B5}" name="Refrigeration unit name"/>
+    <tableColumn id="1" xr3:uid="{6746A01D-1612-49BB-8917-35F6F366E6B5}" name="Refrigeration unit name" dataCellStyle="Input text"/>
     <tableColumn id="2" xr3:uid="{B1D63EF0-427C-44C7-8981-52C505957D8D}" name="Appliance type (select)" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{7D4059A8-3C98-469C-A367-BB4FE7ACBFBE}" name="Refrigerant used (select)" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{B1F7D4BA-0515-4248-ACA9-0BB1E037D020}" name="Unit refrigerant gas capacity (kg)" dataCellStyle="Input number general"/>
@@ -4746,49 +4763,49 @@
     <tableColumn id="1" xr3:uid="{AA8187F8-0042-4C0E-A158-2B1DDD89C55E}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EAA8886F-E011-45A8-B808-0BEFAC3A35DF}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{EAA8886F-E011-45A8-B808-0BEFAC3A35DF}" name="MAT" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{AA7B88F7-095C-4E16-9CF8-A98235D82885}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{AA7B88F7-095C-4E16-9CF8-A98235D82885}" name="MAP" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0ECBB133-8208-4BC5-87AC-C9A17199BA63}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{0ECBB133-8208-4BC5-87AC-C9A17199BA63}" name="Frost days per year" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3D9AC821-75C8-4D27-BCEF-C2056472F642}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{3D9AC821-75C8-4D27-BCEF-C2056472F642}" name="Elevation" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D643E4EB-D004-46BD-9D3C-B84163D0D6FB}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{D643E4EB-D004-46BD-9D3C-B84163D0D6FB}" name="MAP:PET" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{12A07609-F08E-4413-B6D3-C87FDF66E215}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{12A07609-F08E-4413-B6D3-C87FDF66E215}" name="Min temp" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F102AF9F-9FEA-40DD-AF28-041C1461D83E}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{F102AF9F-9FEA-40DD-AF28-041C1461D83E}" name="Max temp" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{90A51AC4-8B22-4441-A14C-E02D0326E5F8}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{90A51AC4-8B22-4441-A14C-E02D0326E5F8}" name="Min rainfall" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{3FD86231-C6F8-4A32-80AD-5D4060FD1B31}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{3FD86231-C6F8-4A32-80AD-5D4060FD1B31}" name="Max rainfall" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{73D202BF-BFCE-42FA-9D0F-2DA13C4481FC}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{73D202BF-BFCE-42FA-9D0F-2DA13C4481FC}" name="Min frost days" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{F3AAFA92-EA40-43BB-8481-31088FE8F2A5}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{F3AAFA92-EA40-43BB-8481-31088FE8F2A5}" name="Max frost days" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EFBF1273-7CCE-435E-9C54-D0FC021C2D12}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{EFBF1273-7CCE-435E-9C54-D0FC021C2D12}" name="Min elevation" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{35C9987E-D507-47A4-9DE5-D9177126FF2D}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{35C9987E-D507-47A4-9DE5-D9177126FF2D}" name="Max elevation" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{F27CE1D5-2216-4EDB-B3ED-8A6CCE6C7142}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{F27CE1D5-2216-4EDB-B3ED-8A6CCE6C7142}" name="Min MAP:PET" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{520A4B37-7DA2-48BF-AF37-03D14FA097BC}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{520A4B37-7DA2-48BF-AF37-03D14FA097BC}" name="Max MAP:PET" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4806,7 +4823,7 @@
     <tableColumn id="1" xr3:uid="{4EF58733-2135-49D9-856E-9C4907356A09}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F7659FA5-BEFD-4223-A8BA-0F0B54D3C77A}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{F7659FA5-BEFD-4223-A8BA-0F0B54D3C77A}" name="Wet or Dry Zone" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4912,7 +4929,7 @@
     <tableColumn id="1" xr3:uid="{75BEBE37-39B4-4E59-A52E-53C1E93F718F}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C0D50F48-A838-46A3-8B4E-BD74578D5EA5}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{C0D50F48-A838-46A3-8B4E-BD74578D5EA5}" name="FracWET" dataDxfId="31">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4960,7 +4977,7 @@
     <tableColumn id="1" xr3:uid="{058EE474-821C-46B8-B9DB-A856FC27B7A9}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{64C441F6-07CD-4748-BEAE-C8625EB5AEF9}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{64C441F6-07CD-4748-BEAE-C8625EB5AEF9}" name="FracWET" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4978,7 +4995,7 @@
     <tableColumn id="1" xr3:uid="{A9D82E06-BBC8-48FF-87E0-4E5D302CD314}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6B8B8187-2CE6-4828-B655-AC0E679BD856}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6B8B8187-2CE6-4828-B655-AC0E679BD856}" name="EFPRP" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5026,7 +5043,7 @@
     <tableColumn id="1" xr3:uid="{DB86F89E-F0C6-4E23-84FA-724586BBF2C0}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E19CC679-0382-4B3E-B2BA-CA84BD9BEC57}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E19CC679-0382-4B3E-B2BA-CA84BD9BEC57}" name="Season" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5058,49 +5075,49 @@
     <tableColumn id="1" xr3:uid="{DD282435-2C2B-4691-B43F-3A454A86ADF0}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9F6E82C4-3071-42FC-93D6-968F926A0031}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{9F6E82C4-3071-42FC-93D6-968F926A0031}" name="MAT (ºC)" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B27891F1-2A40-4958-9F1E-6BEBC12FF7C4}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{B27891F1-2A40-4958-9F1E-6BEBC12FF7C4}" name="Anaerobic lagoon" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5662A798-B4DE-4CC1-A843-7A6191D9632B}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{5662A798-B4DE-4CC1-A843-7A6191D9632B}" name="Digester / covered lagoons" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{605030C8-492D-4496-BF8E-7FA67C7FE1EA}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{605030C8-492D-4496-BF8E-7FA67C7FE1EA}" name="Liquid systems" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{0002A82C-EACF-411E-A58B-682D7665BB39}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{0002A82C-EACF-411E-A58B-682D7665BB39}" name="Daily spread" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{4BF9F484-91EC-450F-8028-73876D34E694}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{4BF9F484-91EC-450F-8028-73876D34E694}" name="Composting (passive windrow)" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{8A5C68A4-F5AA-4764-A03E-2279AB444523}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{8A5C68A4-F5AA-4764-A03E-2279AB444523}" name="Solid storage" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{123BF989-3B2E-4BA3-8E54-20C4BE277CFE}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{123BF989-3B2E-4BA3-8E54-20C4BE277CFE}" name="Pit storage" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8DAAE1D4-960B-4197-A78A-30E617DF6E41}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{8DAAE1D4-960B-4197-A78A-30E617DF6E41}" name="Deep litter" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{34450AE7-D05C-4631-8EE5-4679D80792CD}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{34450AE7-D05C-4631-8EE5-4679D80792CD}" name="Poultry manure with bedding" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{3C9DF90B-C67E-43D8-8207-6500A71BC3F4}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{3C9DF90B-C67E-43D8-8207-6500A71BC3F4}" name="Poultry manure without bedding" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{89E1FE1C-A229-4E74-BA5A-27BCE54D61FC}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{89E1FE1C-A229-4E74-BA5A-27BCE54D61FC}" name="Direct processing" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{12B2DF86-A0C2-49AA-921F-AD97795AEDAB}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{12B2DF86-A0C2-49AA-921F-AD97795AEDAB}" name="Direct application" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{782429A0-44D3-4681-BFA0-84CC3419FDAC}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{782429A0-44D3-4681-BFA0-84CC3419FDAC}" name="Pasture range and paddock" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{FF208E44-6053-4431-AA07-E648AB1553AE}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{FF208E44-6053-4431-AA07-E648AB1553AE}" name="MAT raw" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5118,7 +5135,7 @@
     <tableColumn id="1" xr3:uid="{27068885-8281-4700-BCD0-1F0F37B151C2}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4BCC72ED-670B-4B3C-AECD-20306DA91098}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{4BCC72ED-670B-4B3C-AECD-20306DA91098}" name="EFNi &amp; EFN2Oi" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7103,7 +7120,7 @@
       <c r="A10" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="82" t="s">
         <v>94</v>
       </c>
       <c r="E10" s="27" t="s">
@@ -7124,7 +7141,7 @@
         <f>HYPERLINK("#'9.1.1.1-2 Refrigerant use'!A1", "9.1.1.1-2 Refrigerant use")</f>
         <v>9.1.1.1-2 Refrigerant use</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="82" t="s">
         <v>145</v>
       </c>
       <c r="E11" s="27" t="s">
@@ -7142,7 +7159,7 @@
     </row>
     <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
-      <c r="D12" t="s">
+      <c r="D12" s="82" t="s">
         <v>98</v>
       </c>
       <c r="E12" s="27" t="s">
@@ -7162,7 +7179,7 @@
       <c r="A13" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="82" t="s">
         <v>146</v>
       </c>
       <c r="E13" s="27" t="s">
@@ -7183,7 +7200,7 @@
         <f>HYPERLINK("#'Constants - Refrigerants'!A1", "Constants - Refrigerants")</f>
         <v>Constants - Refrigerants</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="82" t="s">
         <v>147</v>
       </c>
       <c r="E14" s="27" t="s">
@@ -7204,36 +7221,65 @@
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" s="82"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
+    </row>
+    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="82"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="80"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
+    </row>
+    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D17" s="82"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="81"/>
+    </row>
+    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D18" s="82"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="80"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
+    </row>
+    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D19" s="82"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
+    </row>
+    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
     </row>
-    <row r="21" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
     </row>
-    <row r="22" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
     </row>
-    <row r="24" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
     </row>
-    <row r="30" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
     </row>
-    <row r="31" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="32"/>
     </row>
-    <row r="32" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="32"/>
     </row>
     <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7402,62 +7448,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F49">
-    <cfRule type="cellIs" dxfId="47" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F129">
-    <cfRule type="cellIs" dxfId="46" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140:F141">
-    <cfRule type="cellIs" dxfId="45" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F152:F153">
-    <cfRule type="cellIs" dxfId="44" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F164:F165">
-    <cfRule type="cellIs" dxfId="43" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F252:F253">
-    <cfRule type="cellIs" dxfId="42" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F258">
-    <cfRule type="cellIs" dxfId="41" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F262:F263">
-    <cfRule type="cellIs" dxfId="40" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F286:F287">
-    <cfRule type="cellIs" dxfId="39" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F291:F292">
-    <cfRule type="cellIs" dxfId="38" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296:F297">
-    <cfRule type="cellIs" dxfId="37" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45:H47 E212:G212">
-    <cfRule type="cellIs" dxfId="36" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7480,10 +7526,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D46:D47" xr:uid="{23F8C720-A764-46DD-9B01-B7EA3D86E5AB}">
       <formula1>INDIRECT("Table_SourceData_OrganicFertiliserTypes[Organic fertiliser type]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F14" xr:uid="{23277720-0332-4416-A6AF-2DA9CB20A246}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F19" xr:uid="{23277720-0332-4416-A6AF-2DA9CB20A246}">
       <formula1>INDIRECT("Table_RefrigerantBlends_Cleaned[Blend]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10:E14" xr:uid="{101D112D-006B-4A7F-919E-39E781ABCEE3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10:E19" xr:uid="{101D112D-006B-4A7F-919E-39E781ABCEE3}">
       <formula1>INDIRECT("Table_Refrigerants_LeakageRates[Product]")</formula1>
     </dataValidation>
   </dataValidations>
@@ -7818,23 +7864,23 @@
     </row>
     <row r="22" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="29" t="str" cm="1">
-        <f t="array" ref="D22:D26">Table_Input_Refrigerant[Refrigeration unit name]</f>
+        <f t="array" ref="D22:D31">IFERROR(INDEX(Table_Input_Refrigerant[Refrigeration unit name], _xlfn.SEQUENCE(10)),"")</f>
         <v>Cool room</v>
       </c>
       <c r="E22" s="29" t="str" cm="1">
-        <f t="array" ref="E22:E26">Table_Input_Refrigerant[Appliance type (select)]</f>
+        <f t="array" ref="E22:E31">IFERROR(INDEX(Table_Input_Refrigerant[Appliance type (select)], _xlfn.SEQUENCE(10)),"")</f>
         <v>Domestic refrigerators</v>
       </c>
       <c r="F22" s="29" t="str" cm="1">
-        <f t="array" ref="F22:F26">Table_Input_Refrigerant[Refrigerant used (select)]</f>
+        <f t="array" ref="F22:F31">IFERROR(INDEX(Table_Input_Refrigerant[Refrigerant used (select)], _xlfn.SEQUENCE(10)),"")</f>
         <v>R-402A</v>
       </c>
       <c r="G22" s="29" cm="1">
-        <f t="array" ref="G22:G26">Table_Input_Refrigerant[Unit refrigerant gas capacity (kg)]</f>
+        <f t="array" ref="G22:G31">IFERROR(INDEX(Table_Input_Refrigerant[Unit refrigerant gas capacity (kg)], _xlfn.SEQUENCE(10)),0)</f>
         <v>10</v>
       </c>
       <c r="H22" s="29" cm="1">
-        <f t="array" ref="H22:H26">Table_Input_Refrigerant[Number of units in use]</f>
+        <f t="array" ref="H22:H31">IFERROR(INDEX(Table_Input_Refrigerant[Number of units in use], _xlfn.SEQUENCE(10)),0)</f>
         <v>5</v>
       </c>
       <c r="I22" s="29">
@@ -7849,7 +7895,7 @@
         <f t="array" ref="K22">Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking(G22,J22)</f>
         <v>1.7000000000000001E-4</v>
       </c>
-      <c r="L22" s="77">
+      <c r="L22" s="76">
         <f t="shared" ref="L22:L31" si="1">K22*H22</f>
         <v>8.5000000000000006E-4</v>
       </c>
@@ -7883,7 +7929,7 @@
         <f t="array" ref="K23">Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking(G23,J23)</f>
         <v>3.5000000000000005E-4</v>
       </c>
-      <c r="L23" s="77">
+      <c r="L23" s="76">
         <f t="shared" si="1"/>
         <v>1.7500000000000003E-3</v>
       </c>
@@ -7916,7 +7962,7 @@
         <f t="array" ref="K24">Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking(G24,J24)</f>
         <v>6.7000000000000002E-4</v>
       </c>
-      <c r="L24" s="77">
+      <c r="L24" s="76">
         <f t="shared" si="1"/>
         <v>8.7100000000000007E-3</v>
       </c>
@@ -7949,7 +7995,7 @@
         <f t="array" ref="K25">Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking(G25,J25)</f>
         <v>3.5000000000000005E-4</v>
       </c>
-      <c r="L25" s="77">
+      <c r="L25" s="76">
         <f t="shared" si="1"/>
         <v>3.5000000000000005E-3</v>
       </c>
@@ -7982,17 +8028,27 @@
         <f t="array" ref="K26">Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking(G26,J26)</f>
         <v>1.57E-3</v>
       </c>
-      <c r="L26" s="77">
+      <c r="L26" s="76">
         <f t="shared" si="1"/>
         <v>1.5699999999999999E-2</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
+      <c r="D27" s="29">
+        <v>0</v>
+      </c>
+      <c r="E27" s="29">
+        <v>0</v>
+      </c>
+      <c r="F27" s="29">
+        <v>0</v>
+      </c>
+      <c r="G27" s="29">
+        <v>0</v>
+      </c>
+      <c r="H27" s="29">
+        <v>0</v>
+      </c>
       <c r="I27" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8005,17 +8061,27 @@
         <f t="array" ref="K27">Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking(G27,J27)</f>
         <v>0</v>
       </c>
-      <c r="L27" s="77">
+      <c r="L27" s="76">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
+      <c r="D28" s="29">
+        <v>0</v>
+      </c>
+      <c r="E28" s="29">
+        <v>0</v>
+      </c>
+      <c r="F28" s="29">
+        <v>0</v>
+      </c>
+      <c r="G28" s="29">
+        <v>0</v>
+      </c>
+      <c r="H28" s="29">
+        <v>0</v>
+      </c>
       <c r="I28" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8028,17 +8094,27 @@
         <f t="array" ref="K28">Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking(G28,J28)</f>
         <v>0</v>
       </c>
-      <c r="L28" s="77">
+      <c r="L28" s="76">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
+      <c r="D29" s="29">
+        <v>0</v>
+      </c>
+      <c r="E29" s="29">
+        <v>0</v>
+      </c>
+      <c r="F29" s="29">
+        <v>0</v>
+      </c>
+      <c r="G29" s="29">
+        <v>0</v>
+      </c>
+      <c r="H29" s="29">
+        <v>0</v>
+      </c>
       <c r="I29" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8051,17 +8127,27 @@
         <f t="array" ref="K29">Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking(G29,J29)</f>
         <v>0</v>
       </c>
-      <c r="L29" s="77">
+      <c r="L29" s="76">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
+      <c r="D30" s="29">
+        <v>0</v>
+      </c>
+      <c r="E30" s="29">
+        <v>0</v>
+      </c>
+      <c r="F30" s="29">
+        <v>0</v>
+      </c>
+      <c r="G30" s="29">
+        <v>0</v>
+      </c>
+      <c r="H30" s="29">
+        <v>0</v>
+      </c>
       <c r="I30" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8074,17 +8160,27 @@
         <f t="array" ref="K30">Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking(G30,J30)</f>
         <v>0</v>
       </c>
-      <c r="L30" s="77">
+      <c r="L30" s="76">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
+      <c r="D31" s="29">
+        <v>0</v>
+      </c>
+      <c r="E31" s="29">
+        <v>0</v>
+      </c>
+      <c r="F31" s="29">
+        <v>0</v>
+      </c>
+      <c r="G31" s="29">
+        <v>0</v>
+      </c>
+      <c r="H31" s="29">
+        <v>0</v>
+      </c>
       <c r="I31" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8097,7 +8193,7 @@
         <f t="array" ref="K31">Refrigerants_Equations.VEERG_9_1_1__1_RefrigerantLeaking(G31,J31)</f>
         <v>0</v>
       </c>
-      <c r="L31" s="77">
+      <c r="L31" s="76">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8123,7 +8219,7 @@
     </row>
     <row r="36" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="29" t="str" cm="1">
-        <f t="array" ref="D36:D39">_xlfn.UNIQUE(_xlfn._xlws.FILTER(F22:F31, F22:F31&lt;&gt;""))</f>
+        <f t="array" ref="D36:D39">_xlfn.UNIQUE(_xlfn._xlws.FILTER(F22:F31, (F22:F31&lt;&gt;"") * (F22:F31&lt;&gt;0)))</f>
         <v>R-402A</v>
       </c>
       <c r="E36" s="29">
@@ -8132,7 +8228,6 @@
       </c>
       <c r="H36" s="71"/>
       <c r="I36" s="71"/>
-      <c r="J36" s="71"/>
       <c r="K36" s="71"/>
       <c r="L36" s="71"/>
     </row>
@@ -8146,7 +8241,6 @@
       </c>
       <c r="H37" s="71"/>
       <c r="I37" s="71"/>
-      <c r="J37" s="71"/>
       <c r="K37" s="71"/>
       <c r="L37" s="71"/>
     </row>
@@ -8160,7 +8254,6 @@
       </c>
       <c r="H38" s="71"/>
       <c r="I38" s="71"/>
-      <c r="J38" s="71"/>
       <c r="K38" s="71"/>
       <c r="L38" s="71"/>
     </row>
@@ -8172,6 +8265,8 @@
         <f t="shared" si="2"/>
         <v>1.5699999999999999E-2</v>
       </c>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
     </row>
     <row r="40" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="29"/>
@@ -8179,6 +8274,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
     </row>
     <row r="41" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="29"/>
@@ -8186,6 +8283,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
     </row>
     <row r="42" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="29"/>
@@ -8193,6 +8292,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
     </row>
     <row r="43" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="29"/>
@@ -8200,6 +8301,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="H43" s="71"/>
+      <c r="I43" s="71"/>
     </row>
     <row r="44" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="29"/>
@@ -8207,6 +8310,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
     </row>
     <row r="45" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="29"/>
@@ -8214,6 +8319,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
     </row>
     <row r="46" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8522,14 +8629,14 @@
         <f>HYPERLINK("#A1", "▲ Back to top")</f>
         <v>▲ Back to top</v>
       </c>
-      <c r="D73" s="78" t="s">
+      <c r="D73" s="77" t="s">
         <v>138</v>
       </c>
-      <c r="E73" s="79">
+      <c r="E73" s="78">
         <f>SUM(G62:G71)</f>
         <v>108.05338346960002</v>
       </c>
-      <c r="F73" s="80" t="str">
+      <c r="F73" s="79" t="str">
         <f>E54</f>
         <v>t CO2-e</v>
       </c>
@@ -11524,20 +11631,20 @@
       <c r="Q105" s="71"/>
     </row>
     <row r="106" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D106" s="76" t="str">
+      <c r="D106" s="67" t="str">
         <f>"  ℹ️  This table lists the refrigerant blends from the table '"&amp;D49&amp;"' and each constituent gas in separate cells. For each constituent gas, it GWP value is found from the '"&amp;D5&amp;"' table. Then the GWPs for each constituent gas are miltiplied by their blend fraction, and added together to make a GWP for the blend."</f>
         <v xml:space="preserve">  ℹ️  This table lists the refrigerant blends from the table 'Blended refrigerants (many containing HFCS and/or PFCS)' and each constituent gas in separate cells. For each constituent gas, it GWP value is found from the 'Global Warming Potentials' table. Then the GWPs for each constituent gas are miltiplied by their blend fraction, and added together to make a GWP for the blend.</v>
       </c>
-      <c r="E106" s="71"/>
-      <c r="F106" s="71"/>
-      <c r="G106" s="71"/>
-      <c r="H106" s="71"/>
-      <c r="I106" s="71"/>
-      <c r="J106" s="71"/>
-      <c r="K106" s="71"/>
-      <c r="L106" s="71"/>
-      <c r="M106" s="71"/>
-      <c r="N106" s="71"/>
+      <c r="E106" s="69"/>
+      <c r="F106" s="67"/>
+      <c r="G106" s="68"/>
+      <c r="H106" s="68"/>
+      <c r="I106" s="68"/>
+      <c r="J106" s="68"/>
+      <c r="K106" s="68"/>
+      <c r="L106" s="68"/>
+      <c r="M106" s="68"/>
+      <c r="N106" s="69"/>
       <c r="O106" s="71"/>
       <c r="P106" s="71"/>
       <c r="Q106" s="71"/>
@@ -18998,6 +19105,19 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwAgAGkAbgBjAGwAdQBkAGkAbgBnACAAbABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIAAgAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADkALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMgAsACAAMAAuADAAMwAsACAANQAxAC4ANgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAGEAbAAgAG0AaQBuAGUAIAB3AGEAcwB0AGUAIABnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADkALAAgADQALgA2ACwAIAAwAC4AMwAsACAANQA2AC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAKAByAGUAdgBlAHIAdABpAG4AZwAgAHQAbwAgAHMAdABhAG4AZABhAHIAZAAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAKQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBwAHIAbwBjAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAANgAyADkALAAgAFwAIgBtADMAXAAiACwAIAA1ADYALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMAAzACwAIAA1ADYALgA1ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AawBlACAAbwB2AGUAbgAgAGcAYQBzAFwAIgAsACAAMAAuADAAMQA4ADEALAAgAFwAIgBtADMAXAAiACwAIAAzADcALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAA1ACwAIAAzADcALgAwADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGwAYQBzAHQAIABmAHUAcgBuAGEAYwBlACAAZwBhAHMAXAAiACwAIAAwAC4AMAAwADQAMAAsACAAXAAiAG0AMwBcACIALAAgADIAMwA0AC4AMAAsACAAMAAuADAAMwAsACAAMAAuADAAMgAsACAAMgAzADQALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMAAsACAAXAAiAG0AMwBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsATABcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBlAG8AdQBzACAAZgBvAHMAcwBpAGwAIABmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAYQBuAGQAZgBpAGwAbAAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIAAoAG0AZQB0AGgAYQBuAGUAIABvAG4AbAB5ACkAXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4ALAAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA3ADAALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBtAGUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAwADMALAAgADAALgAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAHkAZAByAG8AZwBlAG4AXAAiACwAIAAwAC4AMAAxADIAMgAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMAAsACAAMAAuADUALAAgADAALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgADEALAAgAFwAIgBHAEoAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAzACwAIAA2ADAALgAyADcAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABcAHUAMAAwADIANwBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAdQAwADAAMgA3ACAAdwBlAHIAZQAgAGEAZABkAGUAZAAsACAAZQBhAGMAaAAgAHcAaQB0AGgAIABhAG4AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgADEAIABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAC4AIABUAGgAaQBzACAAaQBzACAAZgBvAHIAIAB1AHMAZQByAHMAIAB3AGgAbwAgAGgAYQB2AGUAIABmAHUAZQBsACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAZABhAHQAYQAgAGkAbgAgAEcASgAgAHIAYQB0AGgAZQByACAAdABoAGEAbgAgAG0AMwAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAuAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABOAGEAdAB1AHIAYQBsACAARwBhAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABNAGUAdAByAG8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AbwBuACAALQAgAE0AZQB0AHIAbwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAOAAuADgALAAgADcALgA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAAxADAALgA3ACwAIAAxADAALgA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAANAAuADEALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAANAAuADAALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIAA0AC4AMQAsACAANAAuADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABOAFMAVwAgAGEAbgBkACAAQQBDAFQAIABzAHAAbABpAHQAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAcgBvAHcAcwAuACAAXAB1ADAAMAAyADcAQwBcAHUAMAAwADIANwAgAFYAYQBsAHUAZQBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAcgBlAHAAbABhAGMAZQBkACAAdwBpAHQAaAAgAHQAaABvAHMAZQAgAGYAbwByACAAVgBpAGMAdABvAHIAaQBhACAAYQBuAGQAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAByAGUAcwBwAGUAYwB0AGkAdgBlAGwAeQAuACAAKABTAGUAZQAgAGEAcABwAGUAbgBkAGkAYwBlAHMAKQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADIALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBBAHMAIABTAGMAbwBwAGUAIAAzACAAZgBhAGMAdABvAHIAcwAgAGEAcgBlACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGEAdAAgAHQAaABlACAAcABvAGkAbgB0ACAAdwBoAGUAcgBlACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAaQBzACAAZABlAGwAaQB2AGUAcgBlAGQAIAB0AG8AIABlAG4AZAAgAHUAcwBlAHIAcwAsACAAaQB0ACAAaQBzACAAbgBlAGMAZQBzAHMAYQByAHkAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAdAAgAGUAYQBjAGgAIABvAGYAIAB0AGgAZQAgAGwAbwBhAGQAIABjAGUAbgB0AHIAZQBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIARwBhAHMAIAByAGUAYQBjAGgAZQBzACAAZQBuAGQAIAB1AHMAZQByAHMAIABlAGkAdABoAGUAcgAgAGYAcgBvAG0AIAB0AGgAZQAgAG0AZQB0AHIAbwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAbgBlAHQAdwBvAHIAawBzACAAbwByACAAZABpAHIAZQBjAHQAIABmAHIAbwBtACAAdABoAGUAIABoAGkAZwBoACAALQAgAHAAcgBlAHMAcwB1AHIAZQAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBIAG8AdQBzAGUAaABvAGwAZABzACAAYQBuAGQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdQBzAGUAcgBzACAAdABlAG4AZAAgAHQAbwAgAGIAZQAgAHMAZQByAHYAZQBkACAAYgB5ACAAdABoAGUAIABmAG8AcgBtAGUAcgAsACAAYQBuAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABnAGUAbgBlAHIAYQB0AG8AcgBzACAAYQBuAGQAIABsAGEAcgBnAGUAIABpAG4AZAB1AHMAdAByAGkAYQBsACAAcABsAGEAbgB0AHMAIABmAHIAbwBtACAAdABoAGUAIABsAGEAdAB0AGUAcgAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIATQBlAHQAcgBvACAAaQBzACAAZABlAGYAaQBuAGUAZAAgAGEAcwAgAGwAbwBjAGEAdABlAGQAIABvAG4AIABvAHIAIABlAGEAcwB0ACAAbwBmACAAdABoAGUAIABkAGkAdgBpAGQAaQBuAGcAIAByAGEAbgBnAGUAIABpAG4AIABOAFMAVwAsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABDAGEAbgBiAGUAcgByAGEAIABhAG4AZAAgAFEAdQBlAGEAbgBiAGUAeQBhAG4ALAAgAE0AZQBsAGIAbwB1AHIAbgBlACwAIABCAHIAaQBzAGIAYQBuAGUALAAgAEEAZABlAGwAYQBpAGQAZQAgAG8AcgAgAFAAZQByAHQAaAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAE8AdABoAGUAcgB3AGkAcwBlACwAIAB0AGgAZQAgAG4AbwBuACAALQAgAG0AZQB0AHIAbwAgAGYAYQBjAHQAbwByACAAcwBoAG8AdQBsAGQAIABiAGUAIAB1AHMAZQBkAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBGAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABhAGwAbAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAB3AGgAaQBjAGgAIABtAGEAeQAgAGkAbgBjAGwAdQBkAGUAIABjAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFQAYQBiAGwAZQAgADYAIABpAHMAIABuAG8AdAAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIAB0AG8AIABlAHQAaABhAG4AZQAuACAAUwBlAGUAIABUAGEAYgBsAGUAIAA3ACAASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGUAdABoAGEAbgBlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBDACAAPQAgAEMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAC4AIABTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAVABhAHMAbQBhAG4AaQBhACAAYQBuAGQAIAB0AGgAZQAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAYQByAGUAIABuAG8AdAAgAGEAdgBhAGkAbABhAGIAbABlACAAZAB1AGUAIAB0AG8AIABjAG8AbgBmAGkAZABlAG4AdABpAGEAbABpAHQAeQAgAGMAbwBuAHMAdAByAGEAaQBuAHQAcwAgAHQAaABhAHQAIABhAHIAaQBzAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABhACAAbABpAG0AaQB0AGUAZAAgAG4AdQBtAGIAZQByACAAbwBmACAATgBHAEUAUgAgAGQAYQB0AGEAIABpAG4AcAB1AHQAcwAuACAASQB0ACAAaQBzACAAcwB1AGcAZwBlAHMAdABlAGQAIAB0AGgAYQB0ACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABWAGkAYwB0AG8AcgBpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgB3AGgAaQBsAGUAIABmAG8AcgAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHQAaABlACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAaQBzACAAYQBwAHAAcgBvAHAAcgBpAGEAdABlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGQAbwAgAG4AbwB0ACAAaQBuAGMAbAB1AGQAZQAgAGYAdQBnAGkAdABpAHYAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGwAZQBhAGsAYQBnAGUAIABmAHIAbwBtACAAbABvAHcAIABwAHIAZQBzAHMAdQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABpAG8AbgAgAHAAaQBwAGUAbABpAG4AZQAgAG4AZQB0AHcAbwByAGsAcwAgAHcAaABpAGwAZQAgAHQAaABvAHMAZQAgAGYAcgBvAG0AIABoAGkAZwBoACAAcAByAGUAcwBzAHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAGcAYQBzACAAbgBlAHQAdwBvAHIAawBzACAAYQByAGUAIABjAG8AbgBzAGkAZABlAHIAZQBkACAAbgBlAGcAbABpAGcAaQBiAGwAZQAuAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGEAbgBkACAAaQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAZQByAHQAYQBpAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgA1ACwAIAA4ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABjAG8AbQBiAHUAcwB0AGUAZABcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAEMAbwBuAHQAZQBuAHQAIABGAGEAYwB0AG8AcgAgACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbABzACAAKABvAHQAaABlAHIAIAB0AGgAYQBuACAAcABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbAAgAHUAcwBlAGQAIABhAHMAIABmAHUAZQBsACkALAAgAGUALgBnAC4AIABsAHUAYgByAGkAYwBhAG4AdABzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADEAMwAuADkALAAgADAALgAwACwAIAAwAC4AMAAsACAAMQAzAC4AOQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAZwByAGUAYQBzAGUAcwBcACIALAAgADMAOAAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAzAC4ANQAsACAAMAAuADAALAAgADAALgAwACwAIAAzAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAcgB1AGQAZQAgAG8AaQBsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABjAHIAdQBkAGUAIABvAGkAbAAgAGMAbwBuAGQAZQBuAHMAYQB0AGUAcwBcACIALAAgADQANQAuADMALAAgAFwAIgB0AFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADYAOQAuADgAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABsAGkAcQB1AGkAZABzAFwAIgAsACAANAA2AC4ANQAsACAAXAAiAHQAXAAiACwAIAA2ADEALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgAxAC4AMgA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdQB0AG8AbQBvAHQAaQB2AGUAIABnAGEAcwBvAGwAaQBuAGUAIAAvACAAcABlAHQAcgBvAGwAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADAALgAyACwAIAAwAC4AMgAsACAANgA3AC4AOAAwACwAIAAxADcALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuACAAZwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsATABcACIALAAgADYANwAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA0ADAALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBLAGUAcgBvAHMAZQBuAGUAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA3AC4ANQAsACAAXAAiAGsATABcACIALAAgADYAOAAuADkALAAgADAALgAwADEALAAgADAALgAyACwAIAA2ADkALgAxADEALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIAB0AHUAcgBiAGkAbgBlACAAZgB1AGUAbAAgAC8AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYAOQAuADgAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHQAaQBuAGcAIABvAGkAbABcACIALAAgADMANwAuADMALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4ANwAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADcAMAAuADIAMAAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA0ACwAIAAwAC4AMgAsACAANwAzAC4AOAA0ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABhAHIAbwBtAGEAdABpAGMAIABoAHkAZAByAG8AYwBhAHIAYgBvAG4AcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAdgBlAG4AdABzADoAIABtAGkAbgBlAHIAYQBsACAAdAB1AHIAcABlAG4AdABpAG4AZQAgAG8AcgAgAHcAaABpAHQAZQAgAHMAcABpAHIAaQB0AHMAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADIALAAgADYAOQAuADkAMwAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYAMAAuADYAMAAsACAAMgAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQBwAGgAdABoAGEAXAAiACwAIAAzADEALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABjAG8AawBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAHQAXAAiACwAIAA5ADIALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAOQAyAC4AOAA4ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAZwBhAHMAIABhAG4AZAAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADIALgA5ACwAIABcACIAdABcACIALAAgADUANAAuADcALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANAAuADcANgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGkAbgBlAHIAeQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADgALAAgADAALgAwADIALAAgADAALgAxACwAIAA2ADkALgA5ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAG8AbAAgAGYAbwByACAAdQBzAGUAIABhAHMAIABhACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGkAbgB0AGUAcgBuAGEAbAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABlAG4AZwBpAG4AZQBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBpAG8AZgB1AGUAbABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAIABhAG4AZAAgAGIAZQBsAG8AdwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAwADIALAAgADAALgAyACwAIAAwAC4AMgAyACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADMAMAAsACAAXAAiAE4ARQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAIABpAG4AIABkAGkAZgBmAGUAcgBlAG4AdAAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADkAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADYALAAgADEAMAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAXAAiACwAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBsAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYANwAuADYAMgAsACAAMQA3AC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAANwAwAC4ANAAxACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAHAAZQB0AHIAbwBsAGUAdQBtACAAZwBhAHMAIAAoAEwAUABHACkAXAAiACwAIAAyADYALgAyACwAIABcACIAawBsAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADUALAAgADAALgAzACwAIAA2ADEALgAwADAALAAgADIAMAAuADIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAGwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4ANQAsACAANwA0AC4AMQA4ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBFAHQAaABhAG4AbwBsAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADIALAAgADAALgA0ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQgBpAG8AZABpAGUAcwBlAGwAXAAiACwAIAAzADQALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgA4ACwAIAAxAC4ANwAsACAAMgAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAAMAAuADUAMQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAE8AdABoAGUAcgAgAGIAaQBvAGYAdQBlAGwAcwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAZwBoAHQAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADcALgAzACwAIAAwAC4AMwAsACAANQA5AC4AMAAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBDAG8AbQBwAHIAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAyAC4AOAAsACAAMAAuADMALAAgADUANAAuADUALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsAbABcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADAANwAsACAAMAAuADQALAAgADcAMAAuADMANwAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADEALAAgADAALgA0ACwAIAA3ADAALgA0ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANAAsACAANwAwAC4ANQAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADcALAAgADAALgA0ACwAIAAwAC4ANAA3ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4ANAAsACAAMAAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADQALAAgADAALgA2ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdABcACIALAAgADMAMwAuADEALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgAwACwAIAAwAC4AMAA2ACwAIAAwAC4ANgAsACAANgA3AC4ANgA2ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwA2AC4AOAAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADYALAAgADAALgAwADEALAAgADAALgA2ACwAIAA3ADAALgAyADEALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA2ACwAIAAwAC4ANgAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADEAMAAuADEALAAgADAALgAzACwAIABcACIAXAAiACwAIAAxADcALgAyACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIABcACIAXAAiACwAIAAxADcALgAzACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEAOAAuADAALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAE8AZgBmAC0AcgBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAaQBuACAAbwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQAgAHEAXAAiACwAIABcACIARQBDAFQAcgBhAG4AcwAsAHEAIAAoAEcASgAvAGsATAApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAE8AMgAgAEUARgBUAHIAYQBuACwAMQAsAHQAcQBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAQwBIADQAIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAE4AMgBPACAARQBGAFQAcgBhAG4ALAAxACwAdABnAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAEYAVAByAGEAbgBzACwAMwAsAHEAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAFAAZQB0AHIAbwBsAFwAIgAsACAAMwA0AC4AMgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgADEANwAuADMAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAATABFAEYAVAAoAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQAgAC0AMQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8ARwBlAHQAUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAFMAdAByAGkAbgBnAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFIASQBHAEgAVAAoAEMAZQBsAGwALABMAEUATgAoAEMAZQBsAGwAKQAtAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8AVABvAHQAYQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBcAG4APQAgAEwAQQBNAEIARABBACgAXABuACAAIAAgACAARgB1AGUAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAsACAARgB1AGUAbABVAHMAZQAsACAARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAsACAARgB1AGUAbABUAHkAcABlACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgAFMAVQBNACgAXABuACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAXABuACAAIAAgACAAIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFQAeQBwAGUAKQAgACoAIABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABVAHMAZQBBAHIAcgBhAHkAIAA9ACAARgB1AGUAbABVAHMAZQApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIAAwAFwAbgAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgAOgAgAEYAdQBlAGwAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA4AC4AMQAgAEYAdQBlAGwAIABVAHMAZQAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsACAARQBDACwAIABFAEYALABcAG4AIAAgACAAIAAoAFEAIAAqACAARQBDACAAKgAgAEUARgApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAGMAbwBtAGIAdQBzAHQAZQBkACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAGsATABcAG4ARQBDACAAOgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwAgADoAIABrAGcAIABDAE8AMgBlACAALwAgAEcASgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AVAByAGEAbgBzAHQAcQAsACAARQBDAF8AVAByAGEAbgBzAHEALAAgAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADgALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADMAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFQAcgBhAG4AcwAsAHQAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEMAXwB7AFQAcgBhAG4AcwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBUAHIAYQBuAHMALAAxACwAdABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBUAHIAYQBuAHMAdABxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlACAALwAgAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHEAXAAiACwAIABcACIARgB1AGUAbAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAXAAiACwAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXABuAFEAIAA6ACAAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABHAEoALwBrAEwAXABuAEUARgAgADoAIABTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBTAEMAcQAsACAARQBDAF8AUwBDAHEALAAgAEUARgBfAFMAQwAxAHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgADIALgAyACAARQBzAHQAaQBtAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABlAG4AZQByAGcAeQAgAHMAbwB1AHIAYwBlAHMAIAAtACAAQwBhAGwAYwB1AGwAYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHQAIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEAXABcAGwAZQBmAHQAKABRAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAUwBDACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFMAQwAsADEALABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFMAQwBxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAdQBzAGUAZAAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAFYAYQByAGkAZQBzACAAYgBhAHMAZQBkACAAbwBuACAAZgB1AGUAbAAgAHQAeQBwAGUAOgAgAGsATAAsACAAbQAzACwAIABHAEoAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMAXwBTAEMAcQBcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFMAQwAxAHEAZwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQwBcACIALAAgAFwAIgBTAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAMQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA5ADoAIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA5AC4AMQAgAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgBUAGgAZQAgAHQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBpAG4AZwAgAGQAdQByAGkAbgBnACAAbwBwAGUAcgBhAHQAaQBvAG4AIAAoAG4AbwB0ACAAZAB1AHIAaQBuAGcAIABpAG4AcwB0AGEAbABsAGEAdABpAG8AbgAgAG8AcgAgAGQAaQBzAHAAbwBzAGEAbAApAFwAbgBHAFcAUABSACAAOgAgAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgADoAIABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBjAGgAYQByAGcAZQBfAFIAYQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIABjAG8AbgB0AGEAaQBuAGUAZAAgAGkAbgAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgADoAIABrAGcAXABuAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEAIAA6ACAAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByACAAOgAgAFAAZQByAGMAZQBuAHQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGMAaABhAHIAZwBlAF8AUgBhACwAIABsAGUAYQBrAGEAZwBlAHIAYQB0AGUAXwBhACwAXABuACAAIAAgACAAKABjAGgAYQByAGcAZQBfAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALwAxADAAMAApACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAFIALAAgAEcAVwBQAF8AUgAsAFwAbgAgACAAIAAgACgAKABFAF8AUgAgACoAIAAxADAAXgAzACkAIAAqACAARwBXAFAAXwBSACkAIAAqACAAMQAwAF4ALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGEAZwBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABjAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBSAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGcAYQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADkALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMwAuADEAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAaQBuAGQAdQBzAHQAcgBpAGEAbAAgAHAAcgBvAGMAZQBzAHMAZQBzACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAtACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBhAGcAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBjAGgAYQByAGcAZQBfAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALwAxADAAMAApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AUgAgAD0AIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGEAIABcAFwAbABlAGYAdAAoACAAYwBoAGEAcgBnAGUAXwB7AFIAYQB9ACAAXABcAHQAaQBtAGUAcwAgAFwAXABmAHIAYQBjAHsAbABlAGEAawBhAGcAZQBcAFwALAByAGEAdABlAF8AYQB9AHsAMQAwADAAfQAgAFwAXAByAGkAZwBoAHQAKQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBDAE8AMgBlACAAPQAgAFwAXABsAGUAZgB0ACgARQBfAFIAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AIABcAFwAcgBpAGcAaAB0ACkAIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwBSACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAGgAYQByAGcAZQBfAFIAYQBcACIALAAgAFwAIgBBAG0AbwB1AG4AdAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIABjAG8AbgB0AGEAaQBuAGUAZAAgAGkAbgAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBsAGUAYQBrAGEAZwBlAHIAYQB0AGUAXwBhAFwAIgAsACAAXAAiAFAAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAAdABvAHQAYQBsACAAYwBoAGEAcgBnAGUAIABsAGUAYQBrAGUAZAAgAGYAcgBvAG0AIABhAHAAcABsAGkAYQBuAGMAZQAgAGEAIABlAGEAYwBoACAAeQBlAGEAcgBcACIALAAgAFwAIgBQAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYQBcACIALAAgAFwAIgBBAHAAcABsAGkAYQBuAGMAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAFwAIgAsACAAXAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAFIAXAAiACwAIABcACIAVABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSAFwAIgAsACAAXAAiAHQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABnAGEAcwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADkALgAxAC4AMQAgACgAMQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABfAFIAXAAiACwAIABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSAFwAIgAsACAAXAAiAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAZQBxAHUAYQB0AGkAbwBuACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIAB0AG8AIABDAE8AMgAtAGUAIAB1AHMAaQBuAGcAIAB0AGgAZQAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABcAHUAMAAwADIANwBzACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIAAoAEcAVwBQACkALgBcACIAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAVABhAGIAbABlACAAMgAzACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAQQBwAHAAZQBuAGQAaQB4ACAAMgAgAC0AIABUAGEAYgBsAGUAIAAyADMAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMAOQAsACAANQAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAGgAZQBtAGkAYwBhAGwAIABmAG8AcgBtAHUAbABhAFwAIgAsACAAXAAiAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAKABBAFIANQApAFwAIgAsACAAXAAiAEcAYQBzACAALQAgAEYAQwAgAG4AYQBtAGUAXAAiACwAIABcACIAQQBkAGkAdABpAG8AbgBhAGwAIABkAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlAFwAIgAsACAAXAAiAEMATwAyAFwAIgAsACAAMQAsACAAXAAiAEMATwAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAQwBIADQAXAAiACwAIAAyADgALAAgAFwAIgBDAEgANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlAFwAIgAsACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUALAAgAFwAIgBOADIATwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAbABwAGgAdQByACAAaABlAHgAYQBmAGwAdQBvAHIAaQBkAGUAXAAiACwAIABcACIAUwBGADYAXAAiACwAIAAyADMANQAwADAALAAgAFwAIgBTAEYANgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMwAgACgAUgAtADIAMwApAFwAIgAsACAAXAAiAEMASABGADMAXAAiACwAIAAgADEAMgA0ADAAMAAsACAAXAAiAEgARgBDAC0AMgAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMwAyACAAKABSAC0AMwAyACkAXAAiACwAIABcACIAQwBIADIARgAyAFwAIgAsACAANgA3ADcALAAgAFwAIgBIAEYAQwAtADMAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADQAMQAgACgAUgAtADQAMQApAFwAIgAsACAAXAAiAEMASAAzAEYAXAAiACwAIAAgADEAMQA2ACwAIABcACIASABGAEMALQA0ADEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQA0ADMALQAxADAAbQBlAGUAIAAoAFIALQA0ADMAMQAwAG0AZQBlACkAXAAiACwAIABcACIAQwA1AEgAMgBGADEAMABcACIALAAgADEANgA1ADAALAAgAFwAIgBIAEYAQwAtADQAMwAtADEAMABtAGUAZQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMgA1ACAAKABSAC0AMQAyADUAKQBcACIALAAgAFwAIgBDADIASABGADUAXAAiACwAIAAgADMAMQA3ADAALAAgAFwAIgBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAzADQAIAAoAFIALQAxADMANAApAFwAIgAsACAAXAAiAEMAMgBIADIARgA0ACAAKABDAEgARgAyAEMASABGADIAKQBcACIALAAgACAAMQAxADIAMAAsACAAXAAiAEgARgBDAC0AMQAzADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADMANABhACAAKABSAC0AMQAzADQAYQApAFwAIgAsACAAXAAiAEMAMgBIADIARgA0ACAAKABDAEgAMgBGAEMARgAzACkAXAAiACwAIAAxADMAMAAwACwAIABcACIASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA0ADMAIAAoAFIALQAxADQAMwApAFwAIgAsACAAXAAiAEMAMgBIADMARgAzACAAKABDAEgARgAyAEMASAAyAEYAKQBcACIALAAgADMAMgA4ACwAIABcACIASABGAEMALQAxADQAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEANAAzAGEAIAAoAFIALQAxADQAMwBhACkAXAAiACwAIABcACIAQwAyAEgAMwBGADMAIAAoAEMARgAzAEMASAAzACkAXAAiACwAIAA0ADgAMAAwACwAIABcACIASABGAEMALQAxADQAMwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA1ADIAYQAgACgAUgAtADEANQAyAGEAKQBcACIALAAgAFwAIgBDADIASAA0AEYAMgAgACgAQwBIADMAQwBIAEYAMgApAFwAIgAsACAAMQAzADgALAAgAFwAIgBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADIANwBlAGEAIAAoAFIALQAyADIANwBlAGEAKQBcACIALAAgAFwAIgBDADMASABGADcAXAAiACwAIAAzADMANQAwACwAIABcACIASABGAEMALQAyADIANwBlAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADMANgBmAGEAIAAoAFIALQAyADMANgBmAGEAKQBcACIALAAgAFwAIgBDADMASAAyAEYANgBcACIALAAgADgAMAA2ADAALAAgAFwAIgBIAEYAQwAtADIAMwA2AGYAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIANAA1AGMAYQAgACgAUgAtADIANAA1AGMAYQApAFwAIgAsACAAXAAiAEMAMwBIADMARgA1AFwAIgAsACAANwAxADYALAAgAFwAIgBIAEYAQwAtADIANAA1AGMAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIANAA1AGYAYQAgACgAUgAtADIANAA1AGYAYQApAFwAIgAsACAAXAAiAEMASABGADIAQwBIADIAQwBGADMAXAAiACwAIAA4ADUAOAAsACAAXAAiAEgARgBDAC0AMgA0ADUAZgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMwA2ADUAbQBmAGMAIAAoAFIALQAzADYANQBtAGYAYwApAFwAIgAsACAAXAAiAEMASAAzAEMARgAyAEMASAAyAEMARgAzAFwAIgAsACAAOAAwADQALAAgAFwAIgBIAEYAQwAtADMANgA1AG0AZgBjAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIAIAAoAFIALQAyADIAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAMgBcACIALAAgADEANwA2ADAALAAgAFwAIgBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADIAMwAgACgAUgAtADEAMgAzACkAXAAiACwAIABcACIAQwBIAEMAbAAyADIAQwBGADMAXAAiACwAIAA3ADkALAAgAFwAIgBIAEMARgBDAC0AMQAyADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEAMgA0ACAAKABSAC0AMQAyADQAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAQwBGADMAXAAiACwAIAA1ADIANwAsACAAXAAiAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQA0ADEAYgAgACgAUgAtADEANAAxAGIAKQBcACIALAAgAFwAIgBDAEgAMwBDAEMAbAAyAEYAXAAiACwAIAA3ADgAMgAsACAAXAAiAEgAQwBGAEMALQAxADQAMQBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADQAMgBiACAAKABSAC0AMQA0ADIAYgApAFwAIgAsACAAXAAiAEMASAAyAEMAQwBsAEYAMgBcACIALAAgADEAOQA4ADAALAAgAFwAIgBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBhACAAKABSAC0AMgAyADUAYwBhACkAXAAiACwAIABcACIAQwBIAEMAbAAyAEMARgAyAEMARgAzAFwAIgAsACAAMQAyADcALAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGIAIAAoAFIALQAyADIANQBjAGIAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAQwBGADIAQwBDAEkARgAyAFwAIgAsACAANQAyADUALAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMQA0ACAAUABlAHIAZgBsAHUAbwByAG8AbQBlAHQAaABhAG4AZQAgACgAdABlAHQAcgBhAGYAbAB1AG8AcgBvAG0AZQB0AGgAYQBuAGUAKQBcACIALAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAALAAgAFwAIgBQAEYAQwAtADEANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADEAMQA2ACAAUABlAHIAZgBsAHUAbwByAG8AZQB0AGgAYQBuAGUAIAAoAGgAZQB4AGEAZgBsAHUAbwByAG8AZQB0AGgAYQBuAGUAKQBcACIALAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAxADEAMAAwACwAIABcACIAUABGAEMALQAxADEANgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADIAMQA4ACAAUABlAHIAZgBsAHUAbwByAG8AcAByAG8AcABhAG4AZQBcACIALAAgAFwAIgBDADMARgA4AFwAIgAsACAAOAA5ADAAMAAsACAAXAAiAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAzADEALQAxADAAIABQAGUAcgBmAGwAdQBvAHIAbwBiAHUAdABhAG4AZQBcACIALAAgAFwAIgBDADQARgAxADAAXAAiACwAIAA5ADIAMAAwACwAIABcACIAUABGAEMALQAzADEALQAxADAAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAzADEAOAAgAFAAZQByAGYAbAB1AG8AcgBvAGMAeQBjAGwAbwBiAHUAdABhAG4AZQBcACIALAAgAFwAIgBjAC0AQwA0AEYAOABcACIALAAgADkANQA0ADAALAAgAFwAIgBQAEYAQwAtADMAMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0ANAAxAC0AMQAyACAAUABlAHIAZgBsAHUAbwByAG8AcABlAG4AdABhAG4AZQBcACIALAAgAFwAIgBDADUARgAxADIAXAAiACwAIAA4ADUANQAwACwAIABcACIAUABGAEMALQA0ADEALQAxADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA1ADEALQAxADQAIABQAGUAcgBmAGwAdQBvAHIAbwBoAGUAeABhAG4AZQBcACIALAAgAFwAIgBDADYARgAxADQAXAAiACwAIAA3ADkAMQAwACwAIABcACIAUABGAEMALQA1ADEALQAxADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA5ADEALQAxADgAIABQAGUAcgBmAGwAdQBuAGEAZgBlAG4AZQBcACIALAAgAFwAIgBDADEAMABGADEAOABcACIALAAgADcAMQA5ADAALAAgAFwAIgBQAEYAQwAtADkAMQAtADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMgBcACIALAAgAFwAIgBDAEMAbAAyAEYAMgBcACIALAAgADEAMAAyADAAMAAsACAAXAAiAEMARgBDAC0AMQAyAFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADMAXAAiACwAIABcACIAQwBDAGwARgAzAFwAIgAsACAAMQAzADkAMAAwACwAIABcACIAQwBGAEMALQAxADMAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAEMAQwBsAEYAMgBDAEMAbABGADIAXAAiACwAIAA4ADUAOQAwACwAIABcACIAQwBGAEMALQAxADEANABcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAQwBDAGwARgAyAEMARgAzAFwAIgAsACAANwA2ADcAMAAsACAAXAAiAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcARwBBAFMAIAAtACAARgBDACAAbgBhAG0AZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAHQAcgB1AG4AYwBhAHQAZQBkACAAZwBhAHMAIABuAGEAbQBlACAAdABvACAAYQBsAGwAbwB3ACAAbQBhAHQAYwBoAGkAbgBnACAAdwBpAHQAaAAgAG8AdABoAGUAcgAgAHQAYQBiAGwAZQBzAC4AIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABnAGEAcwBlAHMAIABmAHIAbwBtACAASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQAuACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAQQBkAGQAaQB0AGkAbwBuAGEAbAAgAGQAYQB0AGEAIABzAG8AdQByAGMAZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAC4AXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAQgBsAGUAbgBkAGUAZAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAbABlAG4AZABlAGQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAcwAgACgAbQBhAG4AeQAgAGMAbwBuAHQAYQBpAG4AaQBuAGcAIABIAEYAQwBTACAAYQBuAGQALwBvAHIAIABQAEYAQwBTACkAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABBAHAAcABlAG4AZABpAHgAIAAyACAALQAgAFQAYQBiAGwAZQAgADIANABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAxACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABlAG4AZABcACIALAAgAFwAIgBDAG8AbgBzAHQAaQB0AHUAZQBuAHQAcwBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwBpAHQAaQBvAG4AIAAoACUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAFIALQA0ADAAMAAgAGMAYQBuACAAaABhAHYAZQAgAHYAYQByAGkAbwB1AHMAIABwAHIAbwBwAG8AcgB0AGkAbwBuAHMAIABvAGYAIABDAEYAQwAtADEAMgAgAGEAbgBkACAAQwBGAEMALQAxADEANAAuACAAVABoAGUAIABlAHgAYQBjAHQAIABjAG8AbQBwAG8AcwBpAHQAaQBvAG4AIABuAGUAZQBkAHMAIAB0AG8AIABiAGUAIABzAHAAZQBjAGkAZgBpAGUAZAAsACAAZQAuAGcALgAsACAAUgAtADQAMAAwACAAKAA2ADAALwA0ADAAKQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAA1ADMALgAwAC8AMQAzAC4AMAAvADMANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgANgAxAC4AMAAvADEAMQAuADAALwAyADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEMAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADMAMwAuADAALwAxADUALgAwAC8ANQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA2ADAALgAwAC8AMgAuADAALwAzADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAyAEIAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADMAOAAuADAALwAyAC4AMAAvADYAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADMAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANQAuADAALwA3ADUALgAwAC8AMgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMwBCAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA1AC4AMAAvADUANgAuADAALwAzADkALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA0AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADQANAAuADAALwA1ADIALgAwAC8ANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADUAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AIABIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQA0ADIAYgAvAFAARgBDAC0AMwAxADgAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANwAuADAALwA1AC4ANQAvADQAMgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADYAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQA1AC4AMAAvADEANAAuADAALwA0ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAwAC4AMAAvADQAMAAuADAALwA0ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEIAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQAwAC4AMAAvADcAMAAuADAALwAyADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEMAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAzAC4AMAAvADIANQAuADAALwA1ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEQAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQA1AC4AMAAvADEANQAuADAALwA3ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEUAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgA1AC4AMAAvADEANQAuADAALwA2ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA4AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA3AC4AMAAvADQANgAuADAALwA0ADcALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgAwAC4AMAAvADIANQAuADAALwAxADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgA1AC4AMAAvADIANQAuADAALwAxADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAwAEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiACgANQAwAC4AMAAvADUAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADAAQgBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANQA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBBAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMQAuADUALwA4ADcALgA1AC8AMQAxAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBCAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMwAuADAALwA5ADQALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADEAQwBcACIALAAgAFwAIgBIAEMALQAxADIANwAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADMALgAwAC8AOQA1AC4ANQAvADEALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAyAEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADcAMAAuADAALwA1AC4AMAAvADIANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADMAQQBcACIALAAgAFwAIgBQAEYAQwAtADIAMQA4AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADkALgAwAC8AOAA4AC4AMAAvADMALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMQAuADAALwAyADgALgA1AC8ANAAuADAALwAxADYALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMAAuADAALwAzADkALgAwAC8AMQAuADUALwA5AC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA4ADIALgAwAC8AMQA4AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAyADUALgAwAC8ANwA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAFwAIgAsACAAXAAiACgANQA5AC4AMAAvADMAOQAuADUALwAxAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABcACIALAAgAFwAIgAoADQANgAuADYALwA1ADAALgAwAC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADgAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAxAC4ANQAvADkANgAuADAALwAyAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAOQBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEUALQBFADEANwAwAFwAIgAsACAAXAAiACgANwA3AC4AMAAvADEAOQAuADAALwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMABBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgAOAA4AC4AMAAvADEAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADEAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgANQA4AC4AMAAvADQAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgANQAuADEALwAxADEALgA1AC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQgBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADUANQAuADAALwA0ADIALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQwBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgAMgAuADAALwAxADUALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA3ADMALgA4AC8AMgA2AC4AMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADIAXAAiACwAIABcACIAKAA3ADUALgAwAC8AMgA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADEANQBcACIALAAgAFwAIgAoADQAOAAuADgALwA1ADEALgAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAzAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AQwBGAEMALQAxADMAXAAiACwAIABcACIAKAA0ADAALgAxAC8ANQA5AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANABcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAKAA0ADgALgAyAC8ANQAxAC4AOAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANQBcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEgAQwBGAEMALQAzADEAXAAiACwAIABcACIAKAA3ADgALgAwAC8AMgAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANgBcACIALAAgAFwAIgBDAEYAQwAtADMAMQAvAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAKAA1ADUALgAxAC8ANAA0AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEANAAzAGEAXAAiACwAIABcACIAKAA1ADAALgAwAC8ANQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOABBAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AUABGAEMALQAxADEANgBcACIALAAgAFwAIgAoADMAOQAuADAALwA2ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA4AEIAXAAiACwAIABcACIASABGAEMALQAyADMALwBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiACgANAA2AC4AMAAvADUANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADkAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADQANAAuADAALwA1ADYALgAwACkAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAYwBoAGEAbgBnAGUAZAAgAEgAQwA2ADAAMABhACAAdABvACAASABDAC0ANgAwADAAYQAgAGYAbwByACAAYgBsAGUAbgBkACAAUgAtADQAMQA0AEIALgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABmAG8AcgAgAGIAbABlAG4AZAAgAFIALQA0ADAANQBBACAALQAgAEMAaABhAG4AZwBlAGQAIABIAEMARgBDADEANAAyAGIAIAB0AG8AIABIAEMARgBDAC0AMQA0ADIAYgAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEwAZQBhAGsAYQBnAGUAIAByAGEAdABlAHMAIABmAG8AcgAgAGMAbwBtAG0AbwBuACAAcgBlAGYAcgBpAGcAZQByAGEAdABpAG8AbgAgAGEAbgBkACAAYQBpAHIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAGMAYQB0AGkAdgBlACAAbABlAGEAawBhAGcAZQAgAHIAYQB0AGUAcwAgAGYAbwByACAAYwBvAG0AbQBvAG4AIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuACAAYQBuAGQAIABhAGkAcgAgAC0AIABjAG8AbgBkAGkAdABpAG8AbgBpAG4AZwAgAGUAcQB1AGkAcABtAGUAbgB0AFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADEAMABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ADEALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAGwAZQBhAGsAYQBnAGUAIAByAGEAdABlACAAKAAlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAcgBlAGYAcgBpAGcAZQByAGEAdABvAHIAcwBcACIALAAgADEALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuAFwAIgAsACAAMQA1AC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcABvAHIAdABhAGIAbABlAFwAIgAsACAAMgAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHMAcABsAGkAdABcACIALAAgADMALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABwAGEAYwBrAGEAZwBlAGQAXAAiACwAIAAyAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAHYAZQBoAGkAYwBsAGUAIABBAC8AQwBcACIALAAgADYALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAdgBlAGgAaQBjAGwAZQAgAEEALwBDAFwAIgAsACAAMQAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBhAGwAYwB1AGwAYQB0AGUAQgBsAGUAbgBkAEcAVwBQAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMQAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMgAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMwAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAANAAsAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAxACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAyACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAzACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAA0ACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0ACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGEAbABjAHUAbABhAHQAZQBCAGwAZQBuAGQARwBXAFAAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -19192,19 +19312,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwAgAGkAbgBjAGwAdQBkAGkAbgBnACAAbABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIAAgAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADkALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMgAsACAAMAAuADAAMwAsACAANQAxAC4ANgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAGEAbAAgAG0AaQBuAGUAIAB3AGEAcwB0AGUAIABnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADkALAAgADQALgA2ACwAIAAwAC4AMwAsACAANQA2AC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAKAByAGUAdgBlAHIAdABpAG4AZwAgAHQAbwAgAHMAdABhAG4AZABhAHIAZAAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAKQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBwAHIAbwBjAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAANgAyADkALAAgAFwAIgBtADMAXAAiACwAIAA1ADYALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMAAzACwAIAA1ADYALgA1ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AawBlACAAbwB2AGUAbgAgAGcAYQBzAFwAIgAsACAAMAAuADAAMQA4ADEALAAgAFwAIgBtADMAXAAiACwAIAAzADcALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAA1ACwAIAAzADcALgAwADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGwAYQBzAHQAIABmAHUAcgBuAGEAYwBlACAAZwBhAHMAXAAiACwAIAAwAC4AMAAwADQAMAAsACAAXAAiAG0AMwBcACIALAAgADIAMwA0AC4AMAAsACAAMAAuADAAMwAsACAAMAAuADAAMgAsACAAMgAzADQALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMAAsACAAXAAiAG0AMwBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsATABcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBlAG8AdQBzACAAZgBvAHMAcwBpAGwAIABmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAYQBuAGQAZgBpAGwAbAAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIAAoAG0AZQB0AGgAYQBuAGUAIABvAG4AbAB5ACkAXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4ALAAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA3ADAALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBtAGUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAwADMALAAgADAALgAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAHkAZAByAG8AZwBlAG4AXAAiACwAIAAwAC4AMAAxADIAMgAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMAAsACAAMAAuADUALAAgADAALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgADEALAAgAFwAIgBHAEoAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAzACwAIAA2ADAALgAyADcAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABcAHUAMAAwADIANwBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAdQAwADAAMgA3ACAAdwBlAHIAZQAgAGEAZABkAGUAZAAsACAAZQBhAGMAaAAgAHcAaQB0AGgAIABhAG4AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgADEAIABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAC4AIABUAGgAaQBzACAAaQBzACAAZgBvAHIAIAB1AHMAZQByAHMAIAB3AGgAbwAgAGgAYQB2AGUAIABmAHUAZQBsACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAZABhAHQAYQAgAGkAbgAgAEcASgAgAHIAYQB0AGgAZQByACAAdABoAGEAbgAgAG0AMwAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAuAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABOAGEAdAB1AHIAYQBsACAARwBhAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABNAGUAdAByAG8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AbwBuACAALQAgAE0AZQB0AHIAbwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAOAAuADgALAAgADcALgA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAAxADAALgA3ACwAIAAxADAALgA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAANAAuADEALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAANAAuADAALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIAA0AC4AMQAsACAANAAuADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABOAFMAVwAgAGEAbgBkACAAQQBDAFQAIABzAHAAbABpAHQAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAcgBvAHcAcwAuACAAXAB1ADAAMAAyADcAQwBcAHUAMAAwADIANwAgAFYAYQBsAHUAZQBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAcgBlAHAAbABhAGMAZQBkACAAdwBpAHQAaAAgAHQAaABvAHMAZQAgAGYAbwByACAAVgBpAGMAdABvAHIAaQBhACAAYQBuAGQAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAByAGUAcwBwAGUAYwB0AGkAdgBlAGwAeQAuACAAKABTAGUAZQAgAGEAcABwAGUAbgBkAGkAYwBlAHMAKQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADIALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBBAHMAIABTAGMAbwBwAGUAIAAzACAAZgBhAGMAdABvAHIAcwAgAGEAcgBlACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGEAdAAgAHQAaABlACAAcABvAGkAbgB0ACAAdwBoAGUAcgBlACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAaQBzACAAZABlAGwAaQB2AGUAcgBlAGQAIAB0AG8AIABlAG4AZAAgAHUAcwBlAHIAcwAsACAAaQB0ACAAaQBzACAAbgBlAGMAZQBzAHMAYQByAHkAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAdAAgAGUAYQBjAGgAIABvAGYAIAB0AGgAZQAgAGwAbwBhAGQAIABjAGUAbgB0AHIAZQBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIARwBhAHMAIAByAGUAYQBjAGgAZQBzACAAZQBuAGQAIAB1AHMAZQByAHMAIABlAGkAdABoAGUAcgAgAGYAcgBvAG0AIAB0AGgAZQAgAG0AZQB0AHIAbwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAbgBlAHQAdwBvAHIAawBzACAAbwByACAAZABpAHIAZQBjAHQAIABmAHIAbwBtACAAdABoAGUAIABoAGkAZwBoACAALQAgAHAAcgBlAHMAcwB1AHIAZQAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBIAG8AdQBzAGUAaABvAGwAZABzACAAYQBuAGQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdQBzAGUAcgBzACAAdABlAG4AZAAgAHQAbwAgAGIAZQAgAHMAZQByAHYAZQBkACAAYgB5ACAAdABoAGUAIABmAG8AcgBtAGUAcgAsACAAYQBuAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABnAGUAbgBlAHIAYQB0AG8AcgBzACAAYQBuAGQAIABsAGEAcgBnAGUAIABpAG4AZAB1AHMAdAByAGkAYQBsACAAcABsAGEAbgB0AHMAIABmAHIAbwBtACAAdABoAGUAIABsAGEAdAB0AGUAcgAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIATQBlAHQAcgBvACAAaQBzACAAZABlAGYAaQBuAGUAZAAgAGEAcwAgAGwAbwBjAGEAdABlAGQAIABvAG4AIABvAHIAIABlAGEAcwB0ACAAbwBmACAAdABoAGUAIABkAGkAdgBpAGQAaQBuAGcAIAByAGEAbgBnAGUAIABpAG4AIABOAFMAVwAsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABDAGEAbgBiAGUAcgByAGEAIABhAG4AZAAgAFEAdQBlAGEAbgBiAGUAeQBhAG4ALAAgAE0AZQBsAGIAbwB1AHIAbgBlACwAIABCAHIAaQBzAGIAYQBuAGUALAAgAEEAZABlAGwAYQBpAGQAZQAgAG8AcgAgAFAAZQByAHQAaAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAE8AdABoAGUAcgB3AGkAcwBlACwAIAB0AGgAZQAgAG4AbwBuACAALQAgAG0AZQB0AHIAbwAgAGYAYQBjAHQAbwByACAAcwBoAG8AdQBsAGQAIABiAGUAIAB1AHMAZQBkAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBGAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABhAGwAbAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAB3AGgAaQBjAGgAIABtAGEAeQAgAGkAbgBjAGwAdQBkAGUAIABjAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFQAYQBiAGwAZQAgADYAIABpAHMAIABuAG8AdAAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIAB0AG8AIABlAHQAaABhAG4AZQAuACAAUwBlAGUAIABUAGEAYgBsAGUAIAA3ACAASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGUAdABoAGEAbgBlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBDACAAPQAgAEMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAC4AIABTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAVABhAHMAbQBhAG4AaQBhACAAYQBuAGQAIAB0AGgAZQAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAYQByAGUAIABuAG8AdAAgAGEAdgBhAGkAbABhAGIAbABlACAAZAB1AGUAIAB0AG8AIABjAG8AbgBmAGkAZABlAG4AdABpAGEAbABpAHQAeQAgAGMAbwBuAHMAdAByAGEAaQBuAHQAcwAgAHQAaABhAHQAIABhAHIAaQBzAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABhACAAbABpAG0AaQB0AGUAZAAgAG4AdQBtAGIAZQByACAAbwBmACAATgBHAEUAUgAgAGQAYQB0AGEAIABpAG4AcAB1AHQAcwAuACAASQB0ACAAaQBzACAAcwB1AGcAZwBlAHMAdABlAGQAIAB0AGgAYQB0ACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABWAGkAYwB0AG8AcgBpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgB3AGgAaQBsAGUAIABmAG8AcgAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHQAaABlACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAaQBzACAAYQBwAHAAcgBvAHAAcgBpAGEAdABlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGQAbwAgAG4AbwB0ACAAaQBuAGMAbAB1AGQAZQAgAGYAdQBnAGkAdABpAHYAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGwAZQBhAGsAYQBnAGUAIABmAHIAbwBtACAAbABvAHcAIABwAHIAZQBzAHMAdQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABpAG8AbgAgAHAAaQBwAGUAbABpAG4AZQAgAG4AZQB0AHcAbwByAGsAcwAgAHcAaABpAGwAZQAgAHQAaABvAHMAZQAgAGYAcgBvAG0AIABoAGkAZwBoACAAcAByAGUAcwBzAHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAGcAYQBzACAAbgBlAHQAdwBvAHIAawBzACAAYQByAGUAIABjAG8AbgBzAGkAZABlAHIAZQBkACAAbgBlAGcAbABpAGcAaQBiAGwAZQAuAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGEAbgBkACAAaQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAZQByAHQAYQBpAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgA1ACwAIAA4ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABjAG8AbQBiAHUAcwB0AGUAZABcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAEMAbwBuAHQAZQBuAHQAIABGAGEAYwB0AG8AcgAgACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbABzACAAKABvAHQAaABlAHIAIAB0AGgAYQBuACAAcABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbAAgAHUAcwBlAGQAIABhAHMAIABmAHUAZQBsACkALAAgAGUALgBnAC4AIABsAHUAYgByAGkAYwBhAG4AdABzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADEAMwAuADkALAAgADAALgAwACwAIAAwAC4AMAAsACAAMQAzAC4AOQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAZwByAGUAYQBzAGUAcwBcACIALAAgADMAOAAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAzAC4ANQAsACAAMAAuADAALAAgADAALgAwACwAIAAzAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAcgB1AGQAZQAgAG8AaQBsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABjAHIAdQBkAGUAIABvAGkAbAAgAGMAbwBuAGQAZQBuAHMAYQB0AGUAcwBcACIALAAgADQANQAuADMALAAgAFwAIgB0AFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADYAOQAuADgAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABsAGkAcQB1AGkAZABzAFwAIgAsACAANAA2AC4ANQAsACAAXAAiAHQAXAAiACwAIAA2ADEALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgAxAC4AMgA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdQB0AG8AbQBvAHQAaQB2AGUAIABnAGEAcwBvAGwAaQBuAGUAIAAvACAAcABlAHQAcgBvAGwAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADAALgAyACwAIAAwAC4AMgAsACAANgA3AC4AOAAwACwAIAAxADcALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuACAAZwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsATABcACIALAAgADYANwAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA0ADAALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBLAGUAcgBvAHMAZQBuAGUAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA3AC4ANQAsACAAXAAiAGsATABcACIALAAgADYAOAAuADkALAAgADAALgAwADEALAAgADAALgAyACwAIAA2ADkALgAxADEALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIAB0AHUAcgBiAGkAbgBlACAAZgB1AGUAbAAgAC8AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYAOQAuADgAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHQAaQBuAGcAIABvAGkAbABcACIALAAgADMANwAuADMALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4ANwAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADcAMAAuADIAMAAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA0ACwAIAAwAC4AMgAsACAANwAzAC4AOAA0ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABhAHIAbwBtAGEAdABpAGMAIABoAHkAZAByAG8AYwBhAHIAYgBvAG4AcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAdgBlAG4AdABzADoAIABtAGkAbgBlAHIAYQBsACAAdAB1AHIAcABlAG4AdABpAG4AZQAgAG8AcgAgAHcAaABpAHQAZQAgAHMAcABpAHIAaQB0AHMAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADIALAAgADYAOQAuADkAMwAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYAMAAuADYAMAAsACAAMgAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQBwAGgAdABoAGEAXAAiACwAIAAzADEALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABjAG8AawBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAHQAXAAiACwAIAA5ADIALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAOQAyAC4AOAA4ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAZwBhAHMAIABhAG4AZAAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADIALgA5ACwAIABcACIAdABcACIALAAgADUANAAuADcALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANAAuADcANgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGkAbgBlAHIAeQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADgALAAgADAALgAwADIALAAgADAALgAxACwAIAA2ADkALgA5ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAG8AbAAgAGYAbwByACAAdQBzAGUAIABhAHMAIABhACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGkAbgB0AGUAcgBuAGEAbAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABlAG4AZwBpAG4AZQBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBpAG8AZgB1AGUAbABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAIABhAG4AZAAgAGIAZQBsAG8AdwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAwADIALAAgADAALgAyACwAIAAwAC4AMgAyACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADMAMAAsACAAXAAiAE4ARQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAIABpAG4AIABkAGkAZgBmAGUAcgBlAG4AdAAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADkAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADYALAAgADEAMAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAXAAiACwAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBsAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYANwAuADYAMgAsACAAMQA3AC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAANwAwAC4ANAAxACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAHAAZQB0AHIAbwBsAGUAdQBtACAAZwBhAHMAIAAoAEwAUABHACkAXAAiACwAIAAyADYALgAyACwAIABcACIAawBsAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADUALAAgADAALgAzACwAIAA2ADEALgAwADAALAAgADIAMAAuADIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAGwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4ANQAsACAANwA0AC4AMQA4ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBFAHQAaABhAG4AbwBsAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADIALAAgADAALgA0ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQgBpAG8AZABpAGUAcwBlAGwAXAAiACwAIAAzADQALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgA4ACwAIAAxAC4ANwAsACAAMgAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAAMAAuADUAMQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAE8AdABoAGUAcgAgAGIAaQBvAGYAdQBlAGwAcwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAZwBoAHQAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADcALgAzACwAIAAwAC4AMwAsACAANQA5AC4AMAAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBDAG8AbQBwAHIAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAyAC4AOAAsACAAMAAuADMALAAgADUANAAuADUALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsAbABcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADAANwAsACAAMAAuADQALAAgADcAMAAuADMANwAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADEALAAgADAALgA0ACwAIAA3ADAALgA0ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANAAsACAANwAwAC4ANQAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADcALAAgADAALgA0ACwAIAAwAC4ANAA3ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4ANAAsACAAMAAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADQALAAgADAALgA2ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdABcACIALAAgADMAMwAuADEALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgAwACwAIAAwAC4AMAA2ACwAIAAwAC4ANgAsACAANgA3AC4ANgA2ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwA2AC4AOAAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADYALAAgADAALgAwADEALAAgADAALgA2ACwAIAA3ADAALgAyADEALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA2ACwAIAAwAC4ANgAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADEAMAAuADEALAAgADAALgAzACwAIABcACIAXAAiACwAIAAxADcALgAyACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIABcACIAXAAiACwAIAAxADcALgAzACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEAOAAuADAALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAE8AZgBmAC0AcgBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAaQBuACAAbwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQAgAHEAXAAiACwAIABcACIARQBDAFQAcgBhAG4AcwAsAHEAIAAoAEcASgAvAGsATAApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAE8AMgAgAEUARgBUAHIAYQBuACwAMQAsAHQAcQBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAQwBIADQAIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAE4AMgBPACAARQBGAFQAcgBhAG4ALAAxACwAdABnAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAEYAVAByAGEAbgBzACwAMwAsAHEAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAFAAZQB0AHIAbwBsAFwAIgAsACAAMwA0AC4AMgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgADEANwAuADMAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAATABFAEYAVAAoAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQAgAC0AMQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8ARwBlAHQAUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAFMAdAByAGkAbgBnAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFIASQBHAEgAVAAoAEMAZQBsAGwALABMAEUATgAoAEMAZQBsAGwAKQAtAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8AVABvAHQAYQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBcAG4APQAgAEwAQQBNAEIARABBACgAXABuACAAIAAgACAARgB1AGUAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAsACAARgB1AGUAbABVAHMAZQAsACAARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAsACAARgB1AGUAbABUAHkAcABlACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgAFMAVQBNACgAXABuACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAXABuACAAIAAgACAAIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFQAeQBwAGUAKQAgACoAIABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABVAHMAZQBBAHIAcgBhAHkAIAA9ACAARgB1AGUAbABVAHMAZQApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIAAwAFwAbgAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgAOgAgAEYAdQBlAGwAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA4AC4AMQAgAEYAdQBlAGwAIABVAHMAZQAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsACAARQBDACwAIABFAEYALABcAG4AIAAgACAAIAAoAFEAIAAqACAARQBDACAAKgAgAEUARgApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAGMAbwBtAGIAdQBzAHQAZQBkACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAGsATABcAG4ARQBDACAAOgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwAgADoAIABrAGcAIABDAE8AMgBlACAALwAgAEcASgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AVAByAGEAbgBzAHQAcQAsACAARQBDAF8AVAByAGEAbgBzAHEALAAgAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADgALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADMAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFQAcgBhAG4AcwAsAHQAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEMAXwB7AFQAcgBhAG4AcwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBUAHIAYQBuAHMALAAxACwAdABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBUAHIAYQBuAHMAdABxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlACAALwAgAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHEAXAAiACwAIABcACIARgB1AGUAbAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAXAAiACwAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXABuAFEAIAA6ACAAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABHAEoALwBrAEwAXABuAEUARgAgADoAIABTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBTAEMAcQAsACAARQBDAF8AUwBDAHEALAAgAEUARgBfAFMAQwAxAHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgADIALgAyACAARQBzAHQAaQBtAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABlAG4AZQByAGcAeQAgAHMAbwB1AHIAYwBlAHMAIAAtACAAQwBhAGwAYwB1AGwAYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHQAIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEAXABcAGwAZQBmAHQAKABRAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAUwBDACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFMAQwAsADEALABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFMAQwBxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAdQBzAGUAZAAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAFYAYQByAGkAZQBzACAAYgBhAHMAZQBkACAAbwBuACAAZgB1AGUAbAAgAHQAeQBwAGUAOgAgAGsATAAsACAAbQAzACwAIABHAEoAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMAXwBTAEMAcQBcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFMAQwAxAHEAZwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQwBcACIALAAgAFwAIgBTAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAMQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA5ADoAIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA5AC4AMQAgAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgBUAGgAZQAgAHQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBpAG4AZwAgAGQAdQByAGkAbgBnACAAbwBwAGUAcgBhAHQAaQBvAG4AIAAoAG4AbwB0ACAAZAB1AHIAaQBuAGcAIABpAG4AcwB0AGEAbABsAGEAdABpAG8AbgAgAG8AcgAgAGQAaQBzAHAAbwBzAGEAbAApAFwAbgBHAFcAUABSACAAOgAgAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgADoAIABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBjAGgAYQByAGcAZQBfAFIAYQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIABjAG8AbgB0AGEAaQBuAGUAZAAgAGkAbgAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgADoAIABrAGcAXABuAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEAIAA6ACAAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByACAAOgAgAFAAZQByAGMAZQBuAHQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGMAaABhAHIAZwBlAF8AUgBhACwAIABsAGUAYQBrAGEAZwBlAHIAYQB0AGUAXwBhACwAXABuACAAIAAgACAAKABjAGgAYQByAGcAZQBfAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALwAxADAAMAApACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAFIALAAgAEcAVwBQAF8AUgAsAFwAbgAgACAAIAAgACgAKABFAF8AUgAgACoAIAAxADAAXgAzACkAIAAqACAARwBXAFAAXwBSACkAIAAqACAAMQAwAF4ALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGEAZwBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABjAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBSAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGcAYQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADkALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMwAuADEAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAaQBuAGQAdQBzAHQAcgBpAGEAbAAgAHAAcgBvAGMAZQBzAHMAZQBzACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAtACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBhAGcAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBjAGgAYQByAGcAZQBfAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALwAxADAAMAApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AUgAgAD0AIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGEAIABcAFwAbABlAGYAdAAoACAAYwBoAGEAcgBnAGUAXwB7AFIAYQB9ACAAXABcAHQAaQBtAGUAcwAgAFwAXABmAHIAYQBjAHsAbABlAGEAawBhAGcAZQBcAFwALAByAGEAdABlAF8AYQB9AHsAMQAwADAAfQAgAFwAXAByAGkAZwBoAHQAKQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBDAE8AMgBlACAAPQAgAFwAXABsAGUAZgB0ACgARQBfAFIAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AIABcAFwAcgBpAGcAaAB0ACkAIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwBSACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAGgAYQByAGcAZQBfAFIAYQBcACIALAAgAFwAIgBBAG0AbwB1AG4AdAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIABjAG8AbgB0AGEAaQBuAGUAZAAgAGkAbgAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBsAGUAYQBrAGEAZwBlAHIAYQB0AGUAXwBhAFwAIgAsACAAXAAiAFAAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAAdABvAHQAYQBsACAAYwBoAGEAcgBnAGUAIABsAGUAYQBrAGUAZAAgAGYAcgBvAG0AIABhAHAAcABsAGkAYQBuAGMAZQAgAGEAIABlAGEAYwBoACAAeQBlAGEAcgBcACIALAAgAFwAIgBQAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYQBcACIALAAgAFwAIgBBAHAAcABsAGkAYQBuAGMAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAFwAIgAsACAAXAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAFIAXAAiACwAIABcACIAVABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSAFwAIgAsACAAXAAiAHQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABnAGEAcwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADkALgAxAC4AMQAgACgAMQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABfAFIAXAAiACwAIABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSAFwAIgAsACAAXAAiAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAZQBxAHUAYQB0AGkAbwBuACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIAB0AG8AIABDAE8AMgAtAGUAIAB1AHMAaQBuAGcAIAB0AGgAZQAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABcAHUAMAAwADIANwBzACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIAAoAEcAVwBQACkALgBcACIAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAVABhAGIAbABlACAAMgAzACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAQQBwAHAAZQBuAGQAaQB4ACAAMgAgAC0AIABUAGEAYgBsAGUAIAAyADMAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMAOQAsACAANQAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAGgAZQBtAGkAYwBhAGwAIABmAG8AcgBtAHUAbABhAFwAIgAsACAAXAAiAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAKABBAFIANQApAFwAIgAsACAAXAAiAEcAYQBzACAALQAgAEYAQwAgAG4AYQBtAGUAXAAiACwAIABcACIAQQBkAGkAdABpAG8AbgBhAGwAIABkAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlAFwAIgAsACAAXAAiAEMATwAyAFwAIgAsACAAMQAsACAAXAAiAEMATwAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAQwBIADQAXAAiACwAIAAyADgALAAgAFwAIgBDAEgANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlAFwAIgAsACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUALAAgAFwAIgBOADIATwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAbABwAGgAdQByACAAaABlAHgAYQBmAGwAdQBvAHIAaQBkAGUAXAAiACwAIABcACIAUwBGADYAXAAiACwAIAAyADMANQAwADAALAAgAFwAIgBTAEYANgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMwAgACgAUgAtADIAMwApAFwAIgAsACAAXAAiAEMASABGADMAXAAiACwAIAAgADEAMgA0ADAAMAAsACAAXAAiAEgARgBDAC0AMgAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMwAyACAAKABSAC0AMwAyACkAXAAiACwAIABcACIAQwBIADIARgAyAFwAIgAsACAANgA3ADcALAAgAFwAIgBIAEYAQwAtADMAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADQAMQAgACgAUgAtADQAMQApAFwAIgAsACAAXAAiAEMASAAzAEYAXAAiACwAIAAgADEAMQA2ACwAIABcACIASABGAEMALQA0ADEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQA0ADMALQAxADAAbQBlAGUAIAAoAFIALQA0ADMAMQAwAG0AZQBlACkAXAAiACwAIABcACIAQwA1AEgAMgBGADEAMABcACIALAAgADEANgA1ADAALAAgAFwAIgBIAEYAQwAtADQAMwAtADEAMABtAGUAZQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMgA1ACAAKABSAC0AMQAyADUAKQBcACIALAAgAFwAIgBDADIASABGADUAXAAiACwAIAAgADMAMQA3ADAALAAgAFwAIgBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAzADQAIAAoAFIALQAxADMANAApAFwAIgAsACAAXAAiAEMAMgBIADIARgA0ACAAKABDAEgARgAyAEMASABGADIAKQBcACIALAAgACAAMQAxADIAMAAsACAAXAAiAEgARgBDAC0AMQAzADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADMANABhACAAKABSAC0AMQAzADQAYQApAFwAIgAsACAAXAAiAEMAMgBIADIARgA0ACAAKABDAEgAMgBGAEMARgAzACkAXAAiACwAIAAxADMAMAAwACwAIABcACIASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA0ADMAIAAoAFIALQAxADQAMwApAFwAIgAsACAAXAAiAEMAMgBIADMARgAzACAAKABDAEgARgAyAEMASAAyAEYAKQBcACIALAAgADMAMgA4ACwAIABcACIASABGAEMALQAxADQAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEANAAzAGEAIAAoAFIALQAxADQAMwBhACkAXAAiACwAIABcACIAQwAyAEgAMwBGADMAIAAoAEMARgAzAEMASAAzACkAXAAiACwAIAA0ADgAMAAwACwAIABcACIASABGAEMALQAxADQAMwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA1ADIAYQAgACgAUgAtADEANQAyAGEAKQBcACIALAAgAFwAIgBDADIASAA0AEYAMgAgACgAQwBIADMAQwBIAEYAMgApAFwAIgAsACAAMQAzADgALAAgAFwAIgBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADIANwBlAGEAIAAoAFIALQAyADIANwBlAGEAKQBcACIALAAgAFwAIgBDADMASABGADcAXAAiACwAIAAzADMANQAwACwAIABcACIASABGAEMALQAyADIANwBlAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADMANgBmAGEAIAAoAFIALQAyADMANgBmAGEAKQBcACIALAAgAFwAIgBDADMASAAyAEYANgBcACIALAAgADgAMAA2ADAALAAgAFwAIgBIAEYAQwAtADIAMwA2AGYAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIANAA1AGMAYQAgACgAUgAtADIANAA1AGMAYQApAFwAIgAsACAAXAAiAEMAMwBIADMARgA1AFwAIgAsACAANwAxADYALAAgAFwAIgBIAEYAQwAtADIANAA1AGMAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIANAA1AGYAYQAgACgAUgAtADIANAA1AGYAYQApAFwAIgAsACAAXAAiAEMASABGADIAQwBIADIAQwBGADMAXAAiACwAIAA4ADUAOAAsACAAXAAiAEgARgBDAC0AMgA0ADUAZgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMwA2ADUAbQBmAGMAIAAoAFIALQAzADYANQBtAGYAYwApAFwAIgAsACAAXAAiAEMASAAzAEMARgAyAEMASAAyAEMARgAzAFwAIgAsACAAOAAwADQALAAgAFwAIgBIAEYAQwAtADMANgA1AG0AZgBjAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIAIAAoAFIALQAyADIAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAMgBcACIALAAgADEANwA2ADAALAAgAFwAIgBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADIAMwAgACgAUgAtADEAMgAzACkAXAAiACwAIABcACIAQwBIAEMAbAAyADIAQwBGADMAXAAiACwAIAA3ADkALAAgAFwAIgBIAEMARgBDAC0AMQAyADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEAMgA0ACAAKABSAC0AMQAyADQAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAQwBGADMAXAAiACwAIAA1ADIANwAsACAAXAAiAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQA0ADEAYgAgACgAUgAtADEANAAxAGIAKQBcACIALAAgAFwAIgBDAEgAMwBDAEMAbAAyAEYAXAAiACwAIAA3ADgAMgAsACAAXAAiAEgAQwBGAEMALQAxADQAMQBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADQAMgBiACAAKABSAC0AMQA0ADIAYgApAFwAIgAsACAAXAAiAEMASAAyAEMAQwBsAEYAMgBcACIALAAgADEAOQA4ADAALAAgAFwAIgBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBhACAAKABSAC0AMgAyADUAYwBhACkAXAAiACwAIABcACIAQwBIAEMAbAAyAEMARgAyAEMARgAzAFwAIgAsACAAMQAyADcALAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGIAIAAoAFIALQAyADIANQBjAGIAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAQwBGADIAQwBDAEkARgAyAFwAIgAsACAANQAyADUALAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMQA0ACAAUABlAHIAZgBsAHUAbwByAG8AbQBlAHQAaABhAG4AZQAgACgAdABlAHQAcgBhAGYAbAB1AG8AcgBvAG0AZQB0AGgAYQBuAGUAKQBcACIALAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAALAAgAFwAIgBQAEYAQwAtADEANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADEAMQA2ACAAUABlAHIAZgBsAHUAbwByAG8AZQB0AGgAYQBuAGUAIAAoAGgAZQB4AGEAZgBsAHUAbwByAG8AZQB0AGgAYQBuAGUAKQBcACIALAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAxADEAMAAwACwAIABcACIAUABGAEMALQAxADEANgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADIAMQA4ACAAUABlAHIAZgBsAHUAbwByAG8AcAByAG8AcABhAG4AZQBcACIALAAgAFwAIgBDADMARgA4AFwAIgAsACAAOAA5ADAAMAAsACAAXAAiAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAzADEALQAxADAAIABQAGUAcgBmAGwAdQBvAHIAbwBiAHUAdABhAG4AZQBcACIALAAgAFwAIgBDADQARgAxADAAXAAiACwAIAA5ADIAMAAwACwAIABcACIAUABGAEMALQAzADEALQAxADAAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAzADEAOAAgAFAAZQByAGYAbAB1AG8AcgBvAGMAeQBjAGwAbwBiAHUAdABhAG4AZQBcACIALAAgAFwAIgBjAC0AQwA0AEYAOABcACIALAAgADkANQA0ADAALAAgAFwAIgBQAEYAQwAtADMAMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0ANAAxAC0AMQAyACAAUABlAHIAZgBsAHUAbwByAG8AcABlAG4AdABhAG4AZQBcACIALAAgAFwAIgBDADUARgAxADIAXAAiACwAIAA4ADUANQAwACwAIABcACIAUABGAEMALQA0ADEALQAxADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA1ADEALQAxADQAIABQAGUAcgBmAGwAdQBvAHIAbwBoAGUAeABhAG4AZQBcACIALAAgAFwAIgBDADYARgAxADQAXAAiACwAIAA3ADkAMQAwACwAIABcACIAUABGAEMALQA1ADEALQAxADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA5ADEALQAxADgAIABQAGUAcgBmAGwAdQBuAGEAZgBlAG4AZQBcACIALAAgAFwAIgBDADEAMABGADEAOABcACIALAAgADcAMQA5ADAALAAgAFwAIgBQAEYAQwAtADkAMQAtADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMgBcACIALAAgAFwAIgBDAEMAbAAyAEYAMgBcACIALAAgADEAMAAyADAAMAAsACAAXAAiAEMARgBDAC0AMQAyAFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADMAXAAiACwAIABcACIAQwBDAGwARgAzAFwAIgAsACAAMQAzADkAMAAwACwAIABcACIAQwBGAEMALQAxADMAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAEMAQwBsAEYAMgBDAEMAbABGADIAXAAiACwAIAA4ADUAOQAwACwAIABcACIAQwBGAEMALQAxADEANABcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAQwBDAGwARgAyAEMARgAzAFwAIgAsACAANwA2ADcAMAAsACAAXAAiAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcARwBBAFMAIAAtACAARgBDACAAbgBhAG0AZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAHQAcgB1AG4AYwBhAHQAZQBkACAAZwBhAHMAIABuAGEAbQBlACAAdABvACAAYQBsAGwAbwB3ACAAbQBhAHQAYwBoAGkAbgBnACAAdwBpAHQAaAAgAG8AdABoAGUAcgAgAHQAYQBiAGwAZQBzAC4AIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABnAGEAcwBlAHMAIABmAHIAbwBtACAASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQAuACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAQQBkAGQAaQB0AGkAbwBuAGEAbAAgAGQAYQB0AGEAIABzAG8AdQByAGMAZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAC4AXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAQgBsAGUAbgBkAGUAZAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAbABlAG4AZABlAGQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAcwAgACgAbQBhAG4AeQAgAGMAbwBuAHQAYQBpAG4AaQBuAGcAIABIAEYAQwBTACAAYQBuAGQALwBvAHIAIABQAEYAQwBTACkAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABBAHAAcABlAG4AZABpAHgAIAAyACAALQAgAFQAYQBiAGwAZQAgADIANABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAxACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABlAG4AZABcACIALAAgAFwAIgBDAG8AbgBzAHQAaQB0AHUAZQBuAHQAcwBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwBpAHQAaQBvAG4AIAAoACUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAFIALQA0ADAAMAAgAGMAYQBuACAAaABhAHYAZQAgAHYAYQByAGkAbwB1AHMAIABwAHIAbwBwAG8AcgB0AGkAbwBuAHMAIABvAGYAIABDAEYAQwAtADEAMgAgAGEAbgBkACAAQwBGAEMALQAxADEANAAuACAAVABoAGUAIABlAHgAYQBjAHQAIABjAG8AbQBwAG8AcwBpAHQAaQBvAG4AIABuAGUAZQBkAHMAIAB0AG8AIABiAGUAIABzAHAAZQBjAGkAZgBpAGUAZAAsACAAZQAuAGcALgAsACAAUgAtADQAMAAwACAAKAA2ADAALwA0ADAAKQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAA1ADMALgAwAC8AMQAzAC4AMAAvADMANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgANgAxAC4AMAAvADEAMQAuADAALwAyADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEMAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADMAMwAuADAALwAxADUALgAwAC8ANQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA2ADAALgAwAC8AMgAuADAALwAzADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAyAEIAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADMAOAAuADAALwAyAC4AMAAvADYAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADMAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANQAuADAALwA3ADUALgAwAC8AMgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMwBCAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA1AC4AMAAvADUANgAuADAALwAzADkALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA0AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADQANAAuADAALwA1ADIALgAwAC8ANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADUAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AIABIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQA0ADIAYgAvAFAARgBDAC0AMwAxADgAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANwAuADAALwA1AC4ANQAvADQAMgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADYAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQA1AC4AMAAvADEANAAuADAALwA0ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAwAC4AMAAvADQAMAAuADAALwA0ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEIAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQAwAC4AMAAvADcAMAAuADAALwAyADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEMAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAzAC4AMAAvADIANQAuADAALwA1ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEQAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQA1AC4AMAAvADEANQAuADAALwA3ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEUAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgA1AC4AMAAvADEANQAuADAALwA2ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA4AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA3AC4AMAAvADQANgAuADAALwA0ADcALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgAwAC4AMAAvADIANQAuADAALwAxADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgA1AC4AMAAvADIANQAuADAALwAxADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAwAEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiACgANQAwAC4AMAAvADUAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADAAQgBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANQA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBBAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMQAuADUALwA4ADcALgA1AC8AMQAxAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBCAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMwAuADAALwA5ADQALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADEAQwBcACIALAAgAFwAIgBIAEMALQAxADIANwAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADMALgAwAC8AOQA1AC4ANQAvADEALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAyAEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADcAMAAuADAALwA1AC4AMAAvADIANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADMAQQBcACIALAAgAFwAIgBQAEYAQwAtADIAMQA4AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADkALgAwAC8AOAA4AC4AMAAvADMALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMQAuADAALwAyADgALgA1AC8ANAAuADAALwAxADYALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMAAuADAALwAzADkALgAwAC8AMQAuADUALwA5AC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA4ADIALgAwAC8AMQA4AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAyADUALgAwAC8ANwA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAFwAIgAsACAAXAAiACgANQA5AC4AMAAvADMAOQAuADUALwAxAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABcACIALAAgAFwAIgAoADQANgAuADYALwA1ADAALgAwAC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADgAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAxAC4ANQAvADkANgAuADAALwAyAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAOQBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEUALQBFADEANwAwAFwAIgAsACAAXAAiACgANwA3AC4AMAAvADEAOQAuADAALwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMABBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgAOAA4AC4AMAAvADEAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADEAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgANQA4AC4AMAAvADQAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgANQAuADEALwAxADEALgA1AC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQgBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADUANQAuADAALwA0ADIALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQwBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgAMgAuADAALwAxADUALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA3ADMALgA4AC8AMgA2AC4AMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADIAXAAiACwAIABcACIAKAA3ADUALgAwAC8AMgA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADEANQBcACIALAAgAFwAIgAoADQAOAAuADgALwA1ADEALgAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAzAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AQwBGAEMALQAxADMAXAAiACwAIABcACIAKAA0ADAALgAxAC8ANQA5AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANABcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAKAA0ADgALgAyAC8ANQAxAC4AOAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANQBcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEgAQwBGAEMALQAzADEAXAAiACwAIABcACIAKAA3ADgALgAwAC8AMgAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANgBcACIALAAgAFwAIgBDAEYAQwAtADMAMQAvAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAKAA1ADUALgAxAC8ANAA0AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEANAAzAGEAXAAiACwAIABcACIAKAA1ADAALgAwAC8ANQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOABBAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AUABGAEMALQAxADEANgBcACIALAAgAFwAIgAoADMAOQAuADAALwA2ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA4AEIAXAAiACwAIABcACIASABGAEMALQAyADMALwBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiACgANAA2AC4AMAAvADUANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADkAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADQANAAuADAALwA1ADYALgAwACkAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAYwBoAGEAbgBnAGUAZAAgAEgAQwA2ADAAMABhACAAdABvACAASABDAC0ANgAwADAAYQAgAGYAbwByACAAYgBsAGUAbgBkACAAUgAtADQAMQA0AEIALgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABmAG8AcgAgAGIAbABlAG4AZAAgAFIALQA0ADAANQBBACAALQAgAEMAaABhAG4AZwBlAGQAIABIAEMARgBDADEANAAyAGIAIAB0AG8AIABIAEMARgBDAC0AMQA0ADIAYgAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEwAZQBhAGsAYQBnAGUAIAByAGEAdABlAHMAIABmAG8AcgAgAGMAbwBtAG0AbwBuACAAcgBlAGYAcgBpAGcAZQByAGEAdABpAG8AbgAgAGEAbgBkACAAYQBpAHIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAGMAYQB0AGkAdgBlACAAbABlAGEAawBhAGcAZQAgAHIAYQB0AGUAcwAgAGYAbwByACAAYwBvAG0AbQBvAG4AIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuACAAYQBuAGQAIABhAGkAcgAgAC0AIABjAG8AbgBkAGkAdABpAG8AbgBpAG4AZwAgAGUAcQB1AGkAcABtAGUAbgB0AFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADEAMABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ADEALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAGwAZQBhAGsAYQBnAGUAIAByAGEAdABlACAAKAAlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAcgBlAGYAcgBpAGcAZQByAGEAdABvAHIAcwBcACIALAAgADEALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuAFwAIgAsACAAMQA1AC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcABvAHIAdABhAGIAbABlAFwAIgAsACAAMgAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHMAcABsAGkAdABcACIALAAgADMALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABwAGEAYwBrAGEAZwBlAGQAXAAiACwAIAAyAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAHYAZQBoAGkAYwBsAGUAIABBAC8AQwBcACIALAAgADYALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAdgBlAGgAaQBjAGwAZQAgAEEALwBDAFwAIgAsACAAMQAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBhAGwAYwB1AGwAYQB0AGUAQgBsAGUAbgBkAEcAVwBQAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMQAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMgAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMwAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAANAAsAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAxACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAyACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAzACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAA0ACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0ACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGEAbABjAHUAbABhAHQAZQBCAGwAZQBuAGQARwBXAFAAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
@@ -19217,6 +19324,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19233,20 +19356,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/9_Refrigerants_WIP_v02.xlsx
+++ b/Excel/9_Refrigerants_WIP_v02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139887C6-196F-4183-9A8B-C7801FE3CC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61542CE-DF03-417F-BFF6-634CD64C7B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="255" windowWidth="37335" windowHeight="19740" firstSheet="2" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -315,6 +315,8 @@
     <definedName name="Step1">#REF!</definedName>
     <definedName name="Step2">#REF!</definedName>
     <definedName name="Step3">#REF!</definedName>
+    <definedName name="Table_E_CO2e">'9.1.1.1-2 Refrigerant use'!$D$61:$G$71</definedName>
+    <definedName name="Table_E_R">'9.1.1.1-2 Refrigerant use'!$D$35:$E$39</definedName>
     <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend1_Name_Method1">'9.1.1.1-2 Refrigerant use'!$D$36</definedName>
     <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend1_Value_Method1">'9.1.1.1-2 Refrigerant use'!$E$36</definedName>
     <definedName name="VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend10_Name_Method1">'9.1.1.1-2 Refrigerant use'!$D$45</definedName>
@@ -1985,7 +1987,7 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="17" xfId="15" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="56" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="56" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="14">
@@ -5934,7 +5936,7 @@
         <v>151</v>
       </c>
       <c r="E9" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!E36</f>
+        <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend1_Value_Method1</f>
         <v>8.5000000000000006E-4</v>
       </c>
       <c r="F9" s="59">
@@ -5946,7 +5948,7 @@
         <v>t R-402A</v>
       </c>
       <c r="H9" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!G62</f>
+        <f>INDEX(Table_E_CO2e,2,4)</f>
         <v>1.1860424000000003</v>
       </c>
       <c r="I9" s="59">
@@ -5966,7 +5968,7 @@
       <c r="C10" s="17"/>
       <c r="D10" s="1"/>
       <c r="E10" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!E37</f>
+        <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend2_Value_Method1</f>
         <v>1.7500000000000003E-3</v>
       </c>
       <c r="F10" s="59">
@@ -5978,7 +5980,7 @@
         <v>t R-422B</v>
       </c>
       <c r="H10" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!G63</f>
+        <f>INDEX(Table_E_CO2e,3,4)</f>
         <v>2.0794287500000004</v>
       </c>
       <c r="I10" s="59">
@@ -5999,7 +6001,7 @@
       <c r="C11" s="17"/>
       <c r="D11" s="1"/>
       <c r="E11" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!E38</f>
+        <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend3_Value_Method1</f>
         <v>1.2210000000000002E-2</v>
       </c>
       <c r="F11" s="59">
@@ -6011,7 +6013,7 @@
         <v>t R-400 60/40</v>
       </c>
       <c r="H11" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!G64</f>
+        <f>INDEX(Table_E_CO2e,4,4)</f>
         <v>70.007256000000027</v>
       </c>
       <c r="I11" s="59">
@@ -6029,7 +6031,7 @@
       <c r="C12" s="17"/>
       <c r="D12" s="1"/>
       <c r="E12" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!E39</f>
+        <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend4_Value_Method1</f>
         <v>1.5699999999999999E-2</v>
       </c>
       <c r="F12" s="59">
@@ -6041,7 +6043,7 @@
         <v>t R-504</v>
       </c>
       <c r="H12" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!G65</f>
+        <f>INDEX(Table_E_CO2e,5,4)</f>
         <v>34.780656319599998</v>
       </c>
       <c r="I12" s="59">
@@ -6061,7 +6063,7 @@
       <c r="C13" s="17"/>
       <c r="D13" s="1"/>
       <c r="E13" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!E40</f>
+        <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend5_Value_Method1</f>
         <v>0</v>
       </c>
       <c r="F13" s="59">
@@ -6073,7 +6075,7 @@
         <v/>
       </c>
       <c r="H13" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!G66</f>
+        <f>INDEX(Table_E_CO2e,6,4)</f>
         <v>0</v>
       </c>
       <c r="I13" s="59">
@@ -6094,7 +6096,7 @@
       <c r="C14" s="17"/>
       <c r="D14" s="1"/>
       <c r="E14" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!E41</f>
+        <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend6_Value_Method1</f>
         <v>0</v>
       </c>
       <c r="F14" s="59">
@@ -6106,7 +6108,7 @@
         <v/>
       </c>
       <c r="H14" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!G67</f>
+        <f>INDEX(Table_E_CO2e,7,4)</f>
         <v>0</v>
       </c>
       <c r="I14" s="59">
@@ -6127,7 +6129,7 @@
       <c r="C15" s="17"/>
       <c r="D15" s="1"/>
       <c r="E15" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!E42</f>
+        <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend7_Value_Method1</f>
         <v>0</v>
       </c>
       <c r="F15" s="59">
@@ -6139,7 +6141,7 @@
         <v/>
       </c>
       <c r="H15" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!G68</f>
+        <f>INDEX(Table_E_CO2e,8,4)</f>
         <v>0</v>
       </c>
       <c r="I15" s="59">
@@ -6156,7 +6158,7 @@
       <c r="C16" s="17"/>
       <c r="D16" s="1"/>
       <c r="E16" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!E43</f>
+        <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend8_Value_Method1</f>
         <v>0</v>
       </c>
       <c r="F16" s="59">
@@ -6168,7 +6170,7 @@
         <v/>
       </c>
       <c r="H16" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!G69</f>
+        <f>INDEX(Table_E_CO2e,9,4)</f>
         <v>0</v>
       </c>
       <c r="I16" s="59">
@@ -6185,7 +6187,7 @@
       <c r="C17" s="17"/>
       <c r="D17" s="1"/>
       <c r="E17" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!E44</f>
+        <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend9_Value_Method1</f>
         <v>0</v>
       </c>
       <c r="F17" s="59">
@@ -6197,7 +6199,7 @@
         <v/>
       </c>
       <c r="H17" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!G70</f>
+        <f>INDEX(Table_E_CO2e,10,4)</f>
         <v>0</v>
       </c>
       <c r="I17" s="59">
@@ -6214,7 +6216,7 @@
       <c r="C18" s="17"/>
       <c r="D18" s="1"/>
       <c r="E18" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!E45</f>
+        <f>VEERG_9_1_1__1_RefrigerantLeaking_Result_Blend10_Value_Method1</f>
         <v>0</v>
       </c>
       <c r="F18" s="59">
@@ -6226,7 +6228,7 @@
         <v/>
       </c>
       <c r="H18" s="59">
-        <f>'9.1.1.1-2 Refrigerant use'!G71</f>
+        <f>INDEX(Table_E_CO2e,11,4)</f>
         <v>0</v>
       </c>
       <c r="I18" s="59">

--- a/Excel/9_Refrigerants_WIP_v02.xlsx
+++ b/Excel/9_Refrigerants_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61542CE-DF03-417F-BFF6-634CD64C7B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AF8F28-DB31-432A-B634-7CF1D5926875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" firstSheet="2" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -177,6 +177,7 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Fertiliser type f","FracGASFf","Basis";"Urea-based fertilisers",0.15,"Urea";"Ammonium-based fertilisers",0.08,"Ammonium";"Nitrate-based fertilisers",0.01,"Nitrate";"Ammonium-nitrate based fertilisers",0.05,"Ammonium-nitrate";"Other fertilisers",0.11,"Other"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4 Table 11.3 [1, p. 11]")</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Source">_xlfn.LAMBDA("VEERG 2026:Table 12.2.2.9")</definedName>
@@ -19096,6 +19097,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwAgAGkAbgBjAGwAdQBkAGkAbgBnACAAbABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIAAgAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADkALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMgAsACAAMAAuADAAMwAsACAANQAxAC4ANgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAGEAbAAgAG0AaQBuAGUAIAB3AGEAcwB0AGUAIABnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADkALAAgADQALgA2ACwAIAAwAC4AMwAsACAANQA2AC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAKAByAGUAdgBlAHIAdABpAG4AZwAgAHQAbwAgAHMAdABhAG4AZABhAHIAZAAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAKQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBwAHIAbwBjAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAANgAyADkALAAgAFwAIgBtADMAXAAiACwAIAA1ADYALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMAAzACwAIAA1ADYALgA1ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AawBlACAAbwB2AGUAbgAgAGcAYQBzAFwAIgAsACAAMAAuADAAMQA4ADEALAAgAFwAIgBtADMAXAAiACwAIAAzADcALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAA1ACwAIAAzADcALgAwADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGwAYQBzAHQAIABmAHUAcgBuAGEAYwBlACAAZwBhAHMAXAAiACwAIAAwAC4AMAAwADQAMAAsACAAXAAiAG0AMwBcACIALAAgADIAMwA0AC4AMAAsACAAMAAuADAAMwAsACAAMAAuADAAMgAsACAAMgAzADQALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMAAsACAAXAAiAG0AMwBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsATABcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBlAG8AdQBzACAAZgBvAHMAcwBpAGwAIABmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAYQBuAGQAZgBpAGwAbAAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIAAoAG0AZQB0AGgAYQBuAGUAIABvAG4AbAB5ACkAXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4ALAAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA3ADAALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBtAGUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAwADMALAAgADAALgAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAHkAZAByAG8AZwBlAG4AXAAiACwAIAAwAC4AMAAxADIAMgAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMAAsACAAMAAuADUALAAgADAALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgADEALAAgAFwAIgBHAEoAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAzACwAIAA2ADAALgAyADcAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABcAHUAMAAwADIANwBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAdQAwADAAMgA3ACAAdwBlAHIAZQAgAGEAZABkAGUAZAAsACAAZQBhAGMAaAAgAHcAaQB0AGgAIABhAG4AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgADEAIABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAC4AIABUAGgAaQBzACAAaQBzACAAZgBvAHIAIAB1AHMAZQByAHMAIAB3AGgAbwAgAGgAYQB2AGUAIABmAHUAZQBsACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAZABhAHQAYQAgAGkAbgAgAEcASgAgAHIAYQB0AGgAZQByACAAdABoAGEAbgAgAG0AMwAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAuAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABOAGEAdAB1AHIAYQBsACAARwBhAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABNAGUAdAByAG8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AbwBuACAALQAgAE0AZQB0AHIAbwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAOAAuADgALAAgADcALgA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAAxADAALgA3ACwAIAAxADAALgA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAANAAuADEALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAANAAuADAALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIAA0AC4AMQAsACAANAAuADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABOAFMAVwAgAGEAbgBkACAAQQBDAFQAIABzAHAAbABpAHQAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAcgBvAHcAcwAuACAAXAB1ADAAMAAyADcAQwBcAHUAMAAwADIANwAgAFYAYQBsAHUAZQBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAcgBlAHAAbABhAGMAZQBkACAAdwBpAHQAaAAgAHQAaABvAHMAZQAgAGYAbwByACAAVgBpAGMAdABvAHIAaQBhACAAYQBuAGQAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAByAGUAcwBwAGUAYwB0AGkAdgBlAGwAeQAuACAAKABTAGUAZQAgAGEAcABwAGUAbgBkAGkAYwBlAHMAKQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADIALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBBAHMAIABTAGMAbwBwAGUAIAAzACAAZgBhAGMAdABvAHIAcwAgAGEAcgBlACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGEAdAAgAHQAaABlACAAcABvAGkAbgB0ACAAdwBoAGUAcgBlACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAaQBzACAAZABlAGwAaQB2AGUAcgBlAGQAIAB0AG8AIABlAG4AZAAgAHUAcwBlAHIAcwAsACAAaQB0ACAAaQBzACAAbgBlAGMAZQBzAHMAYQByAHkAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAdAAgAGUAYQBjAGgAIABvAGYAIAB0AGgAZQAgAGwAbwBhAGQAIABjAGUAbgB0AHIAZQBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIARwBhAHMAIAByAGUAYQBjAGgAZQBzACAAZQBuAGQAIAB1AHMAZQByAHMAIABlAGkAdABoAGUAcgAgAGYAcgBvAG0AIAB0AGgAZQAgAG0AZQB0AHIAbwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAbgBlAHQAdwBvAHIAawBzACAAbwByACAAZABpAHIAZQBjAHQAIABmAHIAbwBtACAAdABoAGUAIABoAGkAZwBoACAALQAgAHAAcgBlAHMAcwB1AHIAZQAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBIAG8AdQBzAGUAaABvAGwAZABzACAAYQBuAGQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdQBzAGUAcgBzACAAdABlAG4AZAAgAHQAbwAgAGIAZQAgAHMAZQByAHYAZQBkACAAYgB5ACAAdABoAGUAIABmAG8AcgBtAGUAcgAsACAAYQBuAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABnAGUAbgBlAHIAYQB0AG8AcgBzACAAYQBuAGQAIABsAGEAcgBnAGUAIABpAG4AZAB1AHMAdAByAGkAYQBsACAAcABsAGEAbgB0AHMAIABmAHIAbwBtACAAdABoAGUAIABsAGEAdAB0AGUAcgAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIATQBlAHQAcgBvACAAaQBzACAAZABlAGYAaQBuAGUAZAAgAGEAcwAgAGwAbwBjAGEAdABlAGQAIABvAG4AIABvAHIAIABlAGEAcwB0ACAAbwBmACAAdABoAGUAIABkAGkAdgBpAGQAaQBuAGcAIAByAGEAbgBnAGUAIABpAG4AIABOAFMAVwAsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABDAGEAbgBiAGUAcgByAGEAIABhAG4AZAAgAFEAdQBlAGEAbgBiAGUAeQBhAG4ALAAgAE0AZQBsAGIAbwB1AHIAbgBlACwAIABCAHIAaQBzAGIAYQBuAGUALAAgAEEAZABlAGwAYQBpAGQAZQAgAG8AcgAgAFAAZQByAHQAaAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAE8AdABoAGUAcgB3AGkAcwBlACwAIAB0AGgAZQAgAG4AbwBuACAALQAgAG0AZQB0AHIAbwAgAGYAYQBjAHQAbwByACAAcwBoAG8AdQBsAGQAIABiAGUAIAB1AHMAZQBkAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBGAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABhAGwAbAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAB3AGgAaQBjAGgAIABtAGEAeQAgAGkAbgBjAGwAdQBkAGUAIABjAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFQAYQBiAGwAZQAgADYAIABpAHMAIABuAG8AdAAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIAB0AG8AIABlAHQAaABhAG4AZQAuACAAUwBlAGUAIABUAGEAYgBsAGUAIAA3ACAASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGUAdABoAGEAbgBlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBDACAAPQAgAEMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAC4AIABTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAVABhAHMAbQBhAG4AaQBhACAAYQBuAGQAIAB0AGgAZQAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAYQByAGUAIABuAG8AdAAgAGEAdgBhAGkAbABhAGIAbABlACAAZAB1AGUAIAB0AG8AIABjAG8AbgBmAGkAZABlAG4AdABpAGEAbABpAHQAeQAgAGMAbwBuAHMAdAByAGEAaQBuAHQAcwAgAHQAaABhAHQAIABhAHIAaQBzAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABhACAAbABpAG0AaQB0AGUAZAAgAG4AdQBtAGIAZQByACAAbwBmACAATgBHAEUAUgAgAGQAYQB0AGEAIABpAG4AcAB1AHQAcwAuACAASQB0ACAAaQBzACAAcwB1AGcAZwBlAHMAdABlAGQAIAB0AGgAYQB0ACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABWAGkAYwB0AG8AcgBpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgB3AGgAaQBsAGUAIABmAG8AcgAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHQAaABlACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAaQBzACAAYQBwAHAAcgBvAHAAcgBpAGEAdABlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGQAbwAgAG4AbwB0ACAAaQBuAGMAbAB1AGQAZQAgAGYAdQBnAGkAdABpAHYAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGwAZQBhAGsAYQBnAGUAIABmAHIAbwBtACAAbABvAHcAIABwAHIAZQBzAHMAdQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABpAG8AbgAgAHAAaQBwAGUAbABpAG4AZQAgAG4AZQB0AHcAbwByAGsAcwAgAHcAaABpAGwAZQAgAHQAaABvAHMAZQAgAGYAcgBvAG0AIABoAGkAZwBoACAAcAByAGUAcwBzAHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAGcAYQBzACAAbgBlAHQAdwBvAHIAawBzACAAYQByAGUAIABjAG8AbgBzAGkAZABlAHIAZQBkACAAbgBlAGcAbABpAGcAaQBiAGwAZQAuAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGEAbgBkACAAaQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAZQByAHQAYQBpAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgA1ACwAIAA4ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABjAG8AbQBiAHUAcwB0AGUAZABcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAEMAbwBuAHQAZQBuAHQAIABGAGEAYwB0AG8AcgAgACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbABzACAAKABvAHQAaABlAHIAIAB0AGgAYQBuACAAcABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbAAgAHUAcwBlAGQAIABhAHMAIABmAHUAZQBsACkALAAgAGUALgBnAC4AIABsAHUAYgByAGkAYwBhAG4AdABzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADEAMwAuADkALAAgADAALgAwACwAIAAwAC4AMAAsACAAMQAzAC4AOQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAZwByAGUAYQBzAGUAcwBcACIALAAgADMAOAAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAzAC4ANQAsACAAMAAuADAALAAgADAALgAwACwAIAAzAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAcgB1AGQAZQAgAG8AaQBsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABjAHIAdQBkAGUAIABvAGkAbAAgAGMAbwBuAGQAZQBuAHMAYQB0AGUAcwBcACIALAAgADQANQAuADMALAAgAFwAIgB0AFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADYAOQAuADgAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABsAGkAcQB1AGkAZABzAFwAIgAsACAANAA2AC4ANQAsACAAXAAiAHQAXAAiACwAIAA2ADEALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgAxAC4AMgA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdQB0AG8AbQBvAHQAaQB2AGUAIABnAGEAcwBvAGwAaQBuAGUAIAAvACAAcABlAHQAcgBvAGwAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADAALgAyACwAIAAwAC4AMgAsACAANgA3AC4AOAAwACwAIAAxADcALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuACAAZwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsATABcACIALAAgADYANwAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA0ADAALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBLAGUAcgBvAHMAZQBuAGUAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA3AC4ANQAsACAAXAAiAGsATABcACIALAAgADYAOAAuADkALAAgADAALgAwADEALAAgADAALgAyACwAIAA2ADkALgAxADEALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIAB0AHUAcgBiAGkAbgBlACAAZgB1AGUAbAAgAC8AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYAOQAuADgAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHQAaQBuAGcAIABvAGkAbABcACIALAAgADMANwAuADMALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4ANwAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADcAMAAuADIAMAAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA0ACwAIAAwAC4AMgAsACAANwAzAC4AOAA0ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABhAHIAbwBtAGEAdABpAGMAIABoAHkAZAByAG8AYwBhAHIAYgBvAG4AcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAdgBlAG4AdABzADoAIABtAGkAbgBlAHIAYQBsACAAdAB1AHIAcABlAG4AdABpAG4AZQAgAG8AcgAgAHcAaABpAHQAZQAgAHMAcABpAHIAaQB0AHMAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADIALAAgADYAOQAuADkAMwAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYAMAAuADYAMAAsACAAMgAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQBwAGgAdABoAGEAXAAiACwAIAAzADEALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABjAG8AawBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAHQAXAAiACwAIAA5ADIALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAOQAyAC4AOAA4ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAZwBhAHMAIABhAG4AZAAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADIALgA5ACwAIABcACIAdABcACIALAAgADUANAAuADcALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANAAuADcANgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGkAbgBlAHIAeQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADgALAAgADAALgAwADIALAAgADAALgAxACwAIAA2ADkALgA5ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAG8AbAAgAGYAbwByACAAdQBzAGUAIABhAHMAIABhACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGkAbgB0AGUAcgBuAGEAbAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABlAG4AZwBpAG4AZQBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBpAG8AZgB1AGUAbABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAIABhAG4AZAAgAGIAZQBsAG8AdwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAwADIALAAgADAALgAyACwAIAAwAC4AMgAyACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADMAMAAsACAAXAAiAE4ARQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAIABpAG4AIABkAGkAZgBmAGUAcgBlAG4AdAAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADkAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADYALAAgADEAMAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAXAAiACwAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBsAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYANwAuADYAMgAsACAAMQA3AC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAANwAwAC4ANAAxACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAHAAZQB0AHIAbwBsAGUAdQBtACAAZwBhAHMAIAAoAEwAUABHACkAXAAiACwAIAAyADYALgAyACwAIABcACIAawBsAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADUALAAgADAALgAzACwAIAA2ADEALgAwADAALAAgADIAMAAuADIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAGwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4ANQAsACAANwA0AC4AMQA4ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBFAHQAaABhAG4AbwBsAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADIALAAgADAALgA0ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQgBpAG8AZABpAGUAcwBlAGwAXAAiACwAIAAzADQALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgA4ACwAIAAxAC4ANwAsACAAMgAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAAMAAuADUAMQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAE8AdABoAGUAcgAgAGIAaQBvAGYAdQBlAGwAcwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAZwBoAHQAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADcALgAzACwAIAAwAC4AMwAsACAANQA5AC4AMAAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBDAG8AbQBwAHIAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAyAC4AOAAsACAAMAAuADMALAAgADUANAAuADUALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsAbABcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADAANwAsACAAMAAuADQALAAgADcAMAAuADMANwAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADEALAAgADAALgA0ACwAIAA3ADAALgA0ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANAAsACAANwAwAC4ANQAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADcALAAgADAALgA0ACwAIAAwAC4ANAA3ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4ANAAsACAAMAAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADQALAAgADAALgA2ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdABcACIALAAgADMAMwAuADEALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgAwACwAIAAwAC4AMAA2ACwAIAAwAC4ANgAsACAANgA3AC4ANgA2ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwA2AC4AOAAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADYALAAgADAALgAwADEALAAgADAALgA2ACwAIAA3ADAALgAyADEALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA2ACwAIAAwAC4ANgAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADEAMAAuADEALAAgADAALgAzACwAIABcACIAXAAiACwAIAAxADcALgAyACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIABcACIAXAAiACwAIAAxADcALgAzACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEAOAAuADAALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAE8AZgBmAC0AcgBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAaQBuACAAbwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQAgAHEAXAAiACwAIABcACIARQBDAFQAcgBhAG4AcwAsAHEAIAAoAEcASgAvAGsATAApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAE8AMgAgAEUARgBUAHIAYQBuACwAMQAsAHQAcQBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAQwBIADQAIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAE4AMgBPACAARQBGAFQAcgBhAG4ALAAxACwAdABnAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAEYAVAByAGEAbgBzACwAMwAsAHEAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAFAAZQB0AHIAbwBsAFwAIgAsACAAMwA0AC4AMgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgADEANwAuADMAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAATABFAEYAVAAoAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQAgAC0AMQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8ARwBlAHQAUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAFMAdAByAGkAbgBnAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFIASQBHAEgAVAAoAEMAZQBsAGwALABMAEUATgAoAEMAZQBsAGwAKQAtAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8AVABvAHQAYQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBcAG4APQAgAEwAQQBNAEIARABBACgAXABuACAAIAAgACAARgB1AGUAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAsACAARgB1AGUAbABVAHMAZQAsACAARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAsACAARgB1AGUAbABUAHkAcABlACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgAFMAVQBNACgAXABuACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAXABuACAAIAAgACAAIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFQAeQBwAGUAKQAgACoAIABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABVAHMAZQBBAHIAcgBhAHkAIAA9ACAARgB1AGUAbABVAHMAZQApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIAAwAFwAbgAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgAOgAgAEYAdQBlAGwAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA4AC4AMQAgAEYAdQBlAGwAIABVAHMAZQAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsACAARQBDACwAIABFAEYALABcAG4AIAAgACAAIAAoAFEAIAAqACAARQBDACAAKgAgAEUARgApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAGMAbwBtAGIAdQBzAHQAZQBkACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAGsATABcAG4ARQBDACAAOgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwAgADoAIABrAGcAIABDAE8AMgBlACAALwAgAEcASgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AVAByAGEAbgBzAHQAcQAsACAARQBDAF8AVAByAGEAbgBzAHEALAAgAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADgALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADMAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFQAcgBhAG4AcwAsAHQAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEMAXwB7AFQAcgBhAG4AcwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBUAHIAYQBuAHMALAAxACwAdABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBUAHIAYQBuAHMAdABxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlACAALwAgAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHEAXAAiACwAIABcACIARgB1AGUAbAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAXAAiACwAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXABuAFEAIAA6ACAAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABHAEoALwBrAEwAXABuAEUARgAgADoAIABTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBTAEMAcQAsACAARQBDAF8AUwBDAHEALAAgAEUARgBfAFMAQwAxAHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgADIALgAyACAARQBzAHQAaQBtAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABlAG4AZQByAGcAeQAgAHMAbwB1AHIAYwBlAHMAIAAtACAAQwBhAGwAYwB1AGwAYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHQAIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEAXABcAGwAZQBmAHQAKABRAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAUwBDACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFMAQwAsADEALABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFMAQwBxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAdQBzAGUAZAAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAFYAYQByAGkAZQBzACAAYgBhAHMAZQBkACAAbwBuACAAZgB1AGUAbAAgAHQAeQBwAGUAOgAgAGsATAAsACAAbQAzACwAIABHAEoAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMAXwBTAEMAcQBcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFMAQwAxAHEAZwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQwBcACIALAAgAFwAIgBTAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAMQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA5ADoAIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA5AC4AMQAgAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgBUAGgAZQAgAHQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBpAG4AZwAgAGQAdQByAGkAbgBnACAAbwBwAGUAcgBhAHQAaQBvAG4AIAAoAG4AbwB0ACAAZAB1AHIAaQBuAGcAIABpAG4AcwB0AGEAbABsAGEAdABpAG8AbgAgAG8AcgAgAGQAaQBzAHAAbwBzAGEAbAApAFwAbgBHAFcAUABSACAAOgAgAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgADoAIABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBjAGgAYQByAGcAZQBfAFIAYQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIABjAG8AbgB0AGEAaQBuAGUAZAAgAGkAbgAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgADoAIABrAGcAXABuAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEAIAA6ACAAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByACAAOgAgAFAAZQByAGMAZQBuAHQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGMAaABhAHIAZwBlAF8AUgBhACwAIABsAGUAYQBrAGEAZwBlAHIAYQB0AGUAXwBhACwAXABuACAAIAAgACAAKABjAGgAYQByAGcAZQBfAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALwAxADAAMAApACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAFIALAAgAEcAVwBQAF8AUgAsAFwAbgAgACAAIAAgACgAKABFAF8AUgAgACoAIAAxADAAXgAzACkAIAAqACAARwBXAFAAXwBSACkAIAAqACAAMQAwAF4ALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGEAZwBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABjAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBSAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGcAYQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADkALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMwAuADEAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAaQBuAGQAdQBzAHQAcgBpAGEAbAAgAHAAcgBvAGMAZQBzAHMAZQBzACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAtACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBhAGcAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBjAGgAYQByAGcAZQBfAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALwAxADAAMAApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AUgAgAD0AIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGEAIABcAFwAbABlAGYAdAAoACAAYwBoAGEAcgBnAGUAXwB7AFIAYQB9ACAAXABcAHQAaQBtAGUAcwAgAFwAXABmAHIAYQBjAHsAbABlAGEAawBhAGcAZQBcAFwALAByAGEAdABlAF8AYQB9AHsAMQAwADAAfQAgAFwAXAByAGkAZwBoAHQAKQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBDAE8AMgBlACAAPQAgAFwAXABsAGUAZgB0ACgARQBfAFIAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AIABcAFwAcgBpAGcAaAB0ACkAIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwBSACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAGgAYQByAGcAZQBfAFIAYQBcACIALAAgAFwAIgBBAG0AbwB1AG4AdAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIABjAG8AbgB0AGEAaQBuAGUAZAAgAGkAbgAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBsAGUAYQBrAGEAZwBlAHIAYQB0AGUAXwBhAFwAIgAsACAAXAAiAFAAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAAdABvAHQAYQBsACAAYwBoAGEAcgBnAGUAIABsAGUAYQBrAGUAZAAgAGYAcgBvAG0AIABhAHAAcABsAGkAYQBuAGMAZQAgAGEAIABlAGEAYwBoACAAeQBlAGEAcgBcACIALAAgAFwAIgBQAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYQBcACIALAAgAFwAIgBBAHAAcABsAGkAYQBuAGMAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAFwAIgAsACAAXAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAFIAXAAiACwAIABcACIAVABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSAFwAIgAsACAAXAAiAHQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABnAGEAcwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADkALgAxAC4AMQAgACgAMQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABfAFIAXAAiACwAIABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSAFwAIgAsACAAXAAiAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAZQBxAHUAYQB0AGkAbwBuACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIAB0AG8AIABDAE8AMgAtAGUAIAB1AHMAaQBuAGcAIAB0AGgAZQAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABcAHUAMAAwADIANwBzACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIAAoAEcAVwBQACkALgBcACIAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAVABhAGIAbABlACAAMgAzACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAQQBwAHAAZQBuAGQAaQB4ACAAMgAgAC0AIABUAGEAYgBsAGUAIAAyADMAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMAOQAsACAANQAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAGgAZQBtAGkAYwBhAGwAIABmAG8AcgBtAHUAbABhAFwAIgAsACAAXAAiAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAKABBAFIANQApAFwAIgAsACAAXAAiAEcAYQBzACAALQAgAEYAQwAgAG4AYQBtAGUAXAAiACwAIABcACIAQQBkAGkAdABpAG8AbgBhAGwAIABkAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlAFwAIgAsACAAXAAiAEMATwAyAFwAIgAsACAAMQAsACAAXAAiAEMATwAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAQwBIADQAXAAiACwAIAAyADgALAAgAFwAIgBDAEgANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlAFwAIgAsACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUALAAgAFwAIgBOADIATwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAbABwAGgAdQByACAAaABlAHgAYQBmAGwAdQBvAHIAaQBkAGUAXAAiACwAIABcACIAUwBGADYAXAAiACwAIAAyADMANQAwADAALAAgAFwAIgBTAEYANgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMwAgACgAUgAtADIAMwApAFwAIgAsACAAXAAiAEMASABGADMAXAAiACwAIAAgADEAMgA0ADAAMAAsACAAXAAiAEgARgBDAC0AMgAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMwAyACAAKABSAC0AMwAyACkAXAAiACwAIABcACIAQwBIADIARgAyAFwAIgAsACAANgA3ADcALAAgAFwAIgBIAEYAQwAtADMAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADQAMQAgACgAUgAtADQAMQApAFwAIgAsACAAXAAiAEMASAAzAEYAXAAiACwAIAAgADEAMQA2ACwAIABcACIASABGAEMALQA0ADEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQA0ADMALQAxADAAbQBlAGUAIAAoAFIALQA0ADMAMQAwAG0AZQBlACkAXAAiACwAIABcACIAQwA1AEgAMgBGADEAMABcACIALAAgADEANgA1ADAALAAgAFwAIgBIAEYAQwAtADQAMwAtADEAMABtAGUAZQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMgA1ACAAKABSAC0AMQAyADUAKQBcACIALAAgAFwAIgBDADIASABGADUAXAAiACwAIAAgADMAMQA3ADAALAAgAFwAIgBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAzADQAIAAoAFIALQAxADMANAApAFwAIgAsACAAXAAiAEMAMgBIADIARgA0ACAAKABDAEgARgAyAEMASABGADIAKQBcACIALAAgACAAMQAxADIAMAAsACAAXAAiAEgARgBDAC0AMQAzADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADMANABhACAAKABSAC0AMQAzADQAYQApAFwAIgAsACAAXAAiAEMAMgBIADIARgA0ACAAKABDAEgAMgBGAEMARgAzACkAXAAiACwAIAAxADMAMAAwACwAIABcACIASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA0ADMAIAAoAFIALQAxADQAMwApAFwAIgAsACAAXAAiAEMAMgBIADMARgAzACAAKABDAEgARgAyAEMASAAyAEYAKQBcACIALAAgADMAMgA4ACwAIABcACIASABGAEMALQAxADQAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEANAAzAGEAIAAoAFIALQAxADQAMwBhACkAXAAiACwAIABcACIAQwAyAEgAMwBGADMAIAAoAEMARgAzAEMASAAzACkAXAAiACwAIAA0ADgAMAAwACwAIABcACIASABGAEMALQAxADQAMwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA1ADIAYQAgACgAUgAtADEANQAyAGEAKQBcACIALAAgAFwAIgBDADIASAA0AEYAMgAgACgAQwBIADMAQwBIAEYAMgApAFwAIgAsACAAMQAzADgALAAgAFwAIgBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADIANwBlAGEAIAAoAFIALQAyADIANwBlAGEAKQBcACIALAAgAFwAIgBDADMASABGADcAXAAiACwAIAAzADMANQAwACwAIABcACIASABGAEMALQAyADIANwBlAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADMANgBmAGEAIAAoAFIALQAyADMANgBmAGEAKQBcACIALAAgAFwAIgBDADMASAAyAEYANgBcACIALAAgADgAMAA2ADAALAAgAFwAIgBIAEYAQwAtADIAMwA2AGYAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIANAA1AGMAYQAgACgAUgAtADIANAA1AGMAYQApAFwAIgAsACAAXAAiAEMAMwBIADMARgA1AFwAIgAsACAANwAxADYALAAgAFwAIgBIAEYAQwAtADIANAA1AGMAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIANAA1AGYAYQAgACgAUgAtADIANAA1AGYAYQApAFwAIgAsACAAXAAiAEMASABGADIAQwBIADIAQwBGADMAXAAiACwAIAA4ADUAOAAsACAAXAAiAEgARgBDAC0AMgA0ADUAZgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMwA2ADUAbQBmAGMAIAAoAFIALQAzADYANQBtAGYAYwApAFwAIgAsACAAXAAiAEMASAAzAEMARgAyAEMASAAyAEMARgAzAFwAIgAsACAAOAAwADQALAAgAFwAIgBIAEYAQwAtADMANgA1AG0AZgBjAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIAIAAoAFIALQAyADIAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAMgBcACIALAAgADEANwA2ADAALAAgAFwAIgBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADIAMwAgACgAUgAtADEAMgAzACkAXAAiACwAIABcACIAQwBIAEMAbAAyADIAQwBGADMAXAAiACwAIAA3ADkALAAgAFwAIgBIAEMARgBDAC0AMQAyADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEAMgA0ACAAKABSAC0AMQAyADQAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAQwBGADMAXAAiACwAIAA1ADIANwAsACAAXAAiAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQA0ADEAYgAgACgAUgAtADEANAAxAGIAKQBcACIALAAgAFwAIgBDAEgAMwBDAEMAbAAyAEYAXAAiACwAIAA3ADgAMgAsACAAXAAiAEgAQwBGAEMALQAxADQAMQBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADQAMgBiACAAKABSAC0AMQA0ADIAYgApAFwAIgAsACAAXAAiAEMASAAyAEMAQwBsAEYAMgBcACIALAAgADEAOQA4ADAALAAgAFwAIgBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBhACAAKABSAC0AMgAyADUAYwBhACkAXAAiACwAIABcACIAQwBIAEMAbAAyAEMARgAyAEMARgAzAFwAIgAsACAAMQAyADcALAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGIAIAAoAFIALQAyADIANQBjAGIAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAQwBGADIAQwBDAEkARgAyAFwAIgAsACAANQAyADUALAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMQA0ACAAUABlAHIAZgBsAHUAbwByAG8AbQBlAHQAaABhAG4AZQAgACgAdABlAHQAcgBhAGYAbAB1AG8AcgBvAG0AZQB0AGgAYQBuAGUAKQBcACIALAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAALAAgAFwAIgBQAEYAQwAtADEANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADEAMQA2ACAAUABlAHIAZgBsAHUAbwByAG8AZQB0AGgAYQBuAGUAIAAoAGgAZQB4AGEAZgBsAHUAbwByAG8AZQB0AGgAYQBuAGUAKQBcACIALAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAxADEAMAAwACwAIABcACIAUABGAEMALQAxADEANgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADIAMQA4ACAAUABlAHIAZgBsAHUAbwByAG8AcAByAG8AcABhAG4AZQBcACIALAAgAFwAIgBDADMARgA4AFwAIgAsACAAOAA5ADAAMAAsACAAXAAiAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAzADEALQAxADAAIABQAGUAcgBmAGwAdQBvAHIAbwBiAHUAdABhAG4AZQBcACIALAAgAFwAIgBDADQARgAxADAAXAAiACwAIAA5ADIAMAAwACwAIABcACIAUABGAEMALQAzADEALQAxADAAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAzADEAOAAgAFAAZQByAGYAbAB1AG8AcgBvAGMAeQBjAGwAbwBiAHUAdABhAG4AZQBcACIALAAgAFwAIgBjAC0AQwA0AEYAOABcACIALAAgADkANQA0ADAALAAgAFwAIgBQAEYAQwAtADMAMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0ANAAxAC0AMQAyACAAUABlAHIAZgBsAHUAbwByAG8AcABlAG4AdABhAG4AZQBcACIALAAgAFwAIgBDADUARgAxADIAXAAiACwAIAA4ADUANQAwACwAIABcACIAUABGAEMALQA0ADEALQAxADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA1ADEALQAxADQAIABQAGUAcgBmAGwAdQBvAHIAbwBoAGUAeABhAG4AZQBcACIALAAgAFwAIgBDADYARgAxADQAXAAiACwAIAA3ADkAMQAwACwAIABcACIAUABGAEMALQA1ADEALQAxADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA5ADEALQAxADgAIABQAGUAcgBmAGwAdQBuAGEAZgBlAG4AZQBcACIALAAgAFwAIgBDADEAMABGADEAOABcACIALAAgADcAMQA5ADAALAAgAFwAIgBQAEYAQwAtADkAMQAtADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMgBcACIALAAgAFwAIgBDAEMAbAAyAEYAMgBcACIALAAgADEAMAAyADAAMAAsACAAXAAiAEMARgBDAC0AMQAyAFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADMAXAAiACwAIABcACIAQwBDAGwARgAzAFwAIgAsACAAMQAzADkAMAAwACwAIABcACIAQwBGAEMALQAxADMAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAEMAQwBsAEYAMgBDAEMAbABGADIAXAAiACwAIAA4ADUAOQAwACwAIABcACIAQwBGAEMALQAxADEANABcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAQwBDAGwARgAyAEMARgAzAFwAIgAsACAANwA2ADcAMAAsACAAXAAiAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcARwBBAFMAIAAtACAARgBDACAAbgBhAG0AZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAHQAcgB1AG4AYwBhAHQAZQBkACAAZwBhAHMAIABuAGEAbQBlACAAdABvACAAYQBsAGwAbwB3ACAAbQBhAHQAYwBoAGkAbgBnACAAdwBpAHQAaAAgAG8AdABoAGUAcgAgAHQAYQBiAGwAZQBzAC4AIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABnAGEAcwBlAHMAIABmAHIAbwBtACAASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQAuACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAQQBkAGQAaQB0AGkAbwBuAGEAbAAgAGQAYQB0AGEAIABzAG8AdQByAGMAZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAC4AXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAQgBsAGUAbgBkAGUAZAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAbABlAG4AZABlAGQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAcwAgACgAbQBhAG4AeQAgAGMAbwBuAHQAYQBpAG4AaQBuAGcAIABIAEYAQwBTACAAYQBuAGQALwBvAHIAIABQAEYAQwBTACkAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABBAHAAcABlAG4AZABpAHgAIAAyACAALQAgAFQAYQBiAGwAZQAgADIANABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAxACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABlAG4AZABcACIALAAgAFwAIgBDAG8AbgBzAHQAaQB0AHUAZQBuAHQAcwBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwBpAHQAaQBvAG4AIAAoACUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAFIALQA0ADAAMAAgAGMAYQBuACAAaABhAHYAZQAgAHYAYQByAGkAbwB1AHMAIABwAHIAbwBwAG8AcgB0AGkAbwBuAHMAIABvAGYAIABDAEYAQwAtADEAMgAgAGEAbgBkACAAQwBGAEMALQAxADEANAAuACAAVABoAGUAIABlAHgAYQBjAHQAIABjAG8AbQBwAG8AcwBpAHQAaQBvAG4AIABuAGUAZQBkAHMAIAB0AG8AIABiAGUAIABzAHAAZQBjAGkAZgBpAGUAZAAsACAAZQAuAGcALgAsACAAUgAtADQAMAAwACAAKAA2ADAALwA0ADAAKQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAA1ADMALgAwAC8AMQAzAC4AMAAvADMANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgANgAxAC4AMAAvADEAMQAuADAALwAyADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEMAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADMAMwAuADAALwAxADUALgAwAC8ANQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA2ADAALgAwAC8AMgAuADAALwAzADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAyAEIAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADMAOAAuADAALwAyAC4AMAAvADYAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADMAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANQAuADAALwA3ADUALgAwAC8AMgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMwBCAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA1AC4AMAAvADUANgAuADAALwAzADkALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA0AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADQANAAuADAALwA1ADIALgAwAC8ANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADUAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AIABIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQA0ADIAYgAvAFAARgBDAC0AMwAxADgAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANwAuADAALwA1AC4ANQAvADQAMgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADYAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQA1AC4AMAAvADEANAAuADAALwA0ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAwAC4AMAAvADQAMAAuADAALwA0ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEIAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQAwAC4AMAAvADcAMAAuADAALwAyADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEMAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAzAC4AMAAvADIANQAuADAALwA1ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEQAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQA1AC4AMAAvADEANQAuADAALwA3ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEUAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgA1AC4AMAAvADEANQAuADAALwA2ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA4AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA3AC4AMAAvADQANgAuADAALwA0ADcALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgAwAC4AMAAvADIANQAuADAALwAxADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgA1AC4AMAAvADIANQAuADAALwAxADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAwAEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiACgANQAwAC4AMAAvADUAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADAAQgBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANQA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBBAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMQAuADUALwA4ADcALgA1AC8AMQAxAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBCAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMwAuADAALwA5ADQALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADEAQwBcACIALAAgAFwAIgBIAEMALQAxADIANwAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADMALgAwAC8AOQA1AC4ANQAvADEALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAyAEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADcAMAAuADAALwA1AC4AMAAvADIANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADMAQQBcACIALAAgAFwAIgBQAEYAQwAtADIAMQA4AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADkALgAwAC8AOAA4AC4AMAAvADMALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMQAuADAALwAyADgALgA1AC8ANAAuADAALwAxADYALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMAAuADAALwAzADkALgAwAC8AMQAuADUALwA5AC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA4ADIALgAwAC8AMQA4AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAyADUALgAwAC8ANwA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAFwAIgAsACAAXAAiACgANQA5AC4AMAAvADMAOQAuADUALwAxAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABcACIALAAgAFwAIgAoADQANgAuADYALwA1ADAALgAwAC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADgAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAxAC4ANQAvADkANgAuADAALwAyAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAOQBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEUALQBFADEANwAwAFwAIgAsACAAXAAiACgANwA3AC4AMAAvADEAOQAuADAALwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMABBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgAOAA4AC4AMAAvADEAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADEAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgANQA4AC4AMAAvADQAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgANQAuADEALwAxADEALgA1AC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQgBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADUANQAuADAALwA0ADIALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQwBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgAMgAuADAALwAxADUALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA3ADMALgA4AC8AMgA2AC4AMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADIAXAAiACwAIABcACIAKAA3ADUALgAwAC8AMgA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADEANQBcACIALAAgAFwAIgAoADQAOAAuADgALwA1ADEALgAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAzAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AQwBGAEMALQAxADMAXAAiACwAIABcACIAKAA0ADAALgAxAC8ANQA5AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANABcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAKAA0ADgALgAyAC8ANQAxAC4AOAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANQBcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEgAQwBGAEMALQAzADEAXAAiACwAIABcACIAKAA3ADgALgAwAC8AMgAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANgBcACIALAAgAFwAIgBDAEYAQwAtADMAMQAvAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAKAA1ADUALgAxAC8ANAA0AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEANAAzAGEAXAAiACwAIABcACIAKAA1ADAALgAwAC8ANQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOABBAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AUABGAEMALQAxADEANgBcACIALAAgAFwAIgAoADMAOQAuADAALwA2ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA4AEIAXAAiACwAIABcACIASABGAEMALQAyADMALwBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiACgANAA2AC4AMAAvADUANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADkAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADQANAAuADAALwA1ADYALgAwACkAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAYwBoAGEAbgBnAGUAZAAgAEgAQwA2ADAAMABhACAAdABvACAASABDAC0ANgAwADAAYQAgAGYAbwByACAAYgBsAGUAbgBkACAAUgAtADQAMQA0AEIALgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABmAG8AcgAgAGIAbABlAG4AZAAgAFIALQA0ADAANQBBACAALQAgAEMAaABhAG4AZwBlAGQAIABIAEMARgBDADEANAAyAGIAIAB0AG8AIABIAEMARgBDAC0AMQA0ADIAYgAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEwAZQBhAGsAYQBnAGUAIAByAGEAdABlAHMAIABmAG8AcgAgAGMAbwBtAG0AbwBuACAAcgBlAGYAcgBpAGcAZQByAGEAdABpAG8AbgAgAGEAbgBkACAAYQBpAHIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAGMAYQB0AGkAdgBlACAAbABlAGEAawBhAGcAZQAgAHIAYQB0AGUAcwAgAGYAbwByACAAYwBvAG0AbQBvAG4AIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuACAAYQBuAGQAIABhAGkAcgAgAC0AIABjAG8AbgBkAGkAdABpAG8AbgBpAG4AZwAgAGUAcQB1AGkAcABtAGUAbgB0AFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADEAMABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ADEALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAGwAZQBhAGsAYQBnAGUAIAByAGEAdABlACAAKAAlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAcgBlAGYAcgBpAGcAZQByAGEAdABvAHIAcwBcACIALAAgADEALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuAFwAIgAsACAAMQA1AC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcABvAHIAdABhAGIAbABlAFwAIgAsACAAMgAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHMAcABsAGkAdABcACIALAAgADMALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABwAGEAYwBrAGEAZwBlAGQAXAAiACwAIAAyAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAHYAZQBoAGkAYwBsAGUAIABBAC8AQwBcACIALAAgADYALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAdgBlAGgAaQBjAGwAZQAgAEEALwBDAFwAIgAsACAAMQAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBhAGwAYwB1AGwAYQB0AGUAQgBsAGUAbgBkAEcAVwBQAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMQAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMgAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMwAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAANAAsAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAxACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAyACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAzACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAA0ACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0ACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGEAbABjAHUAbABhAHQAZQBCAGwAZQBuAGQARwBXAFAAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -19106,20 +19111,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwAgAGkAbgBjAGwAdQBkAGkAbgBnACAAbABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIAAgAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADkALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMgAsACAAMAAuADAAMwAsACAANQAxAC4ANgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAGEAbAAgAG0AaQBuAGUAIAB3AGEAcwB0AGUAIABnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADkALAAgADQALgA2ACwAIAAwAC4AMwAsACAANQA2AC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAKAByAGUAdgBlAHIAdABpAG4AZwAgAHQAbwAgAHMAdABhAG4AZABhAHIAZAAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAKQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBwAHIAbwBjAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAANgAyADkALAAgAFwAIgBtADMAXAAiACwAIAA1ADYALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMAAzACwAIAA1ADYALgA1ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AawBlACAAbwB2AGUAbgAgAGcAYQBzAFwAIgAsACAAMAAuADAAMQA4ADEALAAgAFwAIgBtADMAXAAiACwAIAAzADcALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAA1ACwAIAAzADcALgAwADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGwAYQBzAHQAIABmAHUAcgBuAGEAYwBlACAAZwBhAHMAXAAiACwAIAAwAC4AMAAwADQAMAAsACAAXAAiAG0AMwBcACIALAAgADIAMwA0AC4AMAAsACAAMAAuADAAMwAsACAAMAAuADAAMgAsACAAMgAzADQALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMAAsACAAXAAiAG0AMwBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsATABcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBlAG8AdQBzACAAZgBvAHMAcwBpAGwAIABmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAYQBuAGQAZgBpAGwAbAAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIAAoAG0AZQB0AGgAYQBuAGUAIABvAG4AbAB5ACkAXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4ALAAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA3ADAALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBtAGUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAwADMALAAgADAALgAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAHkAZAByAG8AZwBlAG4AXAAiACwAIAAwAC4AMAAxADIAMgAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMAAsACAAMAAuADUALAAgADAALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgADEALAAgAFwAIgBHAEoAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAzACwAIAA2ADAALgAyADcAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABcAHUAMAAwADIANwBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAdQAwADAAMgA3ACAAdwBlAHIAZQAgAGEAZABkAGUAZAAsACAAZQBhAGMAaAAgAHcAaQB0AGgAIABhAG4AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgADEAIABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAC4AIABUAGgAaQBzACAAaQBzACAAZgBvAHIAIAB1AHMAZQByAHMAIAB3AGgAbwAgAGgAYQB2AGUAIABmAHUAZQBsACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAZABhAHQAYQAgAGkAbgAgAEcASgAgAHIAYQB0AGgAZQByACAAdABoAGEAbgAgAG0AMwAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAuAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABOAGEAdAB1AHIAYQBsACAARwBhAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABNAGUAdAByAG8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AbwBuACAALQAgAE0AZQB0AHIAbwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAOAAuADgALAAgADcALgA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAAxADAALgA3ACwAIAAxADAALgA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAANAAuADEALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAANAAuADAALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIAA0AC4AMQAsACAANAAuADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABOAFMAVwAgAGEAbgBkACAAQQBDAFQAIABzAHAAbABpAHQAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAcgBvAHcAcwAuACAAXAB1ADAAMAAyADcAQwBcAHUAMAAwADIANwAgAFYAYQBsAHUAZQBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAcgBlAHAAbABhAGMAZQBkACAAdwBpAHQAaAAgAHQAaABvAHMAZQAgAGYAbwByACAAVgBpAGMAdABvAHIAaQBhACAAYQBuAGQAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAByAGUAcwBwAGUAYwB0AGkAdgBlAGwAeQAuACAAKABTAGUAZQAgAGEAcABwAGUAbgBkAGkAYwBlAHMAKQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADIALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBBAHMAIABTAGMAbwBwAGUAIAAzACAAZgBhAGMAdABvAHIAcwAgAGEAcgBlACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGEAdAAgAHQAaABlACAAcABvAGkAbgB0ACAAdwBoAGUAcgBlACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAaQBzACAAZABlAGwAaQB2AGUAcgBlAGQAIAB0AG8AIABlAG4AZAAgAHUAcwBlAHIAcwAsACAAaQB0ACAAaQBzACAAbgBlAGMAZQBzAHMAYQByAHkAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAdAAgAGUAYQBjAGgAIABvAGYAIAB0AGgAZQAgAGwAbwBhAGQAIABjAGUAbgB0AHIAZQBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIARwBhAHMAIAByAGUAYQBjAGgAZQBzACAAZQBuAGQAIAB1AHMAZQByAHMAIABlAGkAdABoAGUAcgAgAGYAcgBvAG0AIAB0AGgAZQAgAG0AZQB0AHIAbwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAbgBlAHQAdwBvAHIAawBzACAAbwByACAAZABpAHIAZQBjAHQAIABmAHIAbwBtACAAdABoAGUAIABoAGkAZwBoACAALQAgAHAAcgBlAHMAcwB1AHIAZQAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBIAG8AdQBzAGUAaABvAGwAZABzACAAYQBuAGQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdQBzAGUAcgBzACAAdABlAG4AZAAgAHQAbwAgAGIAZQAgAHMAZQByAHYAZQBkACAAYgB5ACAAdABoAGUAIABmAG8AcgBtAGUAcgAsACAAYQBuAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABnAGUAbgBlAHIAYQB0AG8AcgBzACAAYQBuAGQAIABsAGEAcgBnAGUAIABpAG4AZAB1AHMAdAByAGkAYQBsACAAcABsAGEAbgB0AHMAIABmAHIAbwBtACAAdABoAGUAIABsAGEAdAB0AGUAcgAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIATQBlAHQAcgBvACAAaQBzACAAZABlAGYAaQBuAGUAZAAgAGEAcwAgAGwAbwBjAGEAdABlAGQAIABvAG4AIABvAHIAIABlAGEAcwB0ACAAbwBmACAAdABoAGUAIABkAGkAdgBpAGQAaQBuAGcAIAByAGEAbgBnAGUAIABpAG4AIABOAFMAVwAsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABDAGEAbgBiAGUAcgByAGEAIABhAG4AZAAgAFEAdQBlAGEAbgBiAGUAeQBhAG4ALAAgAE0AZQBsAGIAbwB1AHIAbgBlACwAIABCAHIAaQBzAGIAYQBuAGUALAAgAEEAZABlAGwAYQBpAGQAZQAgAG8AcgAgAFAAZQByAHQAaAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAE8AdABoAGUAcgB3AGkAcwBlACwAIAB0AGgAZQAgAG4AbwBuACAALQAgAG0AZQB0AHIAbwAgAGYAYQBjAHQAbwByACAAcwBoAG8AdQBsAGQAIABiAGUAIAB1AHMAZQBkAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBGAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABhAGwAbAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAB3AGgAaQBjAGgAIABtAGEAeQAgAGkAbgBjAGwAdQBkAGUAIABjAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFQAYQBiAGwAZQAgADYAIABpAHMAIABuAG8AdAAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIAB0AG8AIABlAHQAaABhAG4AZQAuACAAUwBlAGUAIABUAGEAYgBsAGUAIAA3ACAASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGUAdABoAGEAbgBlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBDACAAPQAgAEMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAC4AIABTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAVABhAHMAbQBhAG4AaQBhACAAYQBuAGQAIAB0AGgAZQAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAYQByAGUAIABuAG8AdAAgAGEAdgBhAGkAbABhAGIAbABlACAAZAB1AGUAIAB0AG8AIABjAG8AbgBmAGkAZABlAG4AdABpAGEAbABpAHQAeQAgAGMAbwBuAHMAdAByAGEAaQBuAHQAcwAgAHQAaABhAHQAIABhAHIAaQBzAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABhACAAbABpAG0AaQB0AGUAZAAgAG4AdQBtAGIAZQByACAAbwBmACAATgBHAEUAUgAgAGQAYQB0AGEAIABpAG4AcAB1AHQAcwAuACAASQB0ACAAaQBzACAAcwB1AGcAZwBlAHMAdABlAGQAIAB0AGgAYQB0ACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABWAGkAYwB0AG8AcgBpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgB3AGgAaQBsAGUAIABmAG8AcgAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHQAaABlACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAaQBzACAAYQBwAHAAcgBvAHAAcgBpAGEAdABlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGQAbwAgAG4AbwB0ACAAaQBuAGMAbAB1AGQAZQAgAGYAdQBnAGkAdABpAHYAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGwAZQBhAGsAYQBnAGUAIABmAHIAbwBtACAAbABvAHcAIABwAHIAZQBzAHMAdQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABpAG8AbgAgAHAAaQBwAGUAbABpAG4AZQAgAG4AZQB0AHcAbwByAGsAcwAgAHcAaABpAGwAZQAgAHQAaABvAHMAZQAgAGYAcgBvAG0AIABoAGkAZwBoACAAcAByAGUAcwBzAHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAGcAYQBzACAAbgBlAHQAdwBvAHIAawBzACAAYQByAGUAIABjAG8AbgBzAGkAZABlAHIAZQBkACAAbgBlAGcAbABpAGcAaQBiAGwAZQAuAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGEAbgBkACAAaQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAZQByAHQAYQBpAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgA1ACwAIAA4ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABjAG8AbQBiAHUAcwB0AGUAZABcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAEMAbwBuAHQAZQBuAHQAIABGAGEAYwB0AG8AcgAgACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbABzACAAKABvAHQAaABlAHIAIAB0AGgAYQBuACAAcABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbAAgAHUAcwBlAGQAIABhAHMAIABmAHUAZQBsACkALAAgAGUALgBnAC4AIABsAHUAYgByAGkAYwBhAG4AdABzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADEAMwAuADkALAAgADAALgAwACwAIAAwAC4AMAAsACAAMQAzAC4AOQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAZwByAGUAYQBzAGUAcwBcACIALAAgADMAOAAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAzAC4ANQAsACAAMAAuADAALAAgADAALgAwACwAIAAzAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAcgB1AGQAZQAgAG8AaQBsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABjAHIAdQBkAGUAIABvAGkAbAAgAGMAbwBuAGQAZQBuAHMAYQB0AGUAcwBcACIALAAgADQANQAuADMALAAgAFwAIgB0AFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADYAOQAuADgAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABsAGkAcQB1AGkAZABzAFwAIgAsACAANAA2AC4ANQAsACAAXAAiAHQAXAAiACwAIAA2ADEALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgAxAC4AMgA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdQB0AG8AbQBvAHQAaQB2AGUAIABnAGEAcwBvAGwAaQBuAGUAIAAvACAAcABlAHQAcgBvAGwAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADAALgAyACwAIAAwAC4AMgAsACAANgA3AC4AOAAwACwAIAAxADcALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuACAAZwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsATABcACIALAAgADYANwAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA0ADAALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBLAGUAcgBvAHMAZQBuAGUAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA3AC4ANQAsACAAXAAiAGsATABcACIALAAgADYAOAAuADkALAAgADAALgAwADEALAAgADAALgAyACwAIAA2ADkALgAxADEALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIAB0AHUAcgBiAGkAbgBlACAAZgB1AGUAbAAgAC8AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYAOQAuADgAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHQAaQBuAGcAIABvAGkAbABcACIALAAgADMANwAuADMALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4ANwAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADcAMAAuADIAMAAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA0ACwAIAAwAC4AMgAsACAANwAzAC4AOAA0ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABhAHIAbwBtAGEAdABpAGMAIABoAHkAZAByAG8AYwBhAHIAYgBvAG4AcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAdgBlAG4AdABzADoAIABtAGkAbgBlAHIAYQBsACAAdAB1AHIAcABlAG4AdABpAG4AZQAgAG8AcgAgAHcAaABpAHQAZQAgAHMAcABpAHIAaQB0AHMAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADIALAAgADYAOQAuADkAMwAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYAMAAuADYAMAAsACAAMgAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQBwAGgAdABoAGEAXAAiACwAIAAzADEALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABjAG8AawBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAHQAXAAiACwAIAA5ADIALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAOQAyAC4AOAA4ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAZwBhAHMAIABhAG4AZAAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADIALgA5ACwAIABcACIAdABcACIALAAgADUANAAuADcALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANAAuADcANgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGkAbgBlAHIAeQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADgALAAgADAALgAwADIALAAgADAALgAxACwAIAA2ADkALgA5ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAG8AbAAgAGYAbwByACAAdQBzAGUAIABhAHMAIABhACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGkAbgB0AGUAcgBuAGEAbAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABlAG4AZwBpAG4AZQBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBpAG8AZgB1AGUAbABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAIABhAG4AZAAgAGIAZQBsAG8AdwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAwADIALAAgADAALgAyACwAIAAwAC4AMgAyACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADMAMAAsACAAXAAiAE4ARQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAIABpAG4AIABkAGkAZgBmAGUAcgBlAG4AdAAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADkAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADYALAAgADEAMAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAXAAiACwAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBsAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYANwAuADYAMgAsACAAMQA3AC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAANwAwAC4ANAAxACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAHAAZQB0AHIAbwBsAGUAdQBtACAAZwBhAHMAIAAoAEwAUABHACkAXAAiACwAIAAyADYALgAyACwAIABcACIAawBsAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADUALAAgADAALgAzACwAIAA2ADEALgAwADAALAAgADIAMAAuADIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAGwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4ANQAsACAANwA0AC4AMQA4ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBFAHQAaABhAG4AbwBsAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADIALAAgADAALgA0ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQgBpAG8AZABpAGUAcwBlAGwAXAAiACwAIAAzADQALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgA4ACwAIAAxAC4ANwAsACAAMgAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAAMAAuADUAMQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAE8AdABoAGUAcgAgAGIAaQBvAGYAdQBlAGwAcwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAZwBoAHQAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADcALgAzACwAIAAwAC4AMwAsACAANQA5AC4AMAAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBDAG8AbQBwAHIAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAyAC4AOAAsACAAMAAuADMALAAgADUANAAuADUALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsAbABcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADAANwAsACAAMAAuADQALAAgADcAMAAuADMANwAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADEALAAgADAALgA0ACwAIAA3ADAALgA0ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANAAsACAANwAwAC4ANQAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADcALAAgADAALgA0ACwAIAAwAC4ANAA3ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4ANAAsACAAMAAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADQALAAgADAALgA2ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdABcACIALAAgADMAMwAuADEALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgAwACwAIAAwAC4AMAA2ACwAIAAwAC4ANgAsACAANgA3AC4ANgA2ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwA2AC4AOAAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADYALAAgADAALgAwADEALAAgADAALgA2ACwAIAA3ADAALgAyADEALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA2ACwAIAAwAC4ANgAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADEAMAAuADEALAAgADAALgAzACwAIABcACIAXAAiACwAIAAxADcALgAyACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIABcACIAXAAiACwAIAAxADcALgAzACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEAOAAuADAALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAE8AZgBmAC0AcgBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAaQBuACAAbwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQAgAHEAXAAiACwAIABcACIARQBDAFQAcgBhAG4AcwAsAHEAIAAoAEcASgAvAGsATAApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAE8AMgAgAEUARgBUAHIAYQBuACwAMQAsAHQAcQBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAQwBIADQAIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAE4AMgBPACAARQBGAFQAcgBhAG4ALAAxACwAdABnAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAEYAVAByAGEAbgBzACwAMwAsAHEAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAFAAZQB0AHIAbwBsAFwAIgAsACAAMwA0AC4AMgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgADEANwAuADMAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAATABFAEYAVAAoAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQAgAC0AMQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8ARwBlAHQAUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAFMAdAByAGkAbgBnAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFIASQBHAEgAVAAoAEMAZQBsAGwALABMAEUATgAoAEMAZQBsAGwAKQAtAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8AVABvAHQAYQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBcAG4APQAgAEwAQQBNAEIARABBACgAXABuACAAIAAgACAARgB1AGUAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAsACAARgB1AGUAbABVAHMAZQAsACAARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAsACAARgB1AGUAbABUAHkAcABlACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgAFMAVQBNACgAXABuACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAXABuACAAIAAgACAAIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFQAeQBwAGUAKQAgACoAIABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABVAHMAZQBBAHIAcgBhAHkAIAA9ACAARgB1AGUAbABVAHMAZQApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIAAwAFwAbgAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgAOgAgAEYAdQBlAGwAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA4AC4AMQAgAEYAdQBlAGwAIABVAHMAZQAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsACAARQBDACwAIABFAEYALABcAG4AIAAgACAAIAAoAFEAIAAqACAARQBDACAAKgAgAEUARgApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAGMAbwBtAGIAdQBzAHQAZQBkACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAGsATABcAG4ARQBDACAAOgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwAgADoAIABrAGcAIABDAE8AMgBlACAALwAgAEcASgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AVAByAGEAbgBzAHQAcQAsACAARQBDAF8AVAByAGEAbgBzAHEALAAgAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADgALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADMAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFQAcgBhAG4AcwAsAHQAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEMAXwB7AFQAcgBhAG4AcwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBUAHIAYQBuAHMALAAxACwAdABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBUAHIAYQBuAHMAdABxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlACAALwAgAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHEAXAAiACwAIABcACIARgB1AGUAbAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAXAAiACwAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXABuAFEAIAA6ACAAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABHAEoALwBrAEwAXABuAEUARgAgADoAIABTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBTAEMAcQAsACAARQBDAF8AUwBDAHEALAAgAEUARgBfAFMAQwAxAHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgADIALgAyACAARQBzAHQAaQBtAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABlAG4AZQByAGcAeQAgAHMAbwB1AHIAYwBlAHMAIAAtACAAQwBhAGwAYwB1AGwAYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHQAIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEAXABcAGwAZQBmAHQAKABRAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAUwBDACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFMAQwAsADEALABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFMAQwBxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAdQBzAGUAZAAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAFYAYQByAGkAZQBzACAAYgBhAHMAZQBkACAAbwBuACAAZgB1AGUAbAAgAHQAeQBwAGUAOgAgAGsATAAsACAAbQAzACwAIABHAEoAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMAXwBTAEMAcQBcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFMAQwAxAHEAZwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQwBcACIALAAgAFwAIgBTAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAMQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA5ADoAIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA5AC4AMQAgAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgBUAGgAZQAgAHQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBpAG4AZwAgAGQAdQByAGkAbgBnACAAbwBwAGUAcgBhAHQAaQBvAG4AIAAoAG4AbwB0ACAAZAB1AHIAaQBuAGcAIABpAG4AcwB0AGEAbABsAGEAdABpAG8AbgAgAG8AcgAgAGQAaQBzAHAAbwBzAGEAbAApAFwAbgBHAFcAUABSACAAOgAgAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgADoAIABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBjAGgAYQByAGcAZQBfAFIAYQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIABjAG8AbgB0AGEAaQBuAGUAZAAgAGkAbgAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgADoAIABrAGcAXABuAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEAIAA6ACAAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByACAAOgAgAFAAZQByAGMAZQBuAHQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGMAaABhAHIAZwBlAF8AUgBhACwAIABsAGUAYQBrAGEAZwBlAHIAYQB0AGUAXwBhACwAXABuACAAIAAgACAAKABjAGgAYQByAGcAZQBfAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALwAxADAAMAApACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAFIALAAgAEcAVwBQAF8AUgAsAFwAbgAgACAAIAAgACgAKABFAF8AUgAgACoAIAAxADAAXgAzACkAIAAqACAARwBXAFAAXwBSACkAIAAqACAAMQAwAF4ALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGEAZwBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABjAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBSAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGcAYQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADkALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMwAuADEAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAaQBuAGQAdQBzAHQAcgBpAGEAbAAgAHAAcgBvAGMAZQBzAHMAZQBzACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAtACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBhAGcAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBjAGgAYQByAGcAZQBfAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALwAxADAAMAApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AUgAgAD0AIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGEAIABcAFwAbABlAGYAdAAoACAAYwBoAGEAcgBnAGUAXwB7AFIAYQB9ACAAXABcAHQAaQBtAGUAcwAgAFwAXABmAHIAYQBjAHsAbABlAGEAawBhAGcAZQBcAFwALAByAGEAdABlAF8AYQB9AHsAMQAwADAAfQAgAFwAXAByAGkAZwBoAHQAKQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBDAE8AMgBlACAAPQAgAFwAXABsAGUAZgB0ACgARQBfAFIAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AIABcAFwAcgBpAGcAaAB0ACkAIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwBSACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAGgAYQByAGcAZQBfAFIAYQBcACIALAAgAFwAIgBBAG0AbwB1AG4AdAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIABjAG8AbgB0AGEAaQBuAGUAZAAgAGkAbgAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBsAGUAYQBrAGEAZwBlAHIAYQB0AGUAXwBhAFwAIgAsACAAXAAiAFAAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAAdABvAHQAYQBsACAAYwBoAGEAcgBnAGUAIABsAGUAYQBrAGUAZAAgAGYAcgBvAG0AIABhAHAAcABsAGkAYQBuAGMAZQAgAGEAIABlAGEAYwBoACAAeQBlAGEAcgBcACIALAAgAFwAIgBQAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYQBcACIALAAgAFwAIgBBAHAAcABsAGkAYQBuAGMAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAFwAIgAsACAAXAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAFIAXAAiACwAIABcACIAVABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSAFwAIgAsACAAXAAiAHQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABnAGEAcwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADkALgAxAC4AMQAgACgAMQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABfAFIAXAAiACwAIABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSAFwAIgAsACAAXAAiAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAZQBxAHUAYQB0AGkAbwBuACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIAB0AG8AIABDAE8AMgAtAGUAIAB1AHMAaQBuAGcAIAB0AGgAZQAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABcAHUAMAAwADIANwBzACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIAAoAEcAVwBQACkALgBcACIAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAVABhAGIAbABlACAAMgAzACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAQQBwAHAAZQBuAGQAaQB4ACAAMgAgAC0AIABUAGEAYgBsAGUAIAAyADMAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMAOQAsACAANQAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAGgAZQBtAGkAYwBhAGwAIABmAG8AcgBtAHUAbABhAFwAIgAsACAAXAAiAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAKABBAFIANQApAFwAIgAsACAAXAAiAEcAYQBzACAALQAgAEYAQwAgAG4AYQBtAGUAXAAiACwAIABcACIAQQBkAGkAdABpAG8AbgBhAGwAIABkAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlAFwAIgAsACAAXAAiAEMATwAyAFwAIgAsACAAMQAsACAAXAAiAEMATwAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAQwBIADQAXAAiACwAIAAyADgALAAgAFwAIgBDAEgANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlAFwAIgAsACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUALAAgAFwAIgBOADIATwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAbABwAGgAdQByACAAaABlAHgAYQBmAGwAdQBvAHIAaQBkAGUAXAAiACwAIABcACIAUwBGADYAXAAiACwAIAAyADMANQAwADAALAAgAFwAIgBTAEYANgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMwAgACgAUgAtADIAMwApAFwAIgAsACAAXAAiAEMASABGADMAXAAiACwAIAAgADEAMgA0ADAAMAAsACAAXAAiAEgARgBDAC0AMgAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMwAyACAAKABSAC0AMwAyACkAXAAiACwAIABcACIAQwBIADIARgAyAFwAIgAsACAANgA3ADcALAAgAFwAIgBIAEYAQwAtADMAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADQAMQAgACgAUgAtADQAMQApAFwAIgAsACAAXAAiAEMASAAzAEYAXAAiACwAIAAgADEAMQA2ACwAIABcACIASABGAEMALQA0ADEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQA0ADMALQAxADAAbQBlAGUAIAAoAFIALQA0ADMAMQAwAG0AZQBlACkAXAAiACwAIABcACIAQwA1AEgAMgBGADEAMABcACIALAAgADEANgA1ADAALAAgAFwAIgBIAEYAQwAtADQAMwAtADEAMABtAGUAZQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMgA1ACAAKABSAC0AMQAyADUAKQBcACIALAAgAFwAIgBDADIASABGADUAXAAiACwAIAAgADMAMQA3ADAALAAgAFwAIgBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAzADQAIAAoAFIALQAxADMANAApAFwAIgAsACAAXAAiAEMAMgBIADIARgA0ACAAKABDAEgARgAyAEMASABGADIAKQBcACIALAAgACAAMQAxADIAMAAsACAAXAAiAEgARgBDAC0AMQAzADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADMANABhACAAKABSAC0AMQAzADQAYQApAFwAIgAsACAAXAAiAEMAMgBIADIARgA0ACAAKABDAEgAMgBGAEMARgAzACkAXAAiACwAIAAxADMAMAAwACwAIABcACIASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA0ADMAIAAoAFIALQAxADQAMwApAFwAIgAsACAAXAAiAEMAMgBIADMARgAzACAAKABDAEgARgAyAEMASAAyAEYAKQBcACIALAAgADMAMgA4ACwAIABcACIASABGAEMALQAxADQAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEANAAzAGEAIAAoAFIALQAxADQAMwBhACkAXAAiACwAIABcACIAQwAyAEgAMwBGADMAIAAoAEMARgAzAEMASAAzACkAXAAiACwAIAA0ADgAMAAwACwAIABcACIASABGAEMALQAxADQAMwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA1ADIAYQAgACgAUgAtADEANQAyAGEAKQBcACIALAAgAFwAIgBDADIASAA0AEYAMgAgACgAQwBIADMAQwBIAEYAMgApAFwAIgAsACAAMQAzADgALAAgAFwAIgBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADIANwBlAGEAIAAoAFIALQAyADIANwBlAGEAKQBcACIALAAgAFwAIgBDADMASABGADcAXAAiACwAIAAzADMANQAwACwAIABcACIASABGAEMALQAyADIANwBlAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADMANgBmAGEAIAAoAFIALQAyADMANgBmAGEAKQBcACIALAAgAFwAIgBDADMASAAyAEYANgBcACIALAAgADgAMAA2ADAALAAgAFwAIgBIAEYAQwAtADIAMwA2AGYAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIANAA1AGMAYQAgACgAUgAtADIANAA1AGMAYQApAFwAIgAsACAAXAAiAEMAMwBIADMARgA1AFwAIgAsACAANwAxADYALAAgAFwAIgBIAEYAQwAtADIANAA1AGMAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIANAA1AGYAYQAgACgAUgAtADIANAA1AGYAYQApAFwAIgAsACAAXAAiAEMASABGADIAQwBIADIAQwBGADMAXAAiACwAIAA4ADUAOAAsACAAXAAiAEgARgBDAC0AMgA0ADUAZgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMwA2ADUAbQBmAGMAIAAoAFIALQAzADYANQBtAGYAYwApAFwAIgAsACAAXAAiAEMASAAzAEMARgAyAEMASAAyAEMARgAzAFwAIgAsACAAOAAwADQALAAgAFwAIgBIAEYAQwAtADMANgA1AG0AZgBjAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIAIAAoAFIALQAyADIAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAMgBcACIALAAgADEANwA2ADAALAAgAFwAIgBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADIAMwAgACgAUgAtADEAMgAzACkAXAAiACwAIABcACIAQwBIAEMAbAAyADIAQwBGADMAXAAiACwAIAA3ADkALAAgAFwAIgBIAEMARgBDAC0AMQAyADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEAMgA0ACAAKABSAC0AMQAyADQAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAQwBGADMAXAAiACwAIAA1ADIANwAsACAAXAAiAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQA0ADEAYgAgACgAUgAtADEANAAxAGIAKQBcACIALAAgAFwAIgBDAEgAMwBDAEMAbAAyAEYAXAAiACwAIAA3ADgAMgAsACAAXAAiAEgAQwBGAEMALQAxADQAMQBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADQAMgBiACAAKABSAC0AMQA0ADIAYgApAFwAIgAsACAAXAAiAEMASAAyAEMAQwBsAEYAMgBcACIALAAgADEAOQA4ADAALAAgAFwAIgBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBhACAAKABSAC0AMgAyADUAYwBhACkAXAAiACwAIABcACIAQwBIAEMAbAAyAEMARgAyAEMARgAzAFwAIgAsACAAMQAyADcALAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGIAIAAoAFIALQAyADIANQBjAGIAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAQwBGADIAQwBDAEkARgAyAFwAIgAsACAANQAyADUALAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMQA0ACAAUABlAHIAZgBsAHUAbwByAG8AbQBlAHQAaABhAG4AZQAgACgAdABlAHQAcgBhAGYAbAB1AG8AcgBvAG0AZQB0AGgAYQBuAGUAKQBcACIALAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAALAAgAFwAIgBQAEYAQwAtADEANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADEAMQA2ACAAUABlAHIAZgBsAHUAbwByAG8AZQB0AGgAYQBuAGUAIAAoAGgAZQB4AGEAZgBsAHUAbwByAG8AZQB0AGgAYQBuAGUAKQBcACIALAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAxADEAMAAwACwAIABcACIAUABGAEMALQAxADEANgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADIAMQA4ACAAUABlAHIAZgBsAHUAbwByAG8AcAByAG8AcABhAG4AZQBcACIALAAgAFwAIgBDADMARgA4AFwAIgAsACAAOAA5ADAAMAAsACAAXAAiAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAzADEALQAxADAAIABQAGUAcgBmAGwAdQBvAHIAbwBiAHUAdABhAG4AZQBcACIALAAgAFwAIgBDADQARgAxADAAXAAiACwAIAA5ADIAMAAwACwAIABcACIAUABGAEMALQAzADEALQAxADAAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAzADEAOAAgAFAAZQByAGYAbAB1AG8AcgBvAGMAeQBjAGwAbwBiAHUAdABhAG4AZQBcACIALAAgAFwAIgBjAC0AQwA0AEYAOABcACIALAAgADkANQA0ADAALAAgAFwAIgBQAEYAQwAtADMAMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0ANAAxAC0AMQAyACAAUABlAHIAZgBsAHUAbwByAG8AcABlAG4AdABhAG4AZQBcACIALAAgAFwAIgBDADUARgAxADIAXAAiACwAIAA4ADUANQAwACwAIABcACIAUABGAEMALQA0ADEALQAxADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA1ADEALQAxADQAIABQAGUAcgBmAGwAdQBvAHIAbwBoAGUAeABhAG4AZQBcACIALAAgAFwAIgBDADYARgAxADQAXAAiACwAIAA3ADkAMQAwACwAIABcACIAUABGAEMALQA1ADEALQAxADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA5ADEALQAxADgAIABQAGUAcgBmAGwAdQBuAGEAZgBlAG4AZQBcACIALAAgAFwAIgBDADEAMABGADEAOABcACIALAAgADcAMQA5ADAALAAgAFwAIgBQAEYAQwAtADkAMQAtADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMgBcACIALAAgAFwAIgBDAEMAbAAyAEYAMgBcACIALAAgADEAMAAyADAAMAAsACAAXAAiAEMARgBDAC0AMQAyAFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADMAXAAiACwAIABcACIAQwBDAGwARgAzAFwAIgAsACAAMQAzADkAMAAwACwAIABcACIAQwBGAEMALQAxADMAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAEMAQwBsAEYAMgBDAEMAbABGADIAXAAiACwAIAA4ADUAOQAwACwAIABcACIAQwBGAEMALQAxADEANABcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAQwBDAGwARgAyAEMARgAzAFwAIgAsACAANwA2ADcAMAAsACAAXAAiAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcARwBBAFMAIAAtACAARgBDACAAbgBhAG0AZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAHQAcgB1AG4AYwBhAHQAZQBkACAAZwBhAHMAIABuAGEAbQBlACAAdABvACAAYQBsAGwAbwB3ACAAbQBhAHQAYwBoAGkAbgBnACAAdwBpAHQAaAAgAG8AdABoAGUAcgAgAHQAYQBiAGwAZQBzAC4AIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABnAGEAcwBlAHMAIABmAHIAbwBtACAASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQAuACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAQQBkAGQAaQB0AGkAbwBuAGEAbAAgAGQAYQB0AGEAIABzAG8AdQByAGMAZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAC4AXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAQgBsAGUAbgBkAGUAZAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAbABlAG4AZABlAGQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAcwAgACgAbQBhAG4AeQAgAGMAbwBuAHQAYQBpAG4AaQBuAGcAIABIAEYAQwBTACAAYQBuAGQALwBvAHIAIABQAEYAQwBTACkAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABBAHAAcABlAG4AZABpAHgAIAAyACAALQAgAFQAYQBiAGwAZQAgADIANABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAxACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABlAG4AZABcACIALAAgAFwAIgBDAG8AbgBzAHQAaQB0AHUAZQBuAHQAcwBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwBpAHQAaQBvAG4AIAAoACUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAFIALQA0ADAAMAAgAGMAYQBuACAAaABhAHYAZQAgAHYAYQByAGkAbwB1AHMAIABwAHIAbwBwAG8AcgB0AGkAbwBuAHMAIABvAGYAIABDAEYAQwAtADEAMgAgAGEAbgBkACAAQwBGAEMALQAxADEANAAuACAAVABoAGUAIABlAHgAYQBjAHQAIABjAG8AbQBwAG8AcwBpAHQAaQBvAG4AIABuAGUAZQBkAHMAIAB0AG8AIABiAGUAIABzAHAAZQBjAGkAZgBpAGUAZAAsACAAZQAuAGcALgAsACAAUgAtADQAMAAwACAAKAA2ADAALwA0ADAAKQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAA1ADMALgAwAC8AMQAzAC4AMAAvADMANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgANgAxAC4AMAAvADEAMQAuADAALwAyADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEMAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADMAMwAuADAALwAxADUALgAwAC8ANQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA2ADAALgAwAC8AMgAuADAALwAzADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAyAEIAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADMAOAAuADAALwAyAC4AMAAvADYAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADMAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANQAuADAALwA3ADUALgAwAC8AMgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMwBCAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA1AC4AMAAvADUANgAuADAALwAzADkALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA0AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADQANAAuADAALwA1ADIALgAwAC8ANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADUAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AIABIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQA0ADIAYgAvAFAARgBDAC0AMwAxADgAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANwAuADAALwA1AC4ANQAvADQAMgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADYAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQA1AC4AMAAvADEANAAuADAALwA0ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAwAC4AMAAvADQAMAAuADAALwA0ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEIAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQAwAC4AMAAvADcAMAAuADAALwAyADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEMAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAzAC4AMAAvADIANQAuADAALwA1ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEQAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQA1AC4AMAAvADEANQAuADAALwA3ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEUAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgA1AC4AMAAvADEANQAuADAALwA2ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA4AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA3AC4AMAAvADQANgAuADAALwA0ADcALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgAwAC4AMAAvADIANQAuADAALwAxADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgA1AC4AMAAvADIANQAuADAALwAxADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAwAEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiACgANQAwAC4AMAAvADUAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADAAQgBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANQA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBBAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMQAuADUALwA4ADcALgA1AC8AMQAxAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBCAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMwAuADAALwA5ADQALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADEAQwBcACIALAAgAFwAIgBIAEMALQAxADIANwAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADMALgAwAC8AOQA1AC4ANQAvADEALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAyAEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADcAMAAuADAALwA1AC4AMAAvADIANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADMAQQBcACIALAAgAFwAIgBQAEYAQwAtADIAMQA4AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADkALgAwAC8AOAA4AC4AMAAvADMALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMQAuADAALwAyADgALgA1AC8ANAAuADAALwAxADYALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMAAuADAALwAzADkALgAwAC8AMQAuADUALwA5AC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA4ADIALgAwAC8AMQA4AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAyADUALgAwAC8ANwA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAFwAIgAsACAAXAAiACgANQA5AC4AMAAvADMAOQAuADUALwAxAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABcACIALAAgAFwAIgAoADQANgAuADYALwA1ADAALgAwAC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADgAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAxAC4ANQAvADkANgAuADAALwAyAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAOQBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEUALQBFADEANwAwAFwAIgAsACAAXAAiACgANwA3AC4AMAAvADEAOQAuADAALwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMABBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgAOAA4AC4AMAAvADEAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADEAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgANQA4AC4AMAAvADQAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgANQAuADEALwAxADEALgA1AC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQgBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADUANQAuADAALwA0ADIALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQwBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgAMgAuADAALwAxADUALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA3ADMALgA4AC8AMgA2AC4AMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADIAXAAiACwAIABcACIAKAA3ADUALgAwAC8AMgA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADEANQBcACIALAAgAFwAIgAoADQAOAAuADgALwA1ADEALgAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAzAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AQwBGAEMALQAxADMAXAAiACwAIABcACIAKAA0ADAALgAxAC8ANQA5AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANABcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAKAA0ADgALgAyAC8ANQAxAC4AOAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANQBcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEgAQwBGAEMALQAzADEAXAAiACwAIABcACIAKAA3ADgALgAwAC8AMgAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANgBcACIALAAgAFwAIgBDAEYAQwAtADMAMQAvAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAKAA1ADUALgAxAC8ANAA0AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEANAAzAGEAXAAiACwAIABcACIAKAA1ADAALgAwAC8ANQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOABBAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AUABGAEMALQAxADEANgBcACIALAAgAFwAIgAoADMAOQAuADAALwA2ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA4AEIAXAAiACwAIABcACIASABGAEMALQAyADMALwBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiACgANAA2AC4AMAAvADUANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADkAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADQANAAuADAALwA1ADYALgAwACkAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAYwBoAGEAbgBnAGUAZAAgAEgAQwA2ADAAMABhACAAdABvACAASABDAC0ANgAwADAAYQAgAGYAbwByACAAYgBsAGUAbgBkACAAUgAtADQAMQA0AEIALgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABmAG8AcgAgAGIAbABlAG4AZAAgAFIALQA0ADAANQBBACAALQAgAEMAaABhAG4AZwBlAGQAIABIAEMARgBDADEANAAyAGIAIAB0AG8AIABIAEMARgBDAC0AMQA0ADIAYgAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEwAZQBhAGsAYQBnAGUAIAByAGEAdABlAHMAIABmAG8AcgAgAGMAbwBtAG0AbwBuACAAcgBlAGYAcgBpAGcAZQByAGEAdABpAG8AbgAgAGEAbgBkACAAYQBpAHIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAGMAYQB0AGkAdgBlACAAbABlAGEAawBhAGcAZQAgAHIAYQB0AGUAcwAgAGYAbwByACAAYwBvAG0AbQBvAG4AIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuACAAYQBuAGQAIABhAGkAcgAgAC0AIABjAG8AbgBkAGkAdABpAG8AbgBpAG4AZwAgAGUAcQB1AGkAcABtAGUAbgB0AFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADEAMABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ADEALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAGwAZQBhAGsAYQBnAGUAIAByAGEAdABlACAAKAAlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAcgBlAGYAcgBpAGcAZQByAGEAdABvAHIAcwBcACIALAAgADEALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuAFwAIgAsACAAMQA1AC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcABvAHIAdABhAGIAbABlAFwAIgAsACAAMgAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHMAcABsAGkAdABcACIALAAgADMALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABwAGEAYwBrAGEAZwBlAGQAXAAiACwAIAAyAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAHYAZQBoAGkAYwBsAGUAIABBAC8AQwBcACIALAAgADYALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAdgBlAGgAaQBjAGwAZQAgAEEALwBDAFwAIgAsACAAMQAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBhAGwAYwB1AGwAYQB0AGUAQgBsAGUAbgBkAEcAVwBQAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMQAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMgAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMwAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAANAAsAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAxACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAyACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAzACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAA0ACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0ACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGEAbABjAHUAbABhAHQAZQBCAGwAZQBuAGQARwBXAFAAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -19314,7 +19306,24 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -19325,23 +19334,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19358,4 +19351,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/9_Refrigerants_WIP_v02.xlsx
+++ b/Excel/9_Refrigerants_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AF8F28-DB31-432A-B634-7CF1D5926875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0940498C-268C-4EA9-B5B8-20AB54094FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" firstSheet="2" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -19,8 +19,11 @@
     <sheet name="Input - Refrigerants" sheetId="70" r:id="rId4"/>
     <sheet name="9.1.1.1-2 Refrigerant use" sheetId="69" r:id="rId5"/>
     <sheet name="Constants - Refrigerants" sheetId="110" r:id="rId6"/>
-    <sheet name="Constants - Common" sheetId="119" r:id="rId7"/>
+    <sheet name="Constants - Common" sheetId="120" r:id="rId7"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId8"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -2067,126 +2070,6 @@
   <dxfs count="60">
     <dxf>
       <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3046,6 +2929,126 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4658,6 +4661,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -4743,7 +4766,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{23E8EA07-16D0-4744-9285-B13305AFD092}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{0EC92A31-BE3E-4407-AC09-CFA1164CDD6D}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4763,52 +4786,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{AA8187F8-0042-4C0E-A158-2B1DDD89C55E}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{2066E467-909F-401D-990B-DA61453E0A25}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EAA8886F-E011-45A8-B808-0BEFAC3A35DF}" name="MAT" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{9CF337A1-0763-4378-8E45-0935B1DA5755}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{AA7B88F7-095C-4E16-9CF8-A98235D82885}" name="MAP" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{0B29462C-A2E2-4913-8007-E23D4122483E}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0ECBB133-8208-4BC5-87AC-C9A17199BA63}" name="Frost days per year" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{2D29C59E-80A9-46A0-837F-2D96C943E5F5}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3D9AC821-75C8-4D27-BCEF-C2056472F642}" name="Elevation" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{0C464B99-3A0A-4797-8F15-8D94E0964C7B}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D643E4EB-D004-46BD-9D3C-B84163D0D6FB}" name="MAP:PET" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{18A568C7-FA36-4640-B74C-39132E120746}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{12A07609-F08E-4413-B6D3-C87FDF66E215}" name="Min temp" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{8FD1D5A1-C8C0-45EC-AB2C-BCA818236DF1}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F102AF9F-9FEA-40DD-AF28-041C1461D83E}" name="Max temp" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{8E12D732-5C3F-4B9E-9D25-C5914FF3F8C4}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{90A51AC4-8B22-4441-A14C-E02D0326E5F8}" name="Min rainfall" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{485A2958-6179-4B76-8DF2-FD10C7A4E76D}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{3FD86231-C6F8-4A32-80AD-5D4060FD1B31}" name="Max rainfall" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{247814BC-A593-439C-AC24-05DA24086F84}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{73D202BF-BFCE-42FA-9D0F-2DA13C4481FC}" name="Min frost days" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{8E5D3C3D-192C-4714-A623-5F7D98731D36}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{F3AAFA92-EA40-43BB-8481-31088FE8F2A5}" name="Max frost days" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{CDE8C318-5B61-4943-8290-E9ADCC3F4346}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EFBF1273-7CCE-435E-9C54-D0FC021C2D12}" name="Min elevation" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{54932E10-26EE-48EA-9FF8-5CBB73DE766F}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{35C9987E-D507-47A4-9DE5-D9177126FF2D}" name="Max elevation" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{0A11D405-5F6E-471F-BB3D-DEA4F2D252EC}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{F27CE1D5-2216-4EDB-B3ED-8A6CCE6C7142}" name="Min MAP:PET" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{B10523CC-47C7-4264-8BC6-8F94C1E0D675}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{520A4B37-7DA2-48BF-AF37-03D14FA097BC}" name="Max MAP:PET" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{6905ED76-27A2-4B6C-A2F5-70E8199CC014}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4817,16 +4840,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{5AAD80A4-98CA-4A77-AF91-D13C800FBEDB}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{EA55C38D-3BA7-4332-9B83-24DBB3C433BD}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4EF58733-2135-49D9-856E-9C4907356A09}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{92081869-CFE9-4FFB-AE1B-C91E76914543}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F7659FA5-BEFD-4223-A8BA-0F0B54D3C77A}" name="Wet or Dry Zone" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{C4F80A5A-6BE8-4DA7-9094-CFEBE45BF58C}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4835,7 +4858,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{B4EF9EAB-A496-4FA6-9FF3-9C2DA7DF988D}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{07D652FA-F866-473C-8CA0-3FE2A9B8FBBB}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4843,16 +4866,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{692CCA7F-354D-4462-A5CC-B470737A3175}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{54734147-F9D7-432A-B20A-8B9B4EA07012}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9417D96B-90BA-4033-B9C6-FDA813678B4C}" name="MAT">
+    <tableColumn id="2" xr3:uid="{E799B703-67A7-4F05-832D-2DA2A05A564E}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F61EA434-BCC2-42F2-8919-8D2C0B407D0C}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{708C07DB-9FF2-4D63-BEC2-96481D522E69}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{ECBB14F8-F7FB-45E5-B482-8ACA32BD90F9}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{E0F44F9B-CE94-48F6-BFA3-4B43AAC99B5D}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4861,7 +4884,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{CF1750BE-922B-48E8-ADA4-66091A5A0FE9}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{4BF3CA9E-33A3-444F-AE65-A95742B7EEBA}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4869,16 +4892,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4F8142C1-4652-4EFB-ACD0-F33E4ADF1A95}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{CD0CA66F-0180-4946-B16B-F930A7B54FC8}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4EAC22C-2A06-49E0-913C-77E92F7B10F6}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{13A77870-14E3-43C1-A9A2-0C1D7DEF1F1E}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{433AECB9-327A-4C6E-8EE9-E1448F5E2DBE}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{24836987-45E5-4BCB-878A-45369AC62CA2}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2AA94844-B51B-405E-B9AD-53CEE3499D09}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{869314BB-60BD-41DD-9810-8266ADBF1FF5}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4887,16 +4910,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{596BD446-2F05-45FD-83F3-42F2F34B5B9E}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{252ECB62-16EC-4349-94A7-C243609CE1F4}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3FBF0D07-67BB-436A-9984-469656A28704}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{06558AA8-3261-4223-80CB-CD42126B43BA}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EC0DCA32-396C-478E-90F8-04A7BED9BB16}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{BAE1B325-F7DB-4349-8A83-B71D89138ED2}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4905,16 +4928,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{490FA27C-33C1-4662-9AFF-006C08A4211E}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{23B1A042-0A6B-4DE5-A22B-ABEEB211AE21}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F71770D4-9368-4676-B714-C7475FF89B62}" name="Data source">
+    <tableColumn id="1" xr3:uid="{FFEC17F4-63CE-4E8A-B0F2-8FB6193E9B67}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0C157665-6F13-4351-A6EB-9119D273426C}" name="Data score">
+    <tableColumn id="2" xr3:uid="{D3F4B3C1-2BB0-4E80-A8EF-21324678483D}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4923,16 +4946,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{9B5F685E-7CFD-4B01-8F98-11C78979ED5D}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{51196F97-E184-479A-9EF1-6098A7F6CFE8}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{75BEBE37-39B4-4E59-A52E-53C1E93F718F}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{128C8ADE-048D-41D3-8667-4912DBDF4523}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C0D50F48-A838-46A3-8B4E-BD74578D5EA5}" name="FracWET" dataDxfId="31">
+    <tableColumn id="2" xr3:uid="{8853C8AF-CC64-41BA-847D-F2A50F2D8C3F}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4941,7 +4964,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{C38EC5FD-5E4F-4880-BB81-BDF89DA918CA}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{79A95BFA-9340-4FD4-B459-DC50B6863A9A}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4950,19 +4973,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{CFB3196B-0D9B-41E0-81A6-84DA7CAE04DD}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{15FCEEEB-7A32-4254-A48A-F807311A0FA0}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{209F7857-519C-48A2-BB2E-9BCB020F651D}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{DF6330CB-A230-4455-8568-104FC0AE7549}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5DF0D2F4-5F2B-4DE6-ADC7-CD7463078EEE}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{240515AD-CB8D-436E-8A89-8A3FD11C2A4E}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EC04533A-568D-4D72-AC19-2C7248B47182}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{0886C016-9360-46DF-BB64-4D1ABEB1851B}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C32F65B2-1CB1-4ABE-9FC4-BE4364E12ECE}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{D996474C-551F-4FD9-B7DD-BADDC922BE27}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4971,16 +4994,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{89729ED1-E86C-4E41-B0BE-BE545A1501D2}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{E0546C11-8CAB-4B4C-80FF-E2F4F1BD2E07}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{058EE474-821C-46B8-B9DB-A856FC27B7A9}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{6861CB8F-7B79-402A-96D3-07762E7A33AC}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{64C441F6-07CD-4748-BEAE-C8625EB5AEF9}" name="FracWET" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2178DC37-3904-4FCB-96F4-5045568CA5E3}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4989,16 +5012,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{578524F2-0357-449F-ABA2-BC0D3754A4DA}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{23968D22-E960-4329-856D-6288D5AF509B}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A9D82E06-BBC8-48FF-87E0-4E5D302CD314}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{306C314A-3449-4BB7-891E-97AF5556DF2E}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6B8B8187-2CE6-4828-B655-AC0E679BD856}" name="EFPRP" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E655A4AE-202B-4987-8024-2F96DE8EE459}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5037,16 +5060,16 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{87C71CAF-1371-452F-BE5F-BBFF68E929C1}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{7AC42A9E-1375-4D3D-9826-BECB812E7870}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DB86F89E-F0C6-4E23-84FA-724586BBF2C0}" name="Month">
+    <tableColumn id="1" xr3:uid="{9312313D-3289-4AE9-AEC2-1ADDBAAC73C9}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E19CC679-0382-4B3E-B2BA-CA84BD9BEC57}" name="Season" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C080C086-6028-4739-933E-DD28FD2783CE}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5055,7 +5078,7 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{3E8C17E0-8327-49FB-920D-57E9236C3ACA}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{BC3E53E5-5FBC-4B58-ADDA-7A872E540793}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5075,52 +5098,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{DD282435-2C2B-4691-B43F-3A454A86ADF0}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{31DDA435-A4D2-46BF-9332-2B74FAA85B12}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9F6E82C4-3071-42FC-93D6-968F926A0031}" name="MAT (ºC)" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0D0500B2-A6E6-4C85-9CAB-551332D804E7}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B27891F1-2A40-4958-9F1E-6BEBC12FF7C4}" name="Anaerobic lagoon" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{88DCCA65-28BB-452E-974E-9AAF8EB2ED4F}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5662A798-B4DE-4CC1-A843-7A6191D9632B}" name="Digester / covered lagoons" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{E70FB12E-7B35-4BF0-9815-D3B4446F8100}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{605030C8-492D-4496-BF8E-7FA67C7FE1EA}" name="Liquid systems" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{7E7DF08D-5533-4E15-8CD7-37B8E9CB9049}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{0002A82C-EACF-411E-A58B-682D7665BB39}" name="Daily spread" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{D6FDC6A5-43AA-4183-BCD6-3596B65EEF4C}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{4BF9F484-91EC-450F-8028-73876D34E694}" name="Composting (passive windrow)" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{93283AE2-D814-4543-8FFE-C6596572DB4C}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{8A5C68A4-F5AA-4764-A03E-2279AB444523}" name="Solid storage" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{AF5E9CF5-798A-481A-A232-69D17673E778}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{123BF989-3B2E-4BA3-8E54-20C4BE277CFE}" name="Pit storage" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{184B24AA-FFE1-4E05-9EA9-339BADCF7151}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8DAAE1D4-960B-4197-A78A-30E617DF6E41}" name="Deep litter" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{525ADC10-EAE4-4897-BB09-9F56DA2A6F96}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{34450AE7-D05C-4631-8EE5-4679D80792CD}" name="Poultry manure with bedding" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{3044C277-D6FA-497E-9354-B199C178F054}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{3C9DF90B-C67E-43D8-8207-6500A71BC3F4}" name="Poultry manure without bedding" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{30E9BDA4-A6B1-41D3-8B97-0684A2758405}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{89E1FE1C-A229-4E74-BA5A-27BCE54D61FC}" name="Direct processing" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{0E46A02C-1396-46FD-8A9E-4F15D35E5FD1}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{12B2DF86-A0C2-49AA-921F-AD97795AEDAB}" name="Direct application" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{F7F4384A-DE6C-497F-A6C0-2878E3701AAE}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{782429A0-44D3-4681-BFA0-84CC3419FDAC}" name="Pasture range and paddock" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{E4F594DE-43FC-48F5-9EEE-3501E4EBAD7A}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{FF208E44-6053-4431-AA07-E648AB1553AE}" name="MAT raw" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{18B9508F-8F87-44B1-ACC7-771CE2A7A9DB}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5129,16 +5152,16 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{6D5D4212-3420-44AD-9282-E9DBF49BF3A5}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{82D265DA-C04F-4DBF-A34C-D8E68CE0A6B6}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{27068885-8281-4700-BCD0-1F0F37B151C2}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{5A18A9FE-F964-4B97-87AB-D0C35025E01E}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4BCC72ED-670B-4B3C-AECD-20306DA91098}" name="EFNi &amp; EFN2Oi" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E5260A70-10AB-4359-AADE-082AAFAA3867}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5239,20 +5262,20 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{39B225CC-22FF-489B-944A-4F2BEE1F8643}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4016A76B-C16C-4EFE-99D3-755F346E6E05}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0ACCCA86-D47A-49E6-B57D-A4B7CE23D744}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{92E85321-7C28-4AB5-8060-9A6D3EAAB856}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B27BEAA4-A451-46EC-B597-B9703A1B45A7}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{C6C32567-4ADC-45FD-9A74-647C946E2BFC}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9FC59DF2-1592-4CD6-AF02-761876063B49}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{D327B7A0-B3AA-4EC9-B4B1-C8F56C6EE675}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5261,12 +5284,12 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{0A034682-B3AF-4777-98F1-9BE6449F5298}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{086AF855-7A26-446B-8650-DE096E63238A}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{6DBBCDA6-30C0-4638-8E70-258F978DAC2B}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{B52D9896-3889-4A15-A9CF-1E3B3D202F41}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5275,16 +5298,16 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{591615C9-B0E8-48DF-83C0-32D82AC8F59D}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{89233090-5574-4C68-B5CE-7826059CB7CB}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{56F20BC2-56F5-427B-8FF1-7EF09C514D4E}" name="Gas">
+    <tableColumn id="1" xr3:uid="{144444B5-C615-449C-8A99-682019C39CFC}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C03A9D3C-DC7B-4F14-83E7-72FA50D1D978}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{D6CAF961-2C0F-4448-AC79-C1582FB43587}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5293,7 +5316,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C2AF2589-D67C-4A7B-8DF4-E3C3EA7870C2}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{ECF87DD4-60CC-494B-8A20-9673626EDF0F}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5302,19 +5325,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F494CD3D-C587-4121-ACC7-41E23F5D8191}" name="Gas">
+    <tableColumn id="1" xr3:uid="{32A63C00-BD25-4BAB-9766-E4788766820D}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{259B97AB-2FE6-4FFB-A603-AD4E4F868E5E}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{F8870FB6-3945-48A9-A2E7-390F1C1905E1}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{20CFD2D3-87F3-4A7E-8D15-1F8646164388}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{80EFDE92-C01B-4C76-8A62-1F1F49BBE85A}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{76ABA1C2-D154-4611-93A1-492948E1A4E1}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{94FA067B-F6B7-4117-BDF6-A57985245A23}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E61BB90F-07C1-464B-861B-4976CFBE2EEC}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{F4B49C3B-5E5A-4C44-966C-A383082F1E2C}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7451,62 +7474,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F49">
-    <cfRule type="cellIs" dxfId="11" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F129">
-    <cfRule type="cellIs" dxfId="10" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140:F141">
-    <cfRule type="cellIs" dxfId="9" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F152:F153">
-    <cfRule type="cellIs" dxfId="8" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F164:F165">
-    <cfRule type="cellIs" dxfId="7" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F252:F253">
-    <cfRule type="cellIs" dxfId="6" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F258">
-    <cfRule type="cellIs" dxfId="5" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F262:F263">
-    <cfRule type="cellIs" dxfId="4" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F286:F287">
-    <cfRule type="cellIs" dxfId="3" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F291:F292">
-    <cfRule type="cellIs" dxfId="2" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296:F297">
-    <cfRule type="cellIs" dxfId="1" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45:H47 E212:G212">
-    <cfRule type="cellIs" dxfId="0" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15105,7 +15128,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEB3E54E-9905-434A-883A-4B73532B3F1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9935E46-35E8-4F6D-964D-A373358DD24C}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19097,18 +19120,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwAgAGkAbgBjAGwAdQBkAGkAbgBnACAAbABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIAAgAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADkALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMgAsACAAMAAuADAAMwAsACAANQAxAC4ANgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAGEAbAAgAG0AaQBuAGUAIAB3AGEAcwB0AGUAIABnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADkALAAgADQALgA2ACwAIAAwAC4AMwAsACAANQA2AC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAKAByAGUAdgBlAHIAdABpAG4AZwAgAHQAbwAgAHMAdABhAG4AZABhAHIAZAAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAKQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBwAHIAbwBjAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAANgAyADkALAAgAFwAIgBtADMAXAAiACwAIAA1ADYALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMAAzACwAIAA1ADYALgA1ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AawBlACAAbwB2AGUAbgAgAGcAYQBzAFwAIgAsACAAMAAuADAAMQA4ADEALAAgAFwAIgBtADMAXAAiACwAIAAzADcALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAA1ACwAIAAzADcALgAwADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGwAYQBzAHQAIABmAHUAcgBuAGEAYwBlACAAZwBhAHMAXAAiACwAIAAwAC4AMAAwADQAMAAsACAAXAAiAG0AMwBcACIALAAgADIAMwA0AC4AMAAsACAAMAAuADAAMwAsACAAMAAuADAAMgAsACAAMgAzADQALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMAAsACAAXAAiAG0AMwBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsATABcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBlAG8AdQBzACAAZgBvAHMAcwBpAGwAIABmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAYQBuAGQAZgBpAGwAbAAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIAAoAG0AZQB0AGgAYQBuAGUAIABvAG4AbAB5ACkAXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4ALAAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA3ADAALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBtAGUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAwADMALAAgADAALgAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAHkAZAByAG8AZwBlAG4AXAAiACwAIAAwAC4AMAAxADIAMgAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMAAsACAAMAAuADUALAAgADAALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgADEALAAgAFwAIgBHAEoAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAzACwAIAA2ADAALgAyADcAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABcAHUAMAAwADIANwBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAdQAwADAAMgA3ACAAdwBlAHIAZQAgAGEAZABkAGUAZAAsACAAZQBhAGMAaAAgAHcAaQB0AGgAIABhAG4AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgADEAIABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAC4AIABUAGgAaQBzACAAaQBzACAAZgBvAHIAIAB1AHMAZQByAHMAIAB3AGgAbwAgAGgAYQB2AGUAIABmAHUAZQBsACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAZABhAHQAYQAgAGkAbgAgAEcASgAgAHIAYQB0AGgAZQByACAAdABoAGEAbgAgAG0AMwAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAuAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABOAGEAdAB1AHIAYQBsACAARwBhAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABNAGUAdAByAG8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AbwBuACAALQAgAE0AZQB0AHIAbwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAOAAuADgALAAgADcALgA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAAxADAALgA3ACwAIAAxADAALgA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAANAAuADEALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAANAAuADAALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIAA0AC4AMQAsACAANAAuADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABOAFMAVwAgAGEAbgBkACAAQQBDAFQAIABzAHAAbABpAHQAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAcgBvAHcAcwAuACAAXAB1ADAAMAAyADcAQwBcAHUAMAAwADIANwAgAFYAYQBsAHUAZQBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAcgBlAHAAbABhAGMAZQBkACAAdwBpAHQAaAAgAHQAaABvAHMAZQAgAGYAbwByACAAVgBpAGMAdABvAHIAaQBhACAAYQBuAGQAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAByAGUAcwBwAGUAYwB0AGkAdgBlAGwAeQAuACAAKABTAGUAZQAgAGEAcABwAGUAbgBkAGkAYwBlAHMAKQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADIALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBBAHMAIABTAGMAbwBwAGUAIAAzACAAZgBhAGMAdABvAHIAcwAgAGEAcgBlACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGEAdAAgAHQAaABlACAAcABvAGkAbgB0ACAAdwBoAGUAcgBlACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAaQBzACAAZABlAGwAaQB2AGUAcgBlAGQAIAB0AG8AIABlAG4AZAAgAHUAcwBlAHIAcwAsACAAaQB0ACAAaQBzACAAbgBlAGMAZQBzAHMAYQByAHkAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAdAAgAGUAYQBjAGgAIABvAGYAIAB0AGgAZQAgAGwAbwBhAGQAIABjAGUAbgB0AHIAZQBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIARwBhAHMAIAByAGUAYQBjAGgAZQBzACAAZQBuAGQAIAB1AHMAZQByAHMAIABlAGkAdABoAGUAcgAgAGYAcgBvAG0AIAB0AGgAZQAgAG0AZQB0AHIAbwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAbgBlAHQAdwBvAHIAawBzACAAbwByACAAZABpAHIAZQBjAHQAIABmAHIAbwBtACAAdABoAGUAIABoAGkAZwBoACAALQAgAHAAcgBlAHMAcwB1AHIAZQAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBIAG8AdQBzAGUAaABvAGwAZABzACAAYQBuAGQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdQBzAGUAcgBzACAAdABlAG4AZAAgAHQAbwAgAGIAZQAgAHMAZQByAHYAZQBkACAAYgB5ACAAdABoAGUAIABmAG8AcgBtAGUAcgAsACAAYQBuAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABnAGUAbgBlAHIAYQB0AG8AcgBzACAAYQBuAGQAIABsAGEAcgBnAGUAIABpAG4AZAB1AHMAdAByAGkAYQBsACAAcABsAGEAbgB0AHMAIABmAHIAbwBtACAAdABoAGUAIABsAGEAdAB0AGUAcgAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIATQBlAHQAcgBvACAAaQBzACAAZABlAGYAaQBuAGUAZAAgAGEAcwAgAGwAbwBjAGEAdABlAGQAIABvAG4AIABvAHIAIABlAGEAcwB0ACAAbwBmACAAdABoAGUAIABkAGkAdgBpAGQAaQBuAGcAIAByAGEAbgBnAGUAIABpAG4AIABOAFMAVwAsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABDAGEAbgBiAGUAcgByAGEAIABhAG4AZAAgAFEAdQBlAGEAbgBiAGUAeQBhAG4ALAAgAE0AZQBsAGIAbwB1AHIAbgBlACwAIABCAHIAaQBzAGIAYQBuAGUALAAgAEEAZABlAGwAYQBpAGQAZQAgAG8AcgAgAFAAZQByAHQAaAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAE8AdABoAGUAcgB3AGkAcwBlACwAIAB0AGgAZQAgAG4AbwBuACAALQAgAG0AZQB0AHIAbwAgAGYAYQBjAHQAbwByACAAcwBoAG8AdQBsAGQAIABiAGUAIAB1AHMAZQBkAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBGAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABhAGwAbAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAB3AGgAaQBjAGgAIABtAGEAeQAgAGkAbgBjAGwAdQBkAGUAIABjAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFQAYQBiAGwAZQAgADYAIABpAHMAIABuAG8AdAAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIAB0AG8AIABlAHQAaABhAG4AZQAuACAAUwBlAGUAIABUAGEAYgBsAGUAIAA3ACAASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGUAdABoAGEAbgBlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBDACAAPQAgAEMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAC4AIABTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAVABhAHMAbQBhAG4AaQBhACAAYQBuAGQAIAB0AGgAZQAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAYQByAGUAIABuAG8AdAAgAGEAdgBhAGkAbABhAGIAbABlACAAZAB1AGUAIAB0AG8AIABjAG8AbgBmAGkAZABlAG4AdABpAGEAbABpAHQAeQAgAGMAbwBuAHMAdAByAGEAaQBuAHQAcwAgAHQAaABhAHQAIABhAHIAaQBzAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABhACAAbABpAG0AaQB0AGUAZAAgAG4AdQBtAGIAZQByACAAbwBmACAATgBHAEUAUgAgAGQAYQB0AGEAIABpAG4AcAB1AHQAcwAuACAASQB0ACAAaQBzACAAcwB1AGcAZwBlAHMAdABlAGQAIAB0AGgAYQB0ACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABWAGkAYwB0AG8AcgBpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgB3AGgAaQBsAGUAIABmAG8AcgAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHQAaABlACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAaQBzACAAYQBwAHAAcgBvAHAAcgBpAGEAdABlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGQAbwAgAG4AbwB0ACAAaQBuAGMAbAB1AGQAZQAgAGYAdQBnAGkAdABpAHYAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGwAZQBhAGsAYQBnAGUAIABmAHIAbwBtACAAbABvAHcAIABwAHIAZQBzAHMAdQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABpAG8AbgAgAHAAaQBwAGUAbABpAG4AZQAgAG4AZQB0AHcAbwByAGsAcwAgAHcAaABpAGwAZQAgAHQAaABvAHMAZQAgAGYAcgBvAG0AIABoAGkAZwBoACAAcAByAGUAcwBzAHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAGcAYQBzACAAbgBlAHQAdwBvAHIAawBzACAAYQByAGUAIABjAG8AbgBzAGkAZABlAHIAZQBkACAAbgBlAGcAbABpAGcAaQBiAGwAZQAuAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGEAbgBkACAAaQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAZQByAHQAYQBpAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgA1ACwAIAA4ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABjAG8AbQBiAHUAcwB0AGUAZABcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAEMAbwBuAHQAZQBuAHQAIABGAGEAYwB0AG8AcgAgACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbABzACAAKABvAHQAaABlAHIAIAB0AGgAYQBuACAAcABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbAAgAHUAcwBlAGQAIABhAHMAIABmAHUAZQBsACkALAAgAGUALgBnAC4AIABsAHUAYgByAGkAYwBhAG4AdABzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADEAMwAuADkALAAgADAALgAwACwAIAAwAC4AMAAsACAAMQAzAC4AOQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAZwByAGUAYQBzAGUAcwBcACIALAAgADMAOAAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAzAC4ANQAsACAAMAAuADAALAAgADAALgAwACwAIAAzAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAcgB1AGQAZQAgAG8AaQBsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABjAHIAdQBkAGUAIABvAGkAbAAgAGMAbwBuAGQAZQBuAHMAYQB0AGUAcwBcACIALAAgADQANQAuADMALAAgAFwAIgB0AFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADYAOQAuADgAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABsAGkAcQB1AGkAZABzAFwAIgAsACAANAA2AC4ANQAsACAAXAAiAHQAXAAiACwAIAA2ADEALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgAxAC4AMgA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdQB0AG8AbQBvAHQAaQB2AGUAIABnAGEAcwBvAGwAaQBuAGUAIAAvACAAcABlAHQAcgBvAGwAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADAALgAyACwAIAAwAC4AMgAsACAANgA3AC4AOAAwACwAIAAxADcALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuACAAZwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsATABcACIALAAgADYANwAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA0ADAALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBLAGUAcgBvAHMAZQBuAGUAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA3AC4ANQAsACAAXAAiAGsATABcACIALAAgADYAOAAuADkALAAgADAALgAwADEALAAgADAALgAyACwAIAA2ADkALgAxADEALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIAB0AHUAcgBiAGkAbgBlACAAZgB1AGUAbAAgAC8AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYAOQAuADgAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHQAaQBuAGcAIABvAGkAbABcACIALAAgADMANwAuADMALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4ANwAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADcAMAAuADIAMAAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA0ACwAIAAwAC4AMgAsACAANwAzAC4AOAA0ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABhAHIAbwBtAGEAdABpAGMAIABoAHkAZAByAG8AYwBhAHIAYgBvAG4AcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAdgBlAG4AdABzADoAIABtAGkAbgBlAHIAYQBsACAAdAB1AHIAcABlAG4AdABpAG4AZQAgAG8AcgAgAHcAaABpAHQAZQAgAHMAcABpAHIAaQB0AHMAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADIALAAgADYAOQAuADkAMwAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYAMAAuADYAMAAsACAAMgAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQBwAGgAdABoAGEAXAAiACwAIAAzADEALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABjAG8AawBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAHQAXAAiACwAIAA5ADIALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAOQAyAC4AOAA4ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAZwBhAHMAIABhAG4AZAAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADIALgA5ACwAIABcACIAdABcACIALAAgADUANAAuADcALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANAAuADcANgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGkAbgBlAHIAeQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADgALAAgADAALgAwADIALAAgADAALgAxACwAIAA2ADkALgA5ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAG8AbAAgAGYAbwByACAAdQBzAGUAIABhAHMAIABhACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGkAbgB0AGUAcgBuAGEAbAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABlAG4AZwBpAG4AZQBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBpAG8AZgB1AGUAbABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAIABhAG4AZAAgAGIAZQBsAG8AdwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAwADIALAAgADAALgAyACwAIAAwAC4AMgAyACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADMAMAAsACAAXAAiAE4ARQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAIABpAG4AIABkAGkAZgBmAGUAcgBlAG4AdAAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADkAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADYALAAgADEAMAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAXAAiACwAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBsAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYANwAuADYAMgAsACAAMQA3AC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAANwAwAC4ANAAxACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAHAAZQB0AHIAbwBsAGUAdQBtACAAZwBhAHMAIAAoAEwAUABHACkAXAAiACwAIAAyADYALgAyACwAIABcACIAawBsAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADUALAAgADAALgAzACwAIAA2ADEALgAwADAALAAgADIAMAAuADIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAGwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4ANQAsACAANwA0AC4AMQA4ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBFAHQAaABhAG4AbwBsAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADIALAAgADAALgA0ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQgBpAG8AZABpAGUAcwBlAGwAXAAiACwAIAAzADQALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgA4ACwAIAAxAC4ANwAsACAAMgAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAAMAAuADUAMQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAE8AdABoAGUAcgAgAGIAaQBvAGYAdQBlAGwAcwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAZwBoAHQAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADcALgAzACwAIAAwAC4AMwAsACAANQA5AC4AMAAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBDAG8AbQBwAHIAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAyAC4AOAAsACAAMAAuADMALAAgADUANAAuADUALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsAbABcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADAANwAsACAAMAAuADQALAAgADcAMAAuADMANwAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADEALAAgADAALgA0ACwAIAA3ADAALgA0ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANAAsACAANwAwAC4ANQAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADcALAAgADAALgA0ACwAIAAwAC4ANAA3ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4ANAAsACAAMAAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADQALAAgADAALgA2ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdABcACIALAAgADMAMwAuADEALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgAwACwAIAAwAC4AMAA2ACwAIAAwAC4ANgAsACAANgA3AC4ANgA2ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwA2AC4AOAAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADYALAAgADAALgAwADEALAAgADAALgA2ACwAIAA3ADAALgAyADEALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA2ACwAIAAwAC4ANgAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADEAMAAuADEALAAgADAALgAzACwAIABcACIAXAAiACwAIAAxADcALgAyACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIABcACIAXAAiACwAIAAxADcALgAzACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEAOAAuADAALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAE8AZgBmAC0AcgBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAaQBuACAAbwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQAgAHEAXAAiACwAIABcACIARQBDAFQAcgBhAG4AcwAsAHEAIAAoAEcASgAvAGsATAApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAE8AMgAgAEUARgBUAHIAYQBuACwAMQAsAHQAcQBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAQwBIADQAIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAE4AMgBPACAARQBGAFQAcgBhAG4ALAAxACwAdABnAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAEYAVAByAGEAbgBzACwAMwAsAHEAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAFAAZQB0AHIAbwBsAFwAIgAsACAAMwA0AC4AMgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgADEANwAuADMAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAATABFAEYAVAAoAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQAgAC0AMQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8ARwBlAHQAUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAFMAdAByAGkAbgBnAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFIASQBHAEgAVAAoAEMAZQBsAGwALABMAEUATgAoAEMAZQBsAGwAKQAtAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8AVABvAHQAYQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBcAG4APQAgAEwAQQBNAEIARABBACgAXABuACAAIAAgACAARgB1AGUAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAsACAARgB1AGUAbABVAHMAZQAsACAARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAsACAARgB1AGUAbABUAHkAcABlACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgAFMAVQBNACgAXABuACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAXABuACAAIAAgACAAIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFQAeQBwAGUAKQAgACoAIABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABVAHMAZQBBAHIAcgBhAHkAIAA9ACAARgB1AGUAbABVAHMAZQApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIAAwAFwAbgAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgAOgAgAEYAdQBlAGwAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA4AC4AMQAgAEYAdQBlAGwAIABVAHMAZQAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsACAARQBDACwAIABFAEYALABcAG4AIAAgACAAIAAoAFEAIAAqACAARQBDACAAKgAgAEUARgApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAGMAbwBtAGIAdQBzAHQAZQBkACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAGsATABcAG4ARQBDACAAOgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwAgADoAIABrAGcAIABDAE8AMgBlACAALwAgAEcASgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AVAByAGEAbgBzAHQAcQAsACAARQBDAF8AVAByAGEAbgBzAHEALAAgAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADgALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADMAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFQAcgBhAG4AcwAsAHQAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEMAXwB7AFQAcgBhAG4AcwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBUAHIAYQBuAHMALAAxACwAdABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBUAHIAYQBuAHMAdABxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlACAALwAgAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHEAXAAiACwAIABcACIARgB1AGUAbAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAXAAiACwAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXABuAFEAIAA6ACAAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABHAEoALwBrAEwAXABuAEUARgAgADoAIABTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBTAEMAcQAsACAARQBDAF8AUwBDAHEALAAgAEUARgBfAFMAQwAxAHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgADIALgAyACAARQBzAHQAaQBtAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABlAG4AZQByAGcAeQAgAHMAbwB1AHIAYwBlAHMAIAAtACAAQwBhAGwAYwB1AGwAYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHQAIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEAXABcAGwAZQBmAHQAKABRAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAUwBDACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFMAQwAsADEALABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFMAQwBxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAdQBzAGUAZAAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAFYAYQByAGkAZQBzACAAYgBhAHMAZQBkACAAbwBuACAAZgB1AGUAbAAgAHQAeQBwAGUAOgAgAGsATAAsACAAbQAzACwAIABHAEoAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMAXwBTAEMAcQBcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFMAQwAxAHEAZwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQwBcACIALAAgAFwAIgBTAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAMQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA5ADoAIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA5AC4AMQAgAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgBUAGgAZQAgAHQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBpAG4AZwAgAGQAdQByAGkAbgBnACAAbwBwAGUAcgBhAHQAaQBvAG4AIAAoAG4AbwB0ACAAZAB1AHIAaQBuAGcAIABpAG4AcwB0AGEAbABsAGEAdABpAG8AbgAgAG8AcgAgAGQAaQBzAHAAbwBzAGEAbAApAFwAbgBHAFcAUABSACAAOgAgAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgADoAIABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBjAGgAYQByAGcAZQBfAFIAYQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIABjAG8AbgB0AGEAaQBuAGUAZAAgAGkAbgAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgADoAIABrAGcAXABuAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEAIAA6ACAAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByACAAOgAgAFAAZQByAGMAZQBuAHQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGMAaABhAHIAZwBlAF8AUgBhACwAIABsAGUAYQBrAGEAZwBlAHIAYQB0AGUAXwBhACwAXABuACAAIAAgACAAKABjAGgAYQByAGcAZQBfAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALwAxADAAMAApACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAFIALAAgAEcAVwBQAF8AUgAsAFwAbgAgACAAIAAgACgAKABFAF8AUgAgACoAIAAxADAAXgAzACkAIAAqACAARwBXAFAAXwBSACkAIAAqACAAMQAwAF4ALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGEAZwBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABjAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBSAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGcAYQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADkALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMwAuADEAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAaQBuAGQAdQBzAHQAcgBpAGEAbAAgAHAAcgBvAGMAZQBzAHMAZQBzACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAtACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBhAGcAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBjAGgAYQByAGcAZQBfAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALwAxADAAMAApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AUgAgAD0AIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGEAIABcAFwAbABlAGYAdAAoACAAYwBoAGEAcgBnAGUAXwB7AFIAYQB9ACAAXABcAHQAaQBtAGUAcwAgAFwAXABmAHIAYQBjAHsAbABlAGEAawBhAGcAZQBcAFwALAByAGEAdABlAF8AYQB9AHsAMQAwADAAfQAgAFwAXAByAGkAZwBoAHQAKQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBDAE8AMgBlACAAPQAgAFwAXABsAGUAZgB0ACgARQBfAFIAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AIABcAFwAcgBpAGcAaAB0ACkAIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwBSACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAGgAYQByAGcAZQBfAFIAYQBcACIALAAgAFwAIgBBAG0AbwB1AG4AdAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIABjAG8AbgB0AGEAaQBuAGUAZAAgAGkAbgAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBsAGUAYQBrAGEAZwBlAHIAYQB0AGUAXwBhAFwAIgAsACAAXAAiAFAAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAAdABvAHQAYQBsACAAYwBoAGEAcgBnAGUAIABsAGUAYQBrAGUAZAAgAGYAcgBvAG0AIABhAHAAcABsAGkAYQBuAGMAZQAgAGEAIABlAGEAYwBoACAAeQBlAGEAcgBcACIALAAgAFwAIgBQAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYQBcACIALAAgAFwAIgBBAHAAcABsAGkAYQBuAGMAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAFwAIgAsACAAXAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAFIAXAAiACwAIABcACIAVABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSAFwAIgAsACAAXAAiAHQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABnAGEAcwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADkALgAxAC4AMQAgACgAMQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABfAFIAXAAiACwAIABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSAFwAIgAsACAAXAAiAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAZQBxAHUAYQB0AGkAbwBuACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIAB0AG8AIABDAE8AMgAtAGUAIAB1AHMAaQBuAGcAIAB0AGgAZQAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABcAHUAMAAwADIANwBzACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIAAoAEcAVwBQACkALgBcACIAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAVABhAGIAbABlACAAMgAzACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAQQBwAHAAZQBuAGQAaQB4ACAAMgAgAC0AIABUAGEAYgBsAGUAIAAyADMAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMAOQAsACAANQAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAGgAZQBtAGkAYwBhAGwAIABmAG8AcgBtAHUAbABhAFwAIgAsACAAXAAiAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAKABBAFIANQApAFwAIgAsACAAXAAiAEcAYQBzACAALQAgAEYAQwAgAG4AYQBtAGUAXAAiACwAIABcACIAQQBkAGkAdABpAG8AbgBhAGwAIABkAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlAFwAIgAsACAAXAAiAEMATwAyAFwAIgAsACAAMQAsACAAXAAiAEMATwAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAQwBIADQAXAAiACwAIAAyADgALAAgAFwAIgBDAEgANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlAFwAIgAsACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUALAAgAFwAIgBOADIATwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAbABwAGgAdQByACAAaABlAHgAYQBmAGwAdQBvAHIAaQBkAGUAXAAiACwAIABcACIAUwBGADYAXAAiACwAIAAyADMANQAwADAALAAgAFwAIgBTAEYANgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMwAgACgAUgAtADIAMwApAFwAIgAsACAAXAAiAEMASABGADMAXAAiACwAIAAgADEAMgA0ADAAMAAsACAAXAAiAEgARgBDAC0AMgAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMwAyACAAKABSAC0AMwAyACkAXAAiACwAIABcACIAQwBIADIARgAyAFwAIgAsACAANgA3ADcALAAgAFwAIgBIAEYAQwAtADMAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADQAMQAgACgAUgAtADQAMQApAFwAIgAsACAAXAAiAEMASAAzAEYAXAAiACwAIAAgADEAMQA2ACwAIABcACIASABGAEMALQA0ADEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQA0ADMALQAxADAAbQBlAGUAIAAoAFIALQA0ADMAMQAwAG0AZQBlACkAXAAiACwAIABcACIAQwA1AEgAMgBGADEAMABcACIALAAgADEANgA1ADAALAAgAFwAIgBIAEYAQwAtADQAMwAtADEAMABtAGUAZQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMgA1ACAAKABSAC0AMQAyADUAKQBcACIALAAgAFwAIgBDADIASABGADUAXAAiACwAIAAgADMAMQA3ADAALAAgAFwAIgBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAzADQAIAAoAFIALQAxADMANAApAFwAIgAsACAAXAAiAEMAMgBIADIARgA0ACAAKABDAEgARgAyAEMASABGADIAKQBcACIALAAgACAAMQAxADIAMAAsACAAXAAiAEgARgBDAC0AMQAzADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADMANABhACAAKABSAC0AMQAzADQAYQApAFwAIgAsACAAXAAiAEMAMgBIADIARgA0ACAAKABDAEgAMgBGAEMARgAzACkAXAAiACwAIAAxADMAMAAwACwAIABcACIASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA0ADMAIAAoAFIALQAxADQAMwApAFwAIgAsACAAXAAiAEMAMgBIADMARgAzACAAKABDAEgARgAyAEMASAAyAEYAKQBcACIALAAgADMAMgA4ACwAIABcACIASABGAEMALQAxADQAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEANAAzAGEAIAAoAFIALQAxADQAMwBhACkAXAAiACwAIABcACIAQwAyAEgAMwBGADMAIAAoAEMARgAzAEMASAAzACkAXAAiACwAIAA0ADgAMAAwACwAIABcACIASABGAEMALQAxADQAMwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA1ADIAYQAgACgAUgAtADEANQAyAGEAKQBcACIALAAgAFwAIgBDADIASAA0AEYAMgAgACgAQwBIADMAQwBIAEYAMgApAFwAIgAsACAAMQAzADgALAAgAFwAIgBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADIANwBlAGEAIAAoAFIALQAyADIANwBlAGEAKQBcACIALAAgAFwAIgBDADMASABGADcAXAAiACwAIAAzADMANQAwACwAIABcACIASABGAEMALQAyADIANwBlAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADMANgBmAGEAIAAoAFIALQAyADMANgBmAGEAKQBcACIALAAgAFwAIgBDADMASAAyAEYANgBcACIALAAgADgAMAA2ADAALAAgAFwAIgBIAEYAQwAtADIAMwA2AGYAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIANAA1AGMAYQAgACgAUgAtADIANAA1AGMAYQApAFwAIgAsACAAXAAiAEMAMwBIADMARgA1AFwAIgAsACAANwAxADYALAAgAFwAIgBIAEYAQwAtADIANAA1AGMAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIANAA1AGYAYQAgACgAUgAtADIANAA1AGYAYQApAFwAIgAsACAAXAAiAEMASABGADIAQwBIADIAQwBGADMAXAAiACwAIAA4ADUAOAAsACAAXAAiAEgARgBDAC0AMgA0ADUAZgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMwA2ADUAbQBmAGMAIAAoAFIALQAzADYANQBtAGYAYwApAFwAIgAsACAAXAAiAEMASAAzAEMARgAyAEMASAAyAEMARgAzAFwAIgAsACAAOAAwADQALAAgAFwAIgBIAEYAQwAtADMANgA1AG0AZgBjAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIAIAAoAFIALQAyADIAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAMgBcACIALAAgADEANwA2ADAALAAgAFwAIgBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADIAMwAgACgAUgAtADEAMgAzACkAXAAiACwAIABcACIAQwBIAEMAbAAyADIAQwBGADMAXAAiACwAIAA3ADkALAAgAFwAIgBIAEMARgBDAC0AMQAyADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEAMgA0ACAAKABSAC0AMQAyADQAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAQwBGADMAXAAiACwAIAA1ADIANwAsACAAXAAiAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQA0ADEAYgAgACgAUgAtADEANAAxAGIAKQBcACIALAAgAFwAIgBDAEgAMwBDAEMAbAAyAEYAXAAiACwAIAA3ADgAMgAsACAAXAAiAEgAQwBGAEMALQAxADQAMQBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADQAMgBiACAAKABSAC0AMQA0ADIAYgApAFwAIgAsACAAXAAiAEMASAAyAEMAQwBsAEYAMgBcACIALAAgADEAOQA4ADAALAAgAFwAIgBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBhACAAKABSAC0AMgAyADUAYwBhACkAXAAiACwAIABcACIAQwBIAEMAbAAyAEMARgAyAEMARgAzAFwAIgAsACAAMQAyADcALAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGIAIAAoAFIALQAyADIANQBjAGIAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAQwBGADIAQwBDAEkARgAyAFwAIgAsACAANQAyADUALAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMQA0ACAAUABlAHIAZgBsAHUAbwByAG8AbQBlAHQAaABhAG4AZQAgACgAdABlAHQAcgBhAGYAbAB1AG8AcgBvAG0AZQB0AGgAYQBuAGUAKQBcACIALAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAALAAgAFwAIgBQAEYAQwAtADEANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADEAMQA2ACAAUABlAHIAZgBsAHUAbwByAG8AZQB0AGgAYQBuAGUAIAAoAGgAZQB4AGEAZgBsAHUAbwByAG8AZQB0AGgAYQBuAGUAKQBcACIALAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAxADEAMAAwACwAIABcACIAUABGAEMALQAxADEANgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADIAMQA4ACAAUABlAHIAZgBsAHUAbwByAG8AcAByAG8AcABhAG4AZQBcACIALAAgAFwAIgBDADMARgA4AFwAIgAsACAAOAA5ADAAMAAsACAAXAAiAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAzADEALQAxADAAIABQAGUAcgBmAGwAdQBvAHIAbwBiAHUAdABhAG4AZQBcACIALAAgAFwAIgBDADQARgAxADAAXAAiACwAIAA5ADIAMAAwACwAIABcACIAUABGAEMALQAzADEALQAxADAAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAzADEAOAAgAFAAZQByAGYAbAB1AG8AcgBvAGMAeQBjAGwAbwBiAHUAdABhAG4AZQBcACIALAAgAFwAIgBjAC0AQwA0AEYAOABcACIALAAgADkANQA0ADAALAAgAFwAIgBQAEYAQwAtADMAMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0ANAAxAC0AMQAyACAAUABlAHIAZgBsAHUAbwByAG8AcABlAG4AdABhAG4AZQBcACIALAAgAFwAIgBDADUARgAxADIAXAAiACwAIAA4ADUANQAwACwAIABcACIAUABGAEMALQA0ADEALQAxADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA1ADEALQAxADQAIABQAGUAcgBmAGwAdQBvAHIAbwBoAGUAeABhAG4AZQBcACIALAAgAFwAIgBDADYARgAxADQAXAAiACwAIAA3ADkAMQAwACwAIABcACIAUABGAEMALQA1ADEALQAxADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA5ADEALQAxADgAIABQAGUAcgBmAGwAdQBuAGEAZgBlAG4AZQBcACIALAAgAFwAIgBDADEAMABGADEAOABcACIALAAgADcAMQA5ADAALAAgAFwAIgBQAEYAQwAtADkAMQAtADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMgBcACIALAAgAFwAIgBDAEMAbAAyAEYAMgBcACIALAAgADEAMAAyADAAMAAsACAAXAAiAEMARgBDAC0AMQAyAFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADMAXAAiACwAIABcACIAQwBDAGwARgAzAFwAIgAsACAAMQAzADkAMAAwACwAIABcACIAQwBGAEMALQAxADMAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAEMAQwBsAEYAMgBDAEMAbABGADIAXAAiACwAIAA4ADUAOQAwACwAIABcACIAQwBGAEMALQAxADEANABcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAQwBDAGwARgAyAEMARgAzAFwAIgAsACAANwA2ADcAMAAsACAAXAAiAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcARwBBAFMAIAAtACAARgBDACAAbgBhAG0AZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAHQAcgB1AG4AYwBhAHQAZQBkACAAZwBhAHMAIABuAGEAbQBlACAAdABvACAAYQBsAGwAbwB3ACAAbQBhAHQAYwBoAGkAbgBnACAAdwBpAHQAaAAgAG8AdABoAGUAcgAgAHQAYQBiAGwAZQBzAC4AIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABnAGEAcwBlAHMAIABmAHIAbwBtACAASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQAuACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAQQBkAGQAaQB0AGkAbwBuAGEAbAAgAGQAYQB0AGEAIABzAG8AdQByAGMAZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAC4AXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAQgBsAGUAbgBkAGUAZAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAbABlAG4AZABlAGQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAcwAgACgAbQBhAG4AeQAgAGMAbwBuAHQAYQBpAG4AaQBuAGcAIABIAEYAQwBTACAAYQBuAGQALwBvAHIAIABQAEYAQwBTACkAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABBAHAAcABlAG4AZABpAHgAIAAyACAALQAgAFQAYQBiAGwAZQAgADIANABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAxACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABlAG4AZABcACIALAAgAFwAIgBDAG8AbgBzAHQAaQB0AHUAZQBuAHQAcwBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwBpAHQAaQBvAG4AIAAoACUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAFIALQA0ADAAMAAgAGMAYQBuACAAaABhAHYAZQAgAHYAYQByAGkAbwB1AHMAIABwAHIAbwBwAG8AcgB0AGkAbwBuAHMAIABvAGYAIABDAEYAQwAtADEAMgAgAGEAbgBkACAAQwBGAEMALQAxADEANAAuACAAVABoAGUAIABlAHgAYQBjAHQAIABjAG8AbQBwAG8AcwBpAHQAaQBvAG4AIABuAGUAZQBkAHMAIAB0AG8AIABiAGUAIABzAHAAZQBjAGkAZgBpAGUAZAAsACAAZQAuAGcALgAsACAAUgAtADQAMAAwACAAKAA2ADAALwA0ADAAKQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAA1ADMALgAwAC8AMQAzAC4AMAAvADMANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgANgAxAC4AMAAvADEAMQAuADAALwAyADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEMAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADMAMwAuADAALwAxADUALgAwAC8ANQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA2ADAALgAwAC8AMgAuADAALwAzADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAyAEIAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADMAOAAuADAALwAyAC4AMAAvADYAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADMAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANQAuADAALwA3ADUALgAwAC8AMgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMwBCAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA1AC4AMAAvADUANgAuADAALwAzADkALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA0AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADQANAAuADAALwA1ADIALgAwAC8ANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADUAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AIABIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQA0ADIAYgAvAFAARgBDAC0AMwAxADgAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANwAuADAALwA1AC4ANQAvADQAMgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADYAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQA1AC4AMAAvADEANAAuADAALwA0ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAwAC4AMAAvADQAMAAuADAALwA0ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEIAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQAwAC4AMAAvADcAMAAuADAALwAyADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEMAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAzAC4AMAAvADIANQAuADAALwA1ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEQAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQA1AC4AMAAvADEANQAuADAALwA3ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEUAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgA1AC4AMAAvADEANQAuADAALwA2ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA4AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA3AC4AMAAvADQANgAuADAALwA0ADcALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgAwAC4AMAAvADIANQAuADAALwAxADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgA1AC4AMAAvADIANQAuADAALwAxADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAwAEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiACgANQAwAC4AMAAvADUAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADAAQgBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANQA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBBAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMQAuADUALwA4ADcALgA1AC8AMQAxAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBCAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMwAuADAALwA5ADQALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADEAQwBcACIALAAgAFwAIgBIAEMALQAxADIANwAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADMALgAwAC8AOQA1AC4ANQAvADEALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAyAEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADcAMAAuADAALwA1AC4AMAAvADIANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADMAQQBcACIALAAgAFwAIgBQAEYAQwAtADIAMQA4AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADkALgAwAC8AOAA4AC4AMAAvADMALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMQAuADAALwAyADgALgA1AC8ANAAuADAALwAxADYALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMAAuADAALwAzADkALgAwAC8AMQAuADUALwA5AC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA4ADIALgAwAC8AMQA4AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAyADUALgAwAC8ANwA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAFwAIgAsACAAXAAiACgANQA5AC4AMAAvADMAOQAuADUALwAxAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABcACIALAAgAFwAIgAoADQANgAuADYALwA1ADAALgAwAC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADgAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAxAC4ANQAvADkANgAuADAALwAyAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAOQBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEUALQBFADEANwAwAFwAIgAsACAAXAAiACgANwA3AC4AMAAvADEAOQAuADAALwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMABBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgAOAA4AC4AMAAvADEAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADEAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgANQA4AC4AMAAvADQAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgANQAuADEALwAxADEALgA1AC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQgBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADUANQAuADAALwA0ADIALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQwBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgAMgAuADAALwAxADUALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA3ADMALgA4AC8AMgA2AC4AMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADIAXAAiACwAIABcACIAKAA3ADUALgAwAC8AMgA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADEANQBcACIALAAgAFwAIgAoADQAOAAuADgALwA1ADEALgAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAzAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AQwBGAEMALQAxADMAXAAiACwAIABcACIAKAA0ADAALgAxAC8ANQA5AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANABcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAKAA0ADgALgAyAC8ANQAxAC4AOAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANQBcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEgAQwBGAEMALQAzADEAXAAiACwAIABcACIAKAA3ADgALgAwAC8AMgAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANgBcACIALAAgAFwAIgBDAEYAQwAtADMAMQAvAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAKAA1ADUALgAxAC8ANAA0AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEANAAzAGEAXAAiACwAIABcACIAKAA1ADAALgAwAC8ANQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOABBAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AUABGAEMALQAxADEANgBcACIALAAgAFwAIgAoADMAOQAuADAALwA2ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA4AEIAXAAiACwAIABcACIASABGAEMALQAyADMALwBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiACgANAA2AC4AMAAvADUANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADkAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADQANAAuADAALwA1ADYALgAwACkAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAYwBoAGEAbgBnAGUAZAAgAEgAQwA2ADAAMABhACAAdABvACAASABDAC0ANgAwADAAYQAgAGYAbwByACAAYgBsAGUAbgBkACAAUgAtADQAMQA0AEIALgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABmAG8AcgAgAGIAbABlAG4AZAAgAFIALQA0ADAANQBBACAALQAgAEMAaABhAG4AZwBlAGQAIABIAEMARgBDADEANAAyAGIAIAB0AG8AIABIAEMARgBDAC0AMQA0ADIAYgAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEwAZQBhAGsAYQBnAGUAIAByAGEAdABlAHMAIABmAG8AcgAgAGMAbwBtAG0AbwBuACAAcgBlAGYAcgBpAGcAZQByAGEAdABpAG8AbgAgAGEAbgBkACAAYQBpAHIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAGMAYQB0AGkAdgBlACAAbABlAGEAawBhAGcAZQAgAHIAYQB0AGUAcwAgAGYAbwByACAAYwBvAG0AbQBvAG4AIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuACAAYQBuAGQAIABhAGkAcgAgAC0AIABjAG8AbgBkAGkAdABpAG8AbgBpAG4AZwAgAGUAcQB1AGkAcABtAGUAbgB0AFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADEAMABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ADEALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAGwAZQBhAGsAYQBnAGUAIAByAGEAdABlACAAKAAlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAcgBlAGYAcgBpAGcAZQByAGEAdABvAHIAcwBcACIALAAgADEALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuAFwAIgAsACAAMQA1AC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcABvAHIAdABhAGIAbABlAFwAIgAsACAAMgAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHMAcABsAGkAdABcACIALAAgADMALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABwAGEAYwBrAGEAZwBlAGQAXAAiACwAIAAyAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAHYAZQBoAGkAYwBsAGUAIABBAC8AQwBcACIALAAgADYALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAdgBlAGgAaQBjAGwAZQAgAEEALwBDAFwAIgAsACAAMQAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBhAGwAYwB1AGwAYQB0AGUAQgBsAGUAbgBkAEcAVwBQAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMQAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMgAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMwAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAANAAsAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAxACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAyACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAzACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAA0ACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0ACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGEAbABjAHUAbABhAHQAZQBCAGwAZQBuAGQARwBXAFAAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0